--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="233">
   <si>
     <t xml:space="preserve">KONFIGURATION</t>
   </si>
@@ -388,6 +388,9 @@
     <t xml:space="preserve">Konverteringen stiger for anden måned i træk, og churn normaliseres efter maj-toppen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Juli sætter rekord: 1.461 signups og 10 pct. konvertering midt i lavsæsonen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hvad skete der (2-3 sætn.)</t>
   </si>
   <si>
@@ -397,6 +400,9 @@
     <t xml:space="preserve">Sign-ups landede på 984, et forventet sæsonfald fra maj (1.035), men konverteringen steg igen — blended CVR ramte 6,4% mod 5,8% i maj. Google leverede 74 kunder til en CAC på 133 kr. (kanalens næstbedste måned), og Brand search fastholdt det høje niveau med 446 kunder. Churn faldt tilbage fra 2,6% til 2,2%, og vi rundede 13.318 aktive kunder (+582).</t>
   </si>
   <si>
+    <t xml:space="preserve">Juli blev den største måned i Altid Energis historie med 1.461 signups, klart over den tidligere rekord på 1.300 fra februar. Blended konvertering ramte 10,0 pct. (ny rekord), og blended CAC faldt til 131 kr. fra 157 kr. Brand search leverede 733 kunder (rekord), Google sin bedste konverteringsmåned (CVR 11,1 pct., CAC 105 kr.), og affiliates voksede til 334 kunder. Aktive kunder rundede 13.970 (+652), og churn holdt sig stabil på 2,2 pct.</t>
+  </si>
+  <si>
     <t xml:space="preserve">WINS — HVAD VIRKEDE</t>
   </si>
   <si>
@@ -409,6 +415,9 @@
     <t xml:space="preserve">Blended CVR ramte 6,4% — anden stigning i træk (3,8% → 5,8% → 6,4%) på trods af lavere trafik.</t>
   </si>
   <si>
+    <t xml:space="preserve">1.461 signups, den højeste måned nogensinde (tidligere rekord 1.300 i februar), leveret midt i sommerlavsæsonen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Win 2</t>
   </si>
   <si>
@@ -418,6 +427,9 @@
     <t xml:space="preserve">Churn faldt fra maj's rekordhøje 2,6% til 2,2%, og aktive kunder rundede 13.318 (+582 netto).</t>
   </si>
   <si>
+    <t xml:space="preserve">Blended CVR ramte 10,0 pct. (rekord), og blended CAC faldt til 131 kr. fra 157 kr.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Win 3</t>
   </si>
   <si>
@@ -427,6 +439,9 @@
     <t xml:space="preserve">Google leverede 74 kunder (næstbedste måned nogensinde) til CAC 133 kr., og Brand search fastholdt momentum med 446 kunder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Brand search satte rekord med 733 kunder, og Meta CAC faldt til 252 kr. fra 561 kr. efter optimeringen mod køb.</t>
+  </si>
+  <si>
     <t xml:space="preserve">WATCH-OUTS — OBS OMRÅDER</t>
   </si>
   <si>
@@ -439,6 +454,9 @@
     <t xml:space="preserve">Meta-CAC steg til 561 kr. (fra 432 kr.) — et normalt sæsonmønster, når efterspørgslen falder hen over sommeren. 80 kunder i lavsæsonen er reelt bedre end forventet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Organisk trafik lå på 3.640 klik, fortsat sommerlavt. 389.000 eksponeringer viser dog stærk synlighed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Watch 2</t>
   </si>
   <si>
@@ -466,6 +484,9 @@
     <t xml:space="preserve">Konverteringsarbejdet på hjemmesiden virker: blended CVR er steget to måneder i træk (3,8% → 5,8% → 6,4%) på trods af lavere trafik. Volumen — ikke konvertering — er nu den primære begrænsning ind i sommerens lavsæson.</t>
   </si>
   <si>
+    <t xml:space="preserve">Efterspørgslen fra de 32.500 tvangsflyttede elkunder ramte direkte ned i et optimeret setup: rekordhøj brand search, stigende konvertering og faldende CAC på samme tid. Volumen kom tilbage langt tidligere end ventet i lavsæsonen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Markedsnote / konkurrence</t>
   </si>
   <si>
@@ -473,6 +494,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.500 danske elkunder tvangsflyttes fra deres nuværende leverandører.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.500 danske elkunder er tvangsflyttet fra deres leverandører i sommerens løb.</t>
   </si>
   <si>
     <t xml:space="preserve">NEXT MONTH FOCUS</t>
@@ -2105,8 +2129,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94899266"/>
-        <c:axId val="49404710"/>
+        <c:axId val="86917899"/>
+        <c:axId val="31025123"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2291,11 +2315,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="98418137"/>
-        <c:axId val="9044728"/>
+        <c:axId val="4644969"/>
+        <c:axId val="16117395"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="94899266"/>
+        <c:axId val="86917899"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2326,7 +2350,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49404710"/>
+        <c:crossAx val="31025123"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2334,7 +2358,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="49404710"/>
+        <c:axId val="31025123"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2399,12 +2423,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94899266"/>
+        <c:crossAx val="86917899"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:dateAx>
-        <c:axId val="98418137"/>
+        <c:axId val="4644969"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2435,7 +2459,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9044728"/>
+        <c:crossAx val="16117395"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2443,7 +2467,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="9044728"/>
+        <c:axId val="16117395"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2508,7 +2532,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98418137"/>
+        <c:crossAx val="4644969"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2723,11 +2747,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52091142"/>
-        <c:axId val="42690782"/>
+        <c:axId val="71657506"/>
+        <c:axId val="24797220"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52091142"/>
+        <c:axId val="71657506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2758,7 +2782,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42690782"/>
+        <c:crossAx val="24797220"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2766,7 +2790,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42690782"/>
+        <c:axId val="24797220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2797,7 +2821,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52091142"/>
+        <c:crossAx val="71657506"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2988,11 +3012,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="37218380"/>
-        <c:axId val="63489669"/>
+        <c:axId val="84131102"/>
+        <c:axId val="57461450"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37218380"/>
+        <c:axId val="84131102"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3023,7 +3047,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63489669"/>
+        <c:crossAx val="57461450"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3031,7 +3055,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63489669"/>
+        <c:axId val="57461450"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3071,7 +3095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37218380"/>
+        <c:crossAx val="84131102"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3323,11 +3347,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="17437926"/>
-        <c:axId val="61543854"/>
+        <c:axId val="78426142"/>
+        <c:axId val="93029554"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="17437926"/>
+        <c:axId val="78426142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3358,7 +3382,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61543854"/>
+        <c:crossAx val="93029554"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3366,7 +3390,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="61543854"/>
+        <c:axId val="93029554"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3397,7 +3421,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17437926"/>
+        <c:crossAx val="78426142"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3649,11 +3673,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="59890267"/>
-        <c:axId val="66000661"/>
+        <c:axId val="46415980"/>
+        <c:axId val="59975435"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="59890267"/>
+        <c:axId val="46415980"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3684,7 +3708,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66000661"/>
+        <c:crossAx val="59975435"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3692,7 +3716,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="66000661"/>
+        <c:axId val="59975435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3723,7 +3747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59890267"/>
+        <c:crossAx val="46415980"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3762,9 +3786,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>224280</xdr:colOff>
+      <xdr:colOff>221760</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>104400</xdr:rowOff>
+      <xdr:rowOff>101880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3773,7 +3797,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="2114640"/>
-        <a:ext cx="9636120" cy="2333160"/>
+        <a:ext cx="9633600" cy="2330640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3792,9 +3816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>234360</xdr:colOff>
+      <xdr:colOff>231840</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3803,7 +3827,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="11458440"/>
-        <a:ext cx="4635000" cy="2333160"/>
+        <a:ext cx="4632480" cy="2330640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3822,9 +3846,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>234720</xdr:colOff>
+      <xdr:colOff>232200</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3833,7 +3857,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4694040" y="11458440"/>
-        <a:ext cx="4635000" cy="2333160"/>
+        <a:ext cx="4632480" cy="2330640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3852,9 +3876,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>234360</xdr:colOff>
+      <xdr:colOff>231840</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3863,7 +3887,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="18773640"/>
-        <a:ext cx="4635000" cy="1611360"/>
+        <a:ext cx="4632480" cy="1608840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3882,9 +3906,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>234720</xdr:colOff>
+      <xdr:colOff>232200</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3893,7 +3917,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4694040" y="18773640"/>
-        <a:ext cx="4635000" cy="1611360"/>
+        <a:ext cx="4632480" cy="1608840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4602,7 +4626,9 @@
       <c r="Y5" s="26" t="n">
         <v>44861</v>
       </c>
-      <c r="Z5" s="26"/>
+      <c r="Z5" s="26" t="n">
+        <v>15618</v>
+      </c>
       <c r="AA5" s="26"/>
       <c r="AB5" s="26"/>
       <c r="AC5" s="26"/>
@@ -4682,7 +4708,9 @@
       <c r="Y6" s="26" t="n">
         <v>545000</v>
       </c>
-      <c r="Z6" s="26"/>
+      <c r="Z6" s="26" t="n">
+        <v>191437</v>
+      </c>
       <c r="AA6" s="26"/>
       <c r="AB6" s="26"/>
       <c r="AC6" s="26"/>
@@ -4762,7 +4790,9 @@
       <c r="Y7" s="26" t="n">
         <v>3658</v>
       </c>
-      <c r="Z7" s="26"/>
+      <c r="Z7" s="26" t="n">
+        <v>1392</v>
+      </c>
       <c r="AA7" s="26"/>
       <c r="AB7" s="26"/>
       <c r="AC7" s="26"/>
@@ -4842,7 +4872,9 @@
       <c r="Y8" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="Z8" s="26"/>
+      <c r="Z8" s="26" t="n">
+        <v>62</v>
+      </c>
       <c r="AA8" s="26"/>
       <c r="AB8" s="26"/>
       <c r="AC8" s="26"/>
@@ -4946,7 +4978,7 @@
       </c>
       <c r="Z9" s="27" t="n">
         <f aca="false">IFERROR(Z8/Z7,0)</f>
-        <v>0</v>
+        <v>0.0445402298850575</v>
       </c>
       <c r="AA9" s="27" t="n">
         <f aca="false">IFERROR(AA8/AA7,0)</f>
@@ -5075,7 +5107,7 @@
       </c>
       <c r="Z10" s="28" t="n">
         <f aca="false">IFERROR(Z5/Z8,0)</f>
-        <v>0</v>
+        <v>251.903225806452</v>
       </c>
       <c r="AA10" s="28" t="n">
         <f aca="false">IFERROR(AA5/AA8,0)</f>
@@ -5163,7 +5195,9 @@
       <c r="Y12" s="26" t="n">
         <v>9860</v>
       </c>
-      <c r="Z12" s="26"/>
+      <c r="Z12" s="26" t="n">
+        <v>6079</v>
+      </c>
       <c r="AA12" s="26"/>
       <c r="AB12" s="26"/>
       <c r="AC12" s="26"/>
@@ -5223,7 +5257,9 @@
       <c r="Y13" s="26" t="n">
         <v>18000</v>
       </c>
-      <c r="Z13" s="26"/>
+      <c r="Z13" s="26" t="n">
+        <v>10756</v>
+      </c>
       <c r="AA13" s="26"/>
       <c r="AB13" s="26"/>
       <c r="AC13" s="26"/>
@@ -5283,7 +5319,9 @@
       <c r="Y14" s="26" t="n">
         <v>910</v>
       </c>
-      <c r="Z14" s="26"/>
+      <c r="Z14" s="26" t="n">
+        <v>522</v>
+      </c>
       <c r="AA14" s="26"/>
       <c r="AB14" s="26"/>
       <c r="AC14" s="26"/>
@@ -5343,7 +5381,9 @@
       <c r="Y15" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="Z15" s="26"/>
+      <c r="Z15" s="26" t="n">
+        <v>58</v>
+      </c>
       <c r="AA15" s="26"/>
       <c r="AB15" s="26"/>
       <c r="AC15" s="26"/>
@@ -5447,7 +5487,7 @@
       </c>
       <c r="Z16" s="27" t="n">
         <f aca="false">IFERROR(Z15/Z14,0)</f>
-        <v>0</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="AA16" s="27" t="n">
         <f aca="false">IFERROR(AA15/AA14,0)</f>
@@ -5576,7 +5616,7 @@
       </c>
       <c r="Z17" s="28" t="n">
         <f aca="false">IFERROR(Z12/Z15,0)</f>
-        <v>0</v>
+        <v>104.810344827586</v>
       </c>
       <c r="AA17" s="28" t="n">
         <f aca="false">IFERROR(AA12/AA15,0)</f>
@@ -6534,7 +6574,9 @@
       <c r="Y33" s="26" t="n">
         <v>1322</v>
       </c>
-      <c r="Z33" s="26"/>
+      <c r="Z33" s="26" t="n">
+        <v>2037</v>
+      </c>
       <c r="AA33" s="26"/>
       <c r="AB33" s="26"/>
       <c r="AC33" s="26"/>
@@ -6610,7 +6652,9 @@
       <c r="Y34" s="26" t="n">
         <v>8311</v>
       </c>
-      <c r="Z34" s="26"/>
+      <c r="Z34" s="26" t="n">
+        <v>9641</v>
+      </c>
       <c r="AA34" s="26"/>
       <c r="AB34" s="26"/>
       <c r="AC34" s="26"/>
@@ -6690,7 +6734,9 @@
       <c r="Y35" s="26" t="n">
         <v>3761</v>
       </c>
-      <c r="Z35" s="26"/>
+      <c r="Z35" s="26" t="n">
+        <v>4746</v>
+      </c>
       <c r="AA35" s="26"/>
       <c r="AB35" s="26"/>
       <c r="AC35" s="26"/>
@@ -6770,7 +6816,9 @@
       <c r="Y36" s="26" t="n">
         <v>446</v>
       </c>
-      <c r="Z36" s="26"/>
+      <c r="Z36" s="26" t="n">
+        <v>733</v>
+      </c>
       <c r="AA36" s="26"/>
       <c r="AB36" s="26"/>
       <c r="AC36" s="26"/>
@@ -6874,7 +6922,7 @@
       </c>
       <c r="Z37" s="27" t="n">
         <f aca="false">IFERROR(Z36/Z35,0)</f>
-        <v>0</v>
+        <v>0.154445849136115</v>
       </c>
       <c r="AA37" s="27" t="n">
         <f aca="false">IFERROR(AA36/AA35,0)</f>
@@ -7003,7 +7051,7 @@
       </c>
       <c r="Z38" s="28" t="n">
         <f aca="false">IFERROR(Z33/Z36,0)</f>
-        <v>0</v>
+        <v>2.77899045020464</v>
       </c>
       <c r="AA38" s="28" t="n">
         <f aca="false">IFERROR(AA33/AA36,0)</f>
@@ -7543,7 +7591,9 @@
       <c r="Y48" s="26" t="n">
         <v>98500</v>
       </c>
-      <c r="Z48" s="26"/>
+      <c r="Z48" s="26" t="n">
+        <v>167000</v>
+      </c>
       <c r="AA48" s="26"/>
       <c r="AB48" s="26"/>
       <c r="AC48" s="26"/>
@@ -7647,7 +7697,9 @@
       <c r="Y50" s="26" t="n">
         <v>2225</v>
       </c>
-      <c r="Z50" s="26"/>
+      <c r="Z50" s="26" t="n">
+        <v>4278</v>
+      </c>
       <c r="AA50" s="26"/>
       <c r="AB50" s="26"/>
       <c r="AC50" s="26"/>
@@ -7709,7 +7761,9 @@
       <c r="Y51" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="Z51" s="26"/>
+      <c r="Z51" s="26" t="n">
+        <v>334</v>
+      </c>
       <c r="AA51" s="26"/>
       <c r="AB51" s="26"/>
       <c r="AC51" s="26"/>
@@ -7813,7 +7867,7 @@
       </c>
       <c r="Z52" s="27" t="n">
         <f aca="false">IFERROR(Z51/Z50,0)</f>
-        <v>0</v>
+        <v>0.0780738662926601</v>
       </c>
       <c r="AA52" s="27" t="n">
         <f aca="false">IFERROR(AA51/AA50,0)</f>
@@ -7942,7 +7996,7 @@
       </c>
       <c r="Z53" s="28" t="n">
         <f aca="false">IFERROR(Z48/Z51,0)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA53" s="28" t="n">
         <f aca="false">IFERROR(AA48/AA51,0)</f>
@@ -9765,7 +9819,9 @@
       <c r="Y86" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="26"/>
+      <c r="Z86" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="AA86" s="26"/>
       <c r="AB86" s="26"/>
       <c r="AC86" s="26"/>
@@ -9805,7 +9861,9 @@
       <c r="Y87" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="26"/>
+      <c r="Z87" s="26" t="n">
+        <v>389000</v>
+      </c>
       <c r="AA87" s="26"/>
       <c r="AB87" s="26"/>
       <c r="AC87" s="26"/>
@@ -9871,7 +9929,9 @@
       <c r="Y88" s="26" t="n">
         <v>4800</v>
       </c>
-      <c r="Z88" s="26"/>
+      <c r="Z88" s="26" t="n">
+        <v>3640</v>
+      </c>
       <c r="AA88" s="26"/>
       <c r="AB88" s="26"/>
       <c r="AC88" s="26"/>
@@ -9921,7 +9981,9 @@
       <c r="Y89" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="26"/>
+      <c r="Z89" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="AA89" s="26"/>
       <c r="AB89" s="26"/>
       <c r="AC89" s="26"/>
@@ -11463,7 +11525,7 @@
       </c>
       <c r="Z110" s="33" t="n">
         <f aca="false">Z5+Z12+Z19+Z26+Z33+Z41+Z48+Z56+Z63+Z71+Z78+Z86</f>
-        <v>0</v>
+        <v>190734</v>
       </c>
       <c r="AA110" s="33" t="n">
         <f aca="false">AA5+AA12+AA19+AA26+AA33+AA41+AA48+AA56+AA63+AA71+AA78+AA86</f>
@@ -11592,7 +11654,7 @@
       </c>
       <c r="Z111" s="33" t="n">
         <f aca="false">Z8+Z15+Z22+Z29+Z36+Z44+Z51+Z59+Z66+Z74+Z81+Z89</f>
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="AA111" s="33" t="n">
         <f aca="false">AA8+AA15+AA22+AA29+AA36+AA44+AA51+AA59+AA66+AA74+AA81+AA89</f>
@@ -11721,7 +11783,7 @@
       </c>
       <c r="Z112" s="33" t="n">
         <f aca="false">IFERROR(Z110/Z111,0)</f>
-        <v>0</v>
+        <v>160.685762426285</v>
       </c>
       <c r="AA112" s="33" t="n">
         <f aca="false">IFERROR(AA110/AA111,0)</f>
@@ -11850,7 +11912,7 @@
       </c>
       <c r="Z113" s="33" t="n">
         <f aca="false">Z7+Z14+Z21+Z28+Z35+Z43+Z50+Z58+Z65+Z73+Z80+Z88</f>
-        <v>0</v>
+        <v>14578</v>
       </c>
       <c r="AA113" s="33" t="n">
         <f aca="false">AA7+AA14+AA21+AA28+AA35+AA43+AA50+AA58+AA65+AA73+AA80+AA88</f>
@@ -11979,7 +12041,7 @@
       </c>
       <c r="Z114" s="33" t="n">
         <f aca="false">Z7+Z14+Z21+Z28+Z35+Z43+Z50+Z58+Z65+Z73+Z80</f>
-        <v>0</v>
+        <v>10938</v>
       </c>
       <c r="AA114" s="33" t="n">
         <f aca="false">AA7+AA14+AA21+AA28+AA35+AA43+AA50+AA58+AA65+AA73+AA80</f>
@@ -12108,7 +12170,7 @@
       </c>
       <c r="Z115" s="33" t="n">
         <f aca="false">Z88</f>
-        <v>0</v>
+        <v>3640</v>
       </c>
       <c r="AA115" s="33" t="n">
         <f aca="false">AA88</f>
@@ -12237,7 +12299,7 @@
       </c>
       <c r="Z116" s="34" t="n">
         <f aca="false">IFERROR(Z111/Z113,0)</f>
-        <v>0</v>
+        <v>0.0814240636575662</v>
       </c>
       <c r="AA116" s="34" t="n">
         <f aca="false">IFERROR(AA111/AA113,0)</f>
@@ -12366,7 +12428,7 @@
       </c>
       <c r="Z117" s="33" t="n">
         <f aca="false">Z5+Z12+Z19+Z26+Z33</f>
-        <v>0</v>
+        <v>23734</v>
       </c>
       <c r="AA117" s="33" t="n">
         <f aca="false">AA5+AA12+AA19+AA26+AA33</f>
@@ -12495,7 +12557,7 @@
       </c>
       <c r="Z118" s="33" t="n">
         <f aca="false">Z8+Z15+Z22+Z29+Z36</f>
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="AA118" s="33" t="n">
         <f aca="false">AA8+AA15+AA22+AA29+AA36</f>
@@ -12624,7 +12686,7 @@
       </c>
       <c r="Z119" s="33" t="n">
         <f aca="false">IFERROR(Z117/Z118,0)</f>
-        <v>0</v>
+        <v>27.8241500586167</v>
       </c>
       <c r="AA119" s="33" t="n">
         <f aca="false">IFERROR(AA117/AA118,0)</f>
@@ -12753,7 +12815,7 @@
       </c>
       <c r="Z120" s="33" t="n">
         <f aca="false">Z41+Z48</f>
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="AA120" s="33" t="n">
         <f aca="false">AA41+AA48</f>
@@ -12882,7 +12944,7 @@
       </c>
       <c r="Z121" s="33" t="n">
         <f aca="false">Z44+Z51</f>
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="AA121" s="33" t="n">
         <f aca="false">AA44+AA51</f>
@@ -13011,7 +13073,7 @@
       </c>
       <c r="Z122" s="33" t="n">
         <f aca="false">IFERROR(Z120/Z121,0)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA122" s="33" t="n">
         <f aca="false">IFERROR(AA120/AA121,0)</f>
@@ -13516,7 +13578,9 @@
       <c r="Y129" s="26" t="n">
         <v>984</v>
       </c>
-      <c r="Z129" s="26"/>
+      <c r="Z129" s="26" t="n">
+        <v>1461</v>
+      </c>
       <c r="AA129" s="26"/>
       <c r="AB129" s="26"/>
       <c r="AC129" s="26"/>
@@ -13558,7 +13622,9 @@
       <c r="Y130" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Z130" s="26"/>
+      <c r="Z130" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="AA130" s="26"/>
       <c r="AB130" s="26"/>
       <c r="AC130" s="26"/>
@@ -13584,7 +13650,9 @@
       <c r="Y131" s="26" t="n">
         <v>607.33</v>
       </c>
-      <c r="Z131" s="26"/>
+      <c r="Z131" s="26" t="n">
+        <v>610.33</v>
+      </c>
       <c r="AA131" s="26"/>
       <c r="AB131" s="26"/>
       <c r="AC131" s="26"/>
@@ -13656,7 +13724,9 @@
       <c r="Y132" s="26" t="n">
         <v>13318</v>
       </c>
-      <c r="Z132" s="26"/>
+      <c r="Z132" s="26" t="n">
+        <v>13970</v>
+      </c>
       <c r="AA132" s="26"/>
       <c r="AB132" s="26"/>
       <c r="AC132" s="26"/>
@@ -13728,7 +13798,9 @@
       <c r="Y133" s="37" t="n">
         <v>0.022</v>
       </c>
-      <c r="Z133" s="37"/>
+      <c r="Z133" s="37" t="n">
+        <v>0.022</v>
+      </c>
       <c r="AA133" s="37"/>
       <c r="AB133" s="37"/>
       <c r="AC133" s="37"/>
@@ -14022,7 +14094,9 @@
       <c r="X5" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="42"/>
+      <c r="Y5" s="42" t="s">
+        <v>118</v>
+      </c>
       <c r="Z5" s="42"/>
       <c r="AA5" s="42"/>
       <c r="AB5" s="42"/>
@@ -14034,7 +14108,7 @@
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
@@ -14055,14 +14129,16 @@
       <c r="S6" s="42"/>
       <c r="T6" s="42"/>
       <c r="U6" s="42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="V6" s="42"/>
       <c r="W6" s="42"/>
       <c r="X6" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y6" s="42"/>
+        <v>121</v>
+      </c>
+      <c r="Y6" s="42" t="s">
+        <v>122</v>
+      </c>
       <c r="Z6" s="42"/>
       <c r="AA6" s="42"/>
       <c r="AB6" s="42"/>
@@ -14074,7 +14150,7 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="43"/>
@@ -14098,7 +14174,7 @@
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="44"/>
@@ -14119,14 +14195,16 @@
       <c r="S8" s="44"/>
       <c r="T8" s="44"/>
       <c r="U8" s="44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="V8" s="44"/>
       <c r="W8" s="44"/>
       <c r="X8" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y8" s="44"/>
+        <v>126</v>
+      </c>
+      <c r="Y8" s="44" t="s">
+        <v>127</v>
+      </c>
       <c r="Z8" s="44"/>
       <c r="AA8" s="44"/>
       <c r="AB8" s="44"/>
@@ -14138,7 +14216,7 @@
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
@@ -14159,14 +14237,16 @@
       <c r="S9" s="44"/>
       <c r="T9" s="44"/>
       <c r="U9" s="44" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="V9" s="44"/>
       <c r="W9" s="44"/>
       <c r="X9" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y9" s="44"/>
+        <v>130</v>
+      </c>
+      <c r="Y9" s="44" t="s">
+        <v>131</v>
+      </c>
       <c r="Z9" s="44"/>
       <c r="AA9" s="44"/>
       <c r="AB9" s="44"/>
@@ -14178,7 +14258,7 @@
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="41" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
@@ -14199,14 +14279,16 @@
       <c r="S10" s="44"/>
       <c r="T10" s="44"/>
       <c r="U10" s="44" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="V10" s="44"/>
       <c r="W10" s="44"/>
       <c r="X10" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y10" s="44"/>
+        <v>134</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>135</v>
+      </c>
       <c r="Z10" s="44"/>
       <c r="AA10" s="44"/>
       <c r="AB10" s="44"/>
@@ -14218,7 +14300,7 @@
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="45" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -14242,7 +14324,7 @@
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="41" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46"/>
@@ -14263,14 +14345,16 @@
       <c r="S12" s="46"/>
       <c r="T12" s="46"/>
       <c r="U12" s="46" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="V12" s="46"/>
       <c r="W12" s="46"/>
       <c r="X12" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y12" s="46"/>
+        <v>139</v>
+      </c>
+      <c r="Y12" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="Z12" s="46"/>
       <c r="AA12" s="46"/>
       <c r="AB12" s="46"/>
@@ -14282,7 +14366,7 @@
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="41" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="46"/>
@@ -14303,12 +14387,12 @@
       <c r="S13" s="46"/>
       <c r="T13" s="46"/>
       <c r="U13" s="46" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V13" s="46"/>
       <c r="W13" s="46"/>
       <c r="X13" s="46" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Y13" s="46"/>
       <c r="Z13" s="46"/>
@@ -14322,7 +14406,7 @@
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="46"/>
@@ -14343,7 +14427,7 @@
       <c r="S14" s="46"/>
       <c r="T14" s="46"/>
       <c r="U14" s="46" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="V14" s="46"/>
       <c r="W14" s="46"/>
@@ -14360,7 +14444,7 @@
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="47" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="47"/>
@@ -14384,7 +14468,7 @@
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="41" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C16" s="48"/>
       <c r="D16" s="48"/>
@@ -14405,14 +14489,16 @@
       <c r="S16" s="48"/>
       <c r="T16" s="48"/>
       <c r="U16" s="48" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="V16" s="48"/>
       <c r="W16" s="48"/>
       <c r="X16" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y16" s="48"/>
+        <v>149</v>
+      </c>
+      <c r="Y16" s="48" t="s">
+        <v>150</v>
+      </c>
       <c r="Z16" s="48"/>
       <c r="AA16" s="48"/>
       <c r="AB16" s="48"/>
@@ -14424,7 +14510,7 @@
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="41" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
@@ -14445,14 +14531,16 @@
       <c r="S17" s="48"/>
       <c r="T17" s="48"/>
       <c r="U17" s="48" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="V17" s="48"/>
       <c r="W17" s="48"/>
       <c r="X17" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y17" s="48"/>
+        <v>153</v>
+      </c>
+      <c r="Y17" s="48" t="s">
+        <v>154</v>
+      </c>
       <c r="Z17" s="48"/>
       <c r="AA17" s="48"/>
       <c r="AB17" s="48"/>
@@ -14464,7 +14552,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="49" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="49"/>
@@ -14488,7 +14576,7 @@
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="41" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -14509,12 +14597,12 @@
       <c r="S19" s="50"/>
       <c r="T19" s="50"/>
       <c r="U19" s="50" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="V19" s="50"/>
       <c r="W19" s="50"/>
       <c r="X19" s="50" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Y19" s="50"/>
       <c r="Z19" s="50"/>
@@ -14528,7 +14616,7 @@
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="41" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="50"/>
@@ -14549,12 +14637,12 @@
       <c r="S20" s="50"/>
       <c r="T20" s="50"/>
       <c r="U20" s="50" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="V20" s="50"/>
       <c r="W20" s="50"/>
       <c r="X20" s="50" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="Y20" s="50"/>
       <c r="Z20" s="50"/>
@@ -14568,7 +14656,7 @@
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="41" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -14589,12 +14677,12 @@
       <c r="S21" s="50"/>
       <c r="T21" s="50"/>
       <c r="U21" s="50" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="V21" s="50"/>
       <c r="W21" s="50"/>
       <c r="X21" s="50" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="Y21" s="50"/>
       <c r="Z21" s="50"/>
@@ -14639,7 +14727,7 @@
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="51" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
@@ -14672,7 +14760,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C3" s="52"/>
       <c r="D3" s="52"/>
@@ -14693,7 +14781,7 @@
       <c r="S3" s="52"/>
       <c r="V3" s="53" t="str">
         <f aca="true">TEXT(Input!V$3,"mmmm yyyy")&amp;" · Prepared "&amp;TEXT(TODAY(),"mmm d, yyyy")</f>
-        <v>March 2026 · Prepared Aug 2, 2026</v>
+        <v>March 2026 · Prepared Aug 5, 2026</v>
       </c>
       <c r="W3" s="53"/>
       <c r="X3" s="53"/>
@@ -14738,42 +14826,42 @@
     <row r="5" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="55" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C6" s="55"/>
       <c r="D6" s="55"/>
       <c r="E6" s="55"/>
       <c r="F6" s="55"/>
       <c r="G6" s="55" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H6" s="55"/>
       <c r="I6" s="55"/>
       <c r="J6" s="55"/>
       <c r="K6" s="55"/>
       <c r="L6" s="55" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="M6" s="55"/>
       <c r="N6" s="55"/>
       <c r="O6" s="55"/>
       <c r="P6" s="55"/>
       <c r="Q6" s="55" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="R6" s="55"/>
       <c r="S6" s="55"/>
       <c r="T6" s="55"/>
       <c r="U6" s="55"/>
       <c r="V6" s="55" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="W6" s="55"/>
       <c r="X6" s="55"/>
       <c r="Y6" s="55"/>
       <c r="Z6" s="55"/>
       <c r="AA6" s="55" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="AB6" s="55"/>
       <c r="AC6" s="55"/>
@@ -14930,42 +15018,42 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="66" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C10" s="66"/>
       <c r="D10" s="66"/>
       <c r="E10" s="66"/>
       <c r="F10" s="66"/>
       <c r="G10" s="66" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
       <c r="J10" s="66"/>
       <c r="K10" s="66"/>
       <c r="L10" s="66" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="M10" s="66"/>
       <c r="N10" s="66"/>
       <c r="O10" s="66"/>
       <c r="P10" s="66"/>
       <c r="Q10" s="66" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="R10" s="66"/>
       <c r="S10" s="66"/>
       <c r="T10" s="66"/>
       <c r="U10" s="66"/>
       <c r="V10" s="66" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="W10" s="66"/>
       <c r="X10" s="66"/>
       <c r="Y10" s="66"/>
       <c r="Z10" s="66"/>
       <c r="AA10" s="66" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="AB10" s="66"/>
       <c r="AC10" s="66"/>
@@ -14976,7 +15064,7 @@
     <row r="12" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="67" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="67"/>
@@ -15029,7 +15117,7 @@
     <row r="33" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="67" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C34" s="67"/>
       <c r="D34" s="67"/>
@@ -15062,7 +15150,7 @@
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="68" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C35" s="68"/>
       <c r="D35" s="68"/>
@@ -15074,7 +15162,7 @@
       <c r="J35" s="68"/>
       <c r="K35" s="68"/>
       <c r="L35" s="69" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M35" s="69"/>
       <c r="N35" s="69"/>
@@ -15086,7 +15174,7 @@
       <c r="T35" s="69"/>
       <c r="U35" s="69"/>
       <c r="V35" s="70" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="W35" s="70"/>
       <c r="X35" s="70"/>
@@ -15515,7 +15603,7 @@
     <row r="51" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="38" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C52" s="38"/>
       <c r="D52" s="38"/>
@@ -15549,7 +15637,7 @@
     <row r="53" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="74" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C54" s="74"/>
       <c r="D54" s="74"/>
@@ -15557,37 +15645,37 @@
       <c r="F54" s="74"/>
       <c r="G54" s="74"/>
       <c r="H54" s="75" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I54" s="75"/>
       <c r="J54" s="75"/>
       <c r="K54" s="75"/>
       <c r="L54" s="75" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M54" s="75"/>
       <c r="N54" s="75" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="O54" s="75"/>
       <c r="P54" s="75"/>
       <c r="Q54" s="75" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="R54" s="75"/>
       <c r="S54" s="75"/>
       <c r="T54" s="75" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="U54" s="75"/>
       <c r="V54" s="75"/>
       <c r="W54" s="75" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="X54" s="75"/>
       <c r="Y54" s="75"/>
       <c r="Z54" s="75" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="AA54" s="75"/>
       <c r="AB54" s="75"/>
@@ -16147,7 +16235,7 @@
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="89" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C65" s="89"/>
       <c r="D65" s="89"/>
@@ -16190,7 +16278,7 @@
       <c r="X65" s="95"/>
       <c r="Y65" s="95"/>
       <c r="Z65" s="96" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AA65" s="96"/>
       <c r="AB65" s="96"/>
@@ -16201,7 +16289,7 @@
     <row r="66" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="97" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C67" s="97"/>
       <c r="D67" s="97"/>
@@ -16218,7 +16306,7 @@
       <c r="O67" s="97"/>
       <c r="P67" s="97"/>
       <c r="Q67" s="97" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="R67" s="97"/>
       <c r="S67" s="97"/>
@@ -16400,7 +16488,7 @@
     <row r="87" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="8" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -16433,7 +16521,7 @@
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="55" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C89" s="55"/>
       <c r="D89" s="55"/>
@@ -16442,7 +16530,7 @@
       <c r="G89" s="55"/>
       <c r="H89" s="55"/>
       <c r="I89" s="55" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="J89" s="55"/>
       <c r="K89" s="55"/>
@@ -16451,7 +16539,7 @@
       <c r="N89" s="55"/>
       <c r="O89" s="55"/>
       <c r="P89" s="55" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="Q89" s="55"/>
       <c r="R89" s="55"/>
@@ -16461,7 +16549,7 @@
       <c r="V89" s="55"/>
       <c r="W89" s="55"/>
       <c r="X89" s="55" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="Y89" s="55"/>
       <c r="Z89" s="55"/>
@@ -16544,7 +16632,7 @@
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="101" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C92" s="101"/>
       <c r="D92" s="101"/>
@@ -16553,7 +16641,7 @@
       <c r="G92" s="101"/>
       <c r="H92" s="101"/>
       <c r="I92" s="101" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J92" s="101"/>
       <c r="K92" s="101"/>
@@ -16562,7 +16650,7 @@
       <c r="N92" s="101"/>
       <c r="O92" s="101"/>
       <c r="P92" s="101" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="Q92" s="101"/>
       <c r="R92" s="101"/>
@@ -16572,7 +16660,7 @@
       <c r="V92" s="101"/>
       <c r="W92" s="101"/>
       <c r="X92" s="101" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="Y92" s="101"/>
       <c r="Z92" s="101"/>
@@ -16583,7 +16671,7 @@
     </row>
     <row r="94" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="102" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C94" s="102"/>
       <c r="D94" s="102"/>
@@ -16655,7 +16743,7 @@
     <row r="101" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="102" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="38" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
@@ -16688,7 +16776,7 @@
     </row>
     <row r="104" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="67" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C104" s="67"/>
       <c r="D104" s="67"/>
@@ -16705,7 +16793,7 @@
       <c r="O104" s="67"/>
       <c r="P104" s="67"/>
       <c r="Q104" s="67" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="R104" s="67"/>
       <c r="S104" s="67"/>
@@ -16723,42 +16811,42 @@
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="104" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C106" s="104"/>
       <c r="D106" s="104"/>
       <c r="E106" s="104"/>
       <c r="F106" s="104" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G106" s="104"/>
       <c r="H106" s="104"/>
       <c r="I106" s="104"/>
       <c r="J106" s="104" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="K106" s="104"/>
       <c r="L106" s="104"/>
       <c r="M106" s="104"/>
       <c r="N106" s="104" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="O106" s="104"/>
       <c r="P106" s="104"/>
       <c r="Q106" s="104" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="R106" s="104"/>
       <c r="S106" s="104"/>
       <c r="T106" s="104"/>
       <c r="U106" s="104" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="V106" s="104"/>
       <c r="W106" s="104"/>
       <c r="X106" s="104"/>
       <c r="Y106" s="104" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z106" s="104"/>
       <c r="AA106" s="104"/>
@@ -16851,7 +16939,7 @@
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="109" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C110" s="109"/>
       <c r="D110" s="109"/>
@@ -16868,7 +16956,7 @@
       <c r="O110" s="109"/>
       <c r="P110" s="109"/>
       <c r="Q110" s="109" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="R110" s="109"/>
       <c r="S110" s="109"/>
@@ -17163,7 +17251,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="113" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C137" s="113"/>
       <c r="D137" s="113"/>
@@ -17180,7 +17268,7 @@
       <c r="O137" s="113"/>
       <c r="P137" s="113"/>
       <c r="Q137" s="113" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="R137" s="113"/>
       <c r="S137" s="113"/>
@@ -17330,7 +17418,7 @@
     <row r="143" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="144" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="89" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C144" s="89"/>
       <c r="D144" s="89"/>
@@ -17363,13 +17451,13 @@
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="114" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C145" s="114"/>
       <c r="D145" s="114"/>
       <c r="E145" s="114"/>
       <c r="F145" s="115" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G145" s="115"/>
       <c r="H145" s="115"/>
@@ -17382,13 +17470,13 @@
       <c r="O145" s="115"/>
       <c r="P145" s="115"/>
       <c r="Q145" s="114" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="R145" s="114"/>
       <c r="S145" s="114"/>
       <c r="T145" s="114"/>
       <c r="U145" s="115" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="V145" s="115"/>
       <c r="W145" s="115"/>
@@ -17402,13 +17490,13 @@
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="114" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C146" s="114"/>
       <c r="D146" s="114"/>
       <c r="E146" s="114"/>
       <c r="F146" s="115" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G146" s="115"/>
       <c r="H146" s="115"/>
@@ -17421,13 +17509,13 @@
       <c r="O146" s="115"/>
       <c r="P146" s="115"/>
       <c r="Q146" s="114" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="R146" s="114"/>
       <c r="S146" s="114"/>
       <c r="T146" s="114"/>
       <c r="U146" s="115" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="V146" s="115"/>
       <c r="W146" s="115"/>
@@ -17441,13 +17529,13 @@
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B147" s="114" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C147" s="114"/>
       <c r="D147" s="114"/>
       <c r="E147" s="114"/>
       <c r="F147" s="115" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G147" s="115"/>
       <c r="H147" s="115"/>
@@ -17460,13 +17548,13 @@
       <c r="O147" s="115"/>
       <c r="P147" s="115"/>
       <c r="Q147" s="114" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="R147" s="114"/>
       <c r="S147" s="114"/>
       <c r="T147" s="114"/>
       <c r="U147" s="115" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="V147" s="115"/>
       <c r="W147" s="115"/>
@@ -17480,13 +17568,13 @@
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="114" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C148" s="114"/>
       <c r="D148" s="114"/>
       <c r="E148" s="114"/>
       <c r="F148" s="115" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G148" s="115"/>
       <c r="H148" s="115"/>
@@ -17499,13 +17587,13 @@
       <c r="O148" s="115"/>
       <c r="P148" s="115"/>
       <c r="Q148" s="114" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="R148" s="114"/>
       <c r="S148" s="114"/>
       <c r="T148" s="114"/>
       <c r="U148" s="115" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="V148" s="115"/>
       <c r="W148" s="115"/>
@@ -17519,7 +17607,7 @@
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="116" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C151" s="116"/>
       <c r="D151" s="116"/>

--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -400,7 +400,7 @@
     <t xml:space="preserve">Sign-ups landede på 984, et forventet sæsonfald fra maj (1.035), men konverteringen steg igen — blended CVR ramte 6,4% mod 5,8% i maj. Google leverede 74 kunder til en CAC på 133 kr. (kanalens næstbedste måned), og Brand search fastholdt det høje niveau med 446 kunder. Churn faldt tilbage fra 2,6% til 2,2%, og vi rundede 13.318 aktive kunder (+582).</t>
   </si>
   <si>
-    <t xml:space="preserve">Juli blev den største måned i Altid Energis historie med 1.461 signups, klart over den tidligere rekord på 1.300 fra februar. Blended konvertering ramte 10,0 pct. (ny rekord), og blended CAC faldt til 131 kr. fra 157 kr. Brand search leverede 733 kunder (rekord), Google sin bedste konverteringsmåned (CVR 11,1 pct., CAC 105 kr.), og affiliates voksede til 334 kunder. Aktive kunder rundede 13.970 (+652), og churn holdt sig stabil på 2,2 pct.</t>
+    <t xml:space="preserve">Juli blev den største måned i Altid Energis historie med 1.461 signups, klart over den tidligere rekord på 1.300 fra februar. Blended konvertering ramte 10,0 pct. (ny rekord), og blended CAC faldt til 131 kr. fra 157 kr. Brand search leverede 733 kunder (rekord), Google sin bedste konverteringsmåned (CVR 11,1 pct., CAC 105 kr.), og affiliates voksede til 334 kunder. Aktive kunder rundede 13.970 (15.267 målepunkter) med en nettotilvækst på 652, og churn holdt sig stabil på 2,2 pct.</t>
   </si>
   <si>
     <t xml:space="preserve">WINS — HVAD VIRKEDE</t>
@@ -2129,8 +2129,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="86917899"/>
-        <c:axId val="31025123"/>
+        <c:axId val="2157835"/>
+        <c:axId val="41765347"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2315,11 +2315,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="4644969"/>
-        <c:axId val="16117395"/>
+        <c:axId val="57907455"/>
+        <c:axId val="93378071"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="86917899"/>
+        <c:axId val="2157835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2350,7 +2350,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31025123"/>
+        <c:crossAx val="41765347"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2358,7 +2358,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="31025123"/>
+        <c:axId val="41765347"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2423,12 +2423,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86917899"/>
+        <c:crossAx val="2157835"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:dateAx>
-        <c:axId val="4644969"/>
+        <c:axId val="57907455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2459,7 +2459,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16117395"/>
+        <c:crossAx val="93378071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2467,7 +2467,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="16117395"/>
+        <c:axId val="93378071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2532,7 +2532,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4644969"/>
+        <c:crossAx val="57907455"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2747,11 +2747,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71657506"/>
-        <c:axId val="24797220"/>
+        <c:axId val="55411938"/>
+        <c:axId val="98172424"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71657506"/>
+        <c:axId val="55411938"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2782,7 +2782,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24797220"/>
+        <c:crossAx val="98172424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2790,7 +2790,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24797220"/>
+        <c:axId val="98172424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,7 +2821,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71657506"/>
+        <c:crossAx val="55411938"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3012,11 +3012,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84131102"/>
-        <c:axId val="57461450"/>
+        <c:axId val="78381551"/>
+        <c:axId val="33279198"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84131102"/>
+        <c:axId val="78381551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3047,7 +3047,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57461450"/>
+        <c:crossAx val="33279198"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3055,7 +3055,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57461450"/>
+        <c:axId val="33279198"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3095,7 +3095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84131102"/>
+        <c:crossAx val="78381551"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3347,11 +3347,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78426142"/>
-        <c:axId val="93029554"/>
+        <c:axId val="12541057"/>
+        <c:axId val="33098113"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78426142"/>
+        <c:axId val="12541057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3382,7 +3382,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93029554"/>
+        <c:crossAx val="33098113"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3390,7 +3390,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="93029554"/>
+        <c:axId val="33098113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3421,7 +3421,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78426142"/>
+        <c:crossAx val="12541057"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3673,11 +3673,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="46415980"/>
-        <c:axId val="59975435"/>
+        <c:axId val="82519521"/>
+        <c:axId val="60501339"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="46415980"/>
+        <c:axId val="82519521"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3708,7 +3708,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59975435"/>
+        <c:crossAx val="60501339"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3716,7 +3716,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="59975435"/>
+        <c:axId val="60501339"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3747,7 +3747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46415980"/>
+        <c:crossAx val="82519521"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3786,9 +3786,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>221760</xdr:colOff>
+      <xdr:colOff>221040</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>101880</xdr:rowOff>
+      <xdr:rowOff>101160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3797,7 +3797,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="2114640"/>
-        <a:ext cx="9633600" cy="2330640"/>
+        <a:ext cx="9632880" cy="2329920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3816,9 +3816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>231840</xdr:colOff>
+      <xdr:colOff>231120</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>63720</xdr:rowOff>
+      <xdr:rowOff>63000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3827,7 +3827,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="11458440"/>
-        <a:ext cx="4632480" cy="2330640"/>
+        <a:ext cx="4631760" cy="2329920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3846,9 +3846,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>232200</xdr:colOff>
+      <xdr:colOff>231480</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>63720</xdr:rowOff>
+      <xdr:rowOff>63000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3857,7 +3857,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4694040" y="11458440"/>
-        <a:ext cx="4632480" cy="2330640"/>
+        <a:ext cx="4631760" cy="2329920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3876,9 +3876,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>231840</xdr:colOff>
+      <xdr:colOff>231120</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3887,7 +3887,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="293400" y="18773640"/>
-        <a:ext cx="4632480" cy="1608840"/>
+        <a:ext cx="4631760" cy="1608120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3906,9 +3906,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>232200</xdr:colOff>
+      <xdr:colOff>231480</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3917,7 +3917,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4694040" y="18773640"/>
-        <a:ext cx="4632480" cy="1608840"/>
+        <a:ext cx="4631760" cy="1608120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">

--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -1609,7 +1609,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1790,7 +1790,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1960,7 +1960,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2036,7 +2036,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2076,7 +2076,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2152,7 +2152,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2184,7 +2184,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2253,7 +2253,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2399,7 +2399,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2442,7 +2442,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2515,7 +2515,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2661,7 +2661,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2714,7 +2714,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2831,7 +2831,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3001,7 +3001,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3042,7 +3042,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3159,7 +3159,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3329,7 +3329,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3370,7 +3370,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -4212,83 +4212,85 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D5" s="143" t="n">
+      <c r="D5" s="149" t="n">
         <v>7021</v>
       </c>
-      <c r="E5" s="143" t="n">
+      <c r="E5" s="149" t="n">
         <v>10594</v>
       </c>
-      <c r="F5" s="143" t="n">
+      <c r="F5" s="149" t="n">
         <v>18699</v>
       </c>
-      <c r="G5" s="143" t="n">
+      <c r="G5" s="149" t="n">
         <v>19671</v>
       </c>
-      <c r="H5" s="143" t="n">
+      <c r="H5" s="149" t="n">
         <v>159609</v>
       </c>
-      <c r="I5" s="143" t="n">
+      <c r="I5" s="149" t="n">
         <v>39824</v>
       </c>
-      <c r="J5" s="143" t="n">
+      <c r="J5" s="149" t="n">
         <v>47261</v>
       </c>
-      <c r="K5" s="143" t="n">
+      <c r="K5" s="149" t="n">
         <v>30571</v>
       </c>
-      <c r="L5" s="143" t="n">
+      <c r="L5" s="149" t="n">
         <v>42544</v>
       </c>
-      <c r="M5" s="143" t="n">
+      <c r="M5" s="149" t="n">
         <v>27176</v>
       </c>
-      <c r="N5" s="143" t="n">
+      <c r="N5" s="149" t="n">
         <v>25063</v>
       </c>
-      <c r="O5" s="143" t="n">
+      <c r="O5" s="149" t="n">
         <v>23282</v>
       </c>
-      <c r="P5" s="143" t="n">
+      <c r="P5" s="149" t="n">
         <v>17800</v>
       </c>
-      <c r="Q5" s="143" t="n">
+      <c r="Q5" s="149" t="n">
         <v>41600</v>
       </c>
-      <c r="R5" s="143" t="n">
+      <c r="R5" s="149" t="n">
         <v>128946</v>
       </c>
-      <c r="S5" s="143" t="n">
+      <c r="S5" s="149" t="n">
         <v>15444</v>
       </c>
-      <c r="T5" s="143" t="n">
+      <c r="T5" s="149" t="n">
         <v>40422</v>
       </c>
-      <c r="U5" s="143" t="n">
+      <c r="U5" s="149" t="n">
         <v>41894</v>
       </c>
-      <c r="V5" s="143" t="n">
+      <c r="V5" s="149" t="n">
         <v>46639</v>
       </c>
-      <c r="W5" s="143" t="n">
+      <c r="W5" s="149" t="n">
         <v>53431</v>
       </c>
-      <c r="X5" s="143" t="n">
+      <c r="X5" s="149" t="n">
         <v>43242</v>
       </c>
-      <c r="Y5" s="143" t="n">
+      <c r="Y5" s="149" t="n">
         <v>44861</v>
       </c>
-      <c r="Z5" s="143" t="n">
+      <c r="Z5" s="149" t="n">
         <v>15618</v>
       </c>
-      <c r="AA5" s="143" t="n"/>
-      <c r="AB5" s="143" t="n"/>
-      <c r="AC5" s="143" t="n"/>
-      <c r="AD5" s="143" t="n"/>
-      <c r="AE5" s="143" t="n"/>
-      <c r="AF5" s="143" t="n"/>
-      <c r="AG5" s="143" t="n"/>
-      <c r="AH5" s="143" t="n"/>
+      <c r="AA5" s="149" t="n">
+        <v>16284</v>
+      </c>
+      <c r="AB5" s="149" t="n"/>
+      <c r="AC5" s="149" t="n"/>
+      <c r="AD5" s="149" t="n"/>
+      <c r="AE5" s="149" t="n"/>
+      <c r="AF5" s="149" t="n"/>
+      <c r="AG5" s="149" t="n"/>
+      <c r="AH5" s="149" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="118">
       <c r="C6" s="142" t="inlineStr">
@@ -4296,83 +4298,85 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D6" s="143" t="n">
+      <c r="D6" s="149" t="n">
         <v>62418</v>
       </c>
-      <c r="E6" s="143" t="n">
+      <c r="E6" s="149" t="n">
         <v>76931</v>
       </c>
-      <c r="F6" s="143" t="n">
+      <c r="F6" s="149" t="n">
         <v>106459</v>
       </c>
-      <c r="G6" s="143" t="n">
+      <c r="G6" s="149" t="n">
         <v>135899</v>
       </c>
-      <c r="H6" s="143" t="n">
+      <c r="H6" s="149" t="n">
         <v>1483620</v>
       </c>
-      <c r="I6" s="143" t="n">
+      <c r="I6" s="149" t="n">
         <v>315000</v>
       </c>
-      <c r="J6" s="143" t="n">
+      <c r="J6" s="149" t="n">
         <v>370000</v>
       </c>
-      <c r="K6" s="143" t="n">
+      <c r="K6" s="149" t="n">
         <v>254000</v>
       </c>
-      <c r="L6" s="143" t="n">
+      <c r="L6" s="149" t="n">
         <v>322000</v>
       </c>
-      <c r="M6" s="143" t="n">
+      <c r="M6" s="149" t="n">
         <v>80248</v>
       </c>
-      <c r="N6" s="143" t="n">
+      <c r="N6" s="149" t="n">
         <v>197000</v>
       </c>
-      <c r="O6" s="143" t="n">
+      <c r="O6" s="149" t="n">
         <v>225807</v>
       </c>
-      <c r="P6" s="143" t="n">
+      <c r="P6" s="149" t="n">
         <v>169000</v>
       </c>
-      <c r="Q6" s="143" t="n">
+      <c r="Q6" s="149" t="n">
         <v>349000</v>
       </c>
-      <c r="R6" s="143" t="n">
+      <c r="R6" s="149" t="n">
         <v>850326</v>
       </c>
-      <c r="S6" s="143" t="n">
+      <c r="S6" s="149" t="n">
         <v>118000</v>
       </c>
-      <c r="T6" s="143" t="n">
+      <c r="T6" s="149" t="n">
         <v>375500</v>
       </c>
-      <c r="U6" s="143" t="n">
+      <c r="U6" s="149" t="n">
         <v>345000</v>
       </c>
-      <c r="V6" s="143" t="n">
+      <c r="V6" s="149" t="n">
         <v>420000</v>
       </c>
-      <c r="W6" s="143" t="n">
+      <c r="W6" s="149" t="n">
         <v>641000</v>
       </c>
-      <c r="X6" s="143" t="n">
+      <c r="X6" s="149" t="n">
         <v>404000</v>
       </c>
-      <c r="Y6" s="143" t="n">
+      <c r="Y6" s="149" t="n">
         <v>545000</v>
       </c>
-      <c r="Z6" s="143" t="n">
+      <c r="Z6" s="149" t="n">
         <v>191437</v>
       </c>
-      <c r="AA6" s="143" t="n"/>
-      <c r="AB6" s="143" t="n"/>
-      <c r="AC6" s="143" t="n"/>
-      <c r="AD6" s="143" t="n"/>
-      <c r="AE6" s="143" t="n"/>
-      <c r="AF6" s="143" t="n"/>
-      <c r="AG6" s="143" t="n"/>
-      <c r="AH6" s="143" t="n"/>
+      <c r="AA6" s="149" t="n">
+        <v>188552</v>
+      </c>
+      <c r="AB6" s="149" t="n"/>
+      <c r="AC6" s="149" t="n"/>
+      <c r="AD6" s="149" t="n"/>
+      <c r="AE6" s="149" t="n"/>
+      <c r="AF6" s="149" t="n"/>
+      <c r="AG6" s="149" t="n"/>
+      <c r="AH6" s="149" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="118">
       <c r="C7" s="142" t="inlineStr">
@@ -4380,83 +4384,85 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D7" s="143" t="n">
+      <c r="D7" s="149" t="n">
         <v>992</v>
       </c>
-      <c r="E7" s="143" t="n">
+      <c r="E7" s="149" t="n">
         <v>1755</v>
       </c>
-      <c r="F7" s="143" t="n">
+      <c r="F7" s="149" t="n">
         <v>3886</v>
       </c>
-      <c r="G7" s="143" t="n">
+      <c r="G7" s="149" t="n">
         <v>6353</v>
       </c>
-      <c r="H7" s="143" t="n">
+      <c r="H7" s="149" t="n">
         <v>43416</v>
       </c>
-      <c r="I7" s="143" t="n">
+      <c r="I7" s="149" t="n">
         <v>7290</v>
       </c>
-      <c r="J7" s="143" t="n">
+      <c r="J7" s="149" t="n">
         <v>7500</v>
       </c>
-      <c r="K7" s="143" t="n">
+      <c r="K7" s="149" t="n">
         <v>3857</v>
       </c>
-      <c r="L7" s="143" t="n">
+      <c r="L7" s="149" t="n">
         <v>5197</v>
       </c>
-      <c r="M7" s="143" t="n">
+      <c r="M7" s="149" t="n">
         <v>3846</v>
       </c>
-      <c r="N7" s="143" t="n">
+      <c r="N7" s="149" t="n">
         <v>4264</v>
       </c>
-      <c r="O7" s="143" t="n">
+      <c r="O7" s="149" t="n">
         <v>3920</v>
       </c>
-      <c r="P7" s="143" t="n">
+      <c r="P7" s="149" t="n">
         <v>3692</v>
       </c>
-      <c r="Q7" s="143" t="n">
+      <c r="Q7" s="149" t="n">
         <v>4033</v>
       </c>
-      <c r="R7" s="143" t="n">
+      <c r="R7" s="149" t="n">
         <v>19468</v>
       </c>
-      <c r="S7" s="143" t="n">
+      <c r="S7" s="149" t="n">
         <v>2517</v>
       </c>
-      <c r="T7" s="143" t="n">
+      <c r="T7" s="149" t="n">
         <v>3512</v>
       </c>
-      <c r="U7" s="143" t="n">
+      <c r="U7" s="149" t="n">
         <v>4514</v>
       </c>
-      <c r="V7" s="143" t="n">
+      <c r="V7" s="149" t="n">
         <v>3885</v>
       </c>
-      <c r="W7" s="143" t="n">
+      <c r="W7" s="149" t="n">
         <v>5760</v>
       </c>
-      <c r="X7" s="143" t="n">
+      <c r="X7" s="149" t="n">
         <v>4669</v>
       </c>
-      <c r="Y7" s="143" t="n">
+      <c r="Y7" s="149" t="n">
         <v>3658</v>
       </c>
-      <c r="Z7" s="143" t="n">
+      <c r="Z7" s="149" t="n">
         <v>1392</v>
       </c>
-      <c r="AA7" s="143" t="n"/>
-      <c r="AB7" s="143" t="n"/>
-      <c r="AC7" s="143" t="n"/>
-      <c r="AD7" s="143" t="n"/>
-      <c r="AE7" s="143" t="n"/>
-      <c r="AF7" s="143" t="n"/>
-      <c r="AG7" s="143" t="n"/>
-      <c r="AH7" s="143" t="n"/>
+      <c r="AA7" s="149" t="n">
+        <v>2860</v>
+      </c>
+      <c r="AB7" s="149" t="n"/>
+      <c r="AC7" s="149" t="n"/>
+      <c r="AD7" s="149" t="n"/>
+      <c r="AE7" s="149" t="n"/>
+      <c r="AF7" s="149" t="n"/>
+      <c r="AG7" s="149" t="n"/>
+      <c r="AH7" s="149" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="118">
       <c r="C8" s="142" t="inlineStr">
@@ -4464,83 +4470,85 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D8" s="143" t="n">
+      <c r="D8" s="149" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="143" t="n">
+      <c r="E8" s="149" t="n">
         <v>60</v>
       </c>
-      <c r="F8" s="143" t="n">
+      <c r="F8" s="149" t="n">
         <v>69</v>
       </c>
-      <c r="G8" s="143" t="n">
+      <c r="G8" s="149" t="n">
         <v>38</v>
       </c>
-      <c r="H8" s="143" t="n">
+      <c r="H8" s="149" t="n">
         <v>282</v>
       </c>
-      <c r="I8" s="143" t="n">
+      <c r="I8" s="149" t="n">
         <v>90</v>
       </c>
-      <c r="J8" s="143" t="n">
+      <c r="J8" s="149" t="n">
         <v>84</v>
       </c>
-      <c r="K8" s="143" t="n">
+      <c r="K8" s="149" t="n">
         <v>48</v>
       </c>
-      <c r="L8" s="143" t="n">
+      <c r="L8" s="149" t="n">
         <v>58</v>
       </c>
-      <c r="M8" s="143" t="n">
+      <c r="M8" s="149" t="n">
         <v>50</v>
       </c>
-      <c r="N8" s="143" t="n">
+      <c r="N8" s="149" t="n">
         <v>51</v>
       </c>
-      <c r="O8" s="143" t="n">
+      <c r="O8" s="149" t="n">
         <v>44</v>
       </c>
-      <c r="P8" s="143" t="n">
+      <c r="P8" s="149" t="n">
         <v>31</v>
       </c>
-      <c r="Q8" s="143" t="n">
+      <c r="Q8" s="149" t="n">
         <v>39</v>
       </c>
-      <c r="R8" s="143" t="n">
+      <c r="R8" s="149" t="n">
         <v>162</v>
       </c>
-      <c r="S8" s="143" t="n">
+      <c r="S8" s="149" t="n">
         <v>45</v>
       </c>
-      <c r="T8" s="143" t="n">
+      <c r="T8" s="149" t="n">
         <v>131</v>
       </c>
-      <c r="U8" s="143" t="n">
+      <c r="U8" s="149" t="n">
         <v>150</v>
       </c>
-      <c r="V8" s="143" t="n">
+      <c r="V8" s="149" t="n">
         <v>131</v>
       </c>
-      <c r="W8" s="143" t="n">
+      <c r="W8" s="149" t="n">
         <v>120</v>
       </c>
-      <c r="X8" s="143" t="n">
+      <c r="X8" s="149" t="n">
         <v>100</v>
       </c>
-      <c r="Y8" s="143" t="n">
+      <c r="Y8" s="149" t="n">
         <v>80</v>
       </c>
-      <c r="Z8" s="143" t="n">
+      <c r="Z8" s="149" t="n">
         <v>62</v>
       </c>
-      <c r="AA8" s="143" t="n"/>
-      <c r="AB8" s="143" t="n"/>
-      <c r="AC8" s="143" t="n"/>
-      <c r="AD8" s="143" t="n"/>
-      <c r="AE8" s="143" t="n"/>
-      <c r="AF8" s="143" t="n"/>
-      <c r="AG8" s="143" t="n"/>
-      <c r="AH8" s="143" t="n"/>
+      <c r="AA8" s="149" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB8" s="149" t="n"/>
+      <c r="AC8" s="149" t="n"/>
+      <c r="AD8" s="149" t="n"/>
+      <c r="AE8" s="149" t="n"/>
+      <c r="AF8" s="149" t="n"/>
+      <c r="AG8" s="149" t="n"/>
+      <c r="AH8" s="149" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="118">
       <c r="C9" s="142" t="inlineStr">
@@ -4815,63 +4823,65 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D12" s="143" t="n">
+      <c r="D12" s="149" t="n">
         <v>3191</v>
       </c>
-      <c r="E12" s="143" t="n">
+      <c r="E12" s="149" t="n">
         <v>2292</v>
       </c>
-      <c r="F12" s="143" t="n">
+      <c r="F12" s="149" t="n">
         <v>1826</v>
       </c>
-      <c r="G12" s="143" t="n">
+      <c r="G12" s="149" t="n">
         <v>3124</v>
       </c>
-      <c r="H12" s="143" t="n">
+      <c r="H12" s="149" t="n">
         <v>7997</v>
       </c>
-      <c r="I12" s="143" t="n">
+      <c r="I12" s="149" t="n">
         <v>4004</v>
       </c>
-      <c r="J12" s="143" t="n"/>
-      <c r="K12" s="143" t="n"/>
-      <c r="L12" s="143" t="n"/>
-      <c r="M12" s="143" t="n"/>
-      <c r="N12" s="143" t="n"/>
-      <c r="O12" s="143" t="n"/>
-      <c r="P12" s="143" t="n"/>
-      <c r="Q12" s="143" t="n"/>
-      <c r="R12" s="143" t="n"/>
-      <c r="S12" s="143" t="n"/>
-      <c r="T12" s="143" t="n">
+      <c r="J12" s="149" t="n"/>
+      <c r="K12" s="149" t="n"/>
+      <c r="L12" s="149" t="n"/>
+      <c r="M12" s="149" t="n"/>
+      <c r="N12" s="149" t="n"/>
+      <c r="O12" s="149" t="n"/>
+      <c r="P12" s="149" t="n"/>
+      <c r="Q12" s="149" t="n"/>
+      <c r="R12" s="149" t="n"/>
+      <c r="S12" s="149" t="n"/>
+      <c r="T12" s="149" t="n">
         <v>6070</v>
       </c>
-      <c r="U12" s="143" t="n">
+      <c r="U12" s="149" t="n">
         <v>5389</v>
       </c>
-      <c r="V12" s="143" t="n">
+      <c r="V12" s="149" t="n">
         <v>5600</v>
       </c>
-      <c r="W12" s="143" t="n">
+      <c r="W12" s="149" t="n">
         <v>6086</v>
       </c>
-      <c r="X12" s="143" t="n">
+      <c r="X12" s="149" t="n">
         <v>6093</v>
       </c>
-      <c r="Y12" s="143" t="n">
+      <c r="Y12" s="149" t="n">
         <v>9860</v>
       </c>
-      <c r="Z12" s="143" t="n">
+      <c r="Z12" s="149" t="n">
         <v>6079</v>
       </c>
-      <c r="AA12" s="143" t="n"/>
-      <c r="AB12" s="143" t="n"/>
-      <c r="AC12" s="143" t="n"/>
-      <c r="AD12" s="143" t="n"/>
-      <c r="AE12" s="143" t="n"/>
-      <c r="AF12" s="143" t="n"/>
-      <c r="AG12" s="143" t="n"/>
-      <c r="AH12" s="143" t="n"/>
+      <c r="AA12" s="149" t="n">
+        <v>7371</v>
+      </c>
+      <c r="AB12" s="149" t="n"/>
+      <c r="AC12" s="149" t="n"/>
+      <c r="AD12" s="149" t="n"/>
+      <c r="AE12" s="149" t="n"/>
+      <c r="AF12" s="149" t="n"/>
+      <c r="AG12" s="149" t="n"/>
+      <c r="AH12" s="149" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="118">
       <c r="C13" s="142" t="inlineStr">
@@ -4879,63 +4889,65 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D13" s="143" t="n">
+      <c r="D13" s="149" t="n">
         <v>60886</v>
       </c>
-      <c r="E13" s="143" t="n">
+      <c r="E13" s="149" t="n">
         <v>29714</v>
       </c>
-      <c r="F13" s="143" t="n">
+      <c r="F13" s="149" t="n">
         <v>29210</v>
       </c>
-      <c r="G13" s="143" t="n">
+      <c r="G13" s="149" t="n">
         <v>87821</v>
       </c>
-      <c r="H13" s="143" t="n">
+      <c r="H13" s="149" t="n">
         <v>376050</v>
       </c>
-      <c r="I13" s="143" t="n">
+      <c r="I13" s="149" t="n">
         <v>19400</v>
       </c>
-      <c r="J13" s="143" t="n"/>
-      <c r="K13" s="143" t="n"/>
-      <c r="L13" s="143" t="n"/>
-      <c r="M13" s="143" t="n"/>
-      <c r="N13" s="143" t="n"/>
-      <c r="O13" s="143" t="n"/>
-      <c r="P13" s="143" t="n"/>
-      <c r="Q13" s="143" t="n"/>
-      <c r="R13" s="143" t="n"/>
-      <c r="S13" s="143" t="n"/>
-      <c r="T13" s="143" t="n">
+      <c r="J13" s="149" t="n"/>
+      <c r="K13" s="149" t="n"/>
+      <c r="L13" s="149" t="n"/>
+      <c r="M13" s="149" t="n"/>
+      <c r="N13" s="149" t="n"/>
+      <c r="O13" s="149" t="n"/>
+      <c r="P13" s="149" t="n"/>
+      <c r="Q13" s="149" t="n"/>
+      <c r="R13" s="149" t="n"/>
+      <c r="S13" s="149" t="n"/>
+      <c r="T13" s="149" t="n">
         <v>2355</v>
       </c>
-      <c r="U13" s="143" t="n">
+      <c r="U13" s="149" t="n">
         <v>3071</v>
       </c>
-      <c r="V13" s="143" t="n">
+      <c r="V13" s="149" t="n">
         <v>19500</v>
       </c>
-      <c r="W13" s="143" t="n">
+      <c r="W13" s="149" t="n">
         <v>8900</v>
       </c>
-      <c r="X13" s="143" t="n">
+      <c r="X13" s="149" t="n">
         <v>12000</v>
       </c>
-      <c r="Y13" s="143" t="n">
+      <c r="Y13" s="149" t="n">
         <v>18000</v>
       </c>
-      <c r="Z13" s="143" t="n">
+      <c r="Z13" s="149" t="n">
         <v>10756</v>
       </c>
-      <c r="AA13" s="143" t="n"/>
-      <c r="AB13" s="143" t="n"/>
-      <c r="AC13" s="143" t="n"/>
-      <c r="AD13" s="143" t="n"/>
-      <c r="AE13" s="143" t="n"/>
-      <c r="AF13" s="143" t="n"/>
-      <c r="AG13" s="143" t="n"/>
-      <c r="AH13" s="143" t="n"/>
+      <c r="AA13" s="149" t="n">
+        <v>15817</v>
+      </c>
+      <c r="AB13" s="149" t="n"/>
+      <c r="AC13" s="149" t="n"/>
+      <c r="AD13" s="149" t="n"/>
+      <c r="AE13" s="149" t="n"/>
+      <c r="AF13" s="149" t="n"/>
+      <c r="AG13" s="149" t="n"/>
+      <c r="AH13" s="149" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="118">
       <c r="C14" s="142" t="inlineStr">
@@ -4943,63 +4955,65 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D14" s="143" t="n">
+      <c r="D14" s="149" t="n">
         <v>1035</v>
       </c>
-      <c r="E14" s="143" t="n">
+      <c r="E14" s="149" t="n">
         <v>550</v>
       </c>
-      <c r="F14" s="143" t="n">
+      <c r="F14" s="149" t="n">
         <v>909</v>
       </c>
-      <c r="G14" s="143" t="n">
+      <c r="G14" s="149" t="n">
         <v>2631</v>
       </c>
-      <c r="H14" s="143" t="n">
+      <c r="H14" s="149" t="n">
         <v>3476</v>
       </c>
-      <c r="I14" s="143" t="n">
+      <c r="I14" s="149" t="n">
         <v>849</v>
       </c>
-      <c r="J14" s="143" t="n"/>
-      <c r="K14" s="143" t="n"/>
-      <c r="L14" s="143" t="n"/>
-      <c r="M14" s="143" t="n"/>
-      <c r="N14" s="143" t="n"/>
-      <c r="O14" s="143" t="n"/>
-      <c r="P14" s="143" t="n"/>
-      <c r="Q14" s="143" t="n"/>
-      <c r="R14" s="143" t="n"/>
-      <c r="S14" s="143" t="n"/>
-      <c r="T14" s="143" t="n">
+      <c r="J14" s="149" t="n"/>
+      <c r="K14" s="149" t="n"/>
+      <c r="L14" s="149" t="n"/>
+      <c r="M14" s="149" t="n"/>
+      <c r="N14" s="149" t="n"/>
+      <c r="O14" s="149" t="n"/>
+      <c r="P14" s="149" t="n"/>
+      <c r="Q14" s="149" t="n"/>
+      <c r="R14" s="149" t="n"/>
+      <c r="S14" s="149" t="n"/>
+      <c r="T14" s="149" t="n">
         <v>238</v>
       </c>
-      <c r="U14" s="143" t="n">
+      <c r="U14" s="149" t="n">
         <v>302</v>
       </c>
-      <c r="V14" s="143" t="n">
+      <c r="V14" s="149" t="n">
         <v>8271</v>
       </c>
-      <c r="W14" s="143" t="n">
+      <c r="W14" s="149" t="n">
         <v>593</v>
       </c>
-      <c r="X14" s="143" t="n">
+      <c r="X14" s="149" t="n">
         <v>705</v>
       </c>
-      <c r="Y14" s="143" t="n">
+      <c r="Y14" s="149" t="n">
         <v>910</v>
       </c>
-      <c r="Z14" s="143" t="n">
+      <c r="Z14" s="149" t="n">
         <v>522</v>
       </c>
-      <c r="AA14" s="143" t="n"/>
-      <c r="AB14" s="143" t="n"/>
-      <c r="AC14" s="143" t="n"/>
-      <c r="AD14" s="143" t="n"/>
-      <c r="AE14" s="143" t="n"/>
-      <c r="AF14" s="143" t="n"/>
-      <c r="AG14" s="143" t="n"/>
-      <c r="AH14" s="143" t="n"/>
+      <c r="AA14" s="149" t="n">
+        <v>801</v>
+      </c>
+      <c r="AB14" s="149" t="n"/>
+      <c r="AC14" s="149" t="n"/>
+      <c r="AD14" s="149" t="n"/>
+      <c r="AE14" s="149" t="n"/>
+      <c r="AF14" s="149" t="n"/>
+      <c r="AG14" s="149" t="n"/>
+      <c r="AH14" s="149" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="118">
       <c r="C15" s="142" t="inlineStr">
@@ -5007,63 +5021,65 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D15" s="143" t="n">
+      <c r="D15" s="149" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="143" t="n">
+      <c r="E15" s="149" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="143" t="n">
+      <c r="F15" s="149" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="143" t="n">
+      <c r="G15" s="149" t="n">
         <v>20</v>
       </c>
-      <c r="H15" s="143" t="n">
+      <c r="H15" s="149" t="n">
         <v>69</v>
       </c>
-      <c r="I15" s="143" t="n">
+      <c r="I15" s="149" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="143" t="n"/>
-      <c r="K15" s="143" t="n"/>
-      <c r="L15" s="143" t="n"/>
-      <c r="M15" s="143" t="n"/>
-      <c r="N15" s="143" t="n"/>
-      <c r="O15" s="143" t="n"/>
-      <c r="P15" s="143" t="n"/>
-      <c r="Q15" s="143" t="n"/>
-      <c r="R15" s="143" t="n"/>
-      <c r="S15" s="143" t="n"/>
-      <c r="T15" s="143" t="n">
+      <c r="J15" s="149" t="n"/>
+      <c r="K15" s="149" t="n"/>
+      <c r="L15" s="149" t="n"/>
+      <c r="M15" s="149" t="n"/>
+      <c r="N15" s="149" t="n"/>
+      <c r="O15" s="149" t="n"/>
+      <c r="P15" s="149" t="n"/>
+      <c r="Q15" s="149" t="n"/>
+      <c r="R15" s="149" t="n"/>
+      <c r="S15" s="149" t="n"/>
+      <c r="T15" s="149" t="n">
         <v>28</v>
       </c>
-      <c r="U15" s="143" t="n">
+      <c r="U15" s="149" t="n">
         <v>32</v>
       </c>
-      <c r="V15" s="143" t="n">
+      <c r="V15" s="149" t="n">
         <v>47</v>
       </c>
-      <c r="W15" s="143" t="n">
+      <c r="W15" s="149" t="n">
         <v>41</v>
       </c>
-      <c r="X15" s="143" t="n">
+      <c r="X15" s="149" t="n">
         <v>80</v>
       </c>
-      <c r="Y15" s="143" t="n">
+      <c r="Y15" s="149" t="n">
         <v>74</v>
       </c>
-      <c r="Z15" s="143" t="n">
+      <c r="Z15" s="149" t="n">
         <v>58</v>
       </c>
-      <c r="AA15" s="143" t="n"/>
-      <c r="AB15" s="143" t="n"/>
-      <c r="AC15" s="143" t="n"/>
-      <c r="AD15" s="143" t="n"/>
-      <c r="AE15" s="143" t="n"/>
-      <c r="AF15" s="143" t="n"/>
-      <c r="AG15" s="143" t="n"/>
-      <c r="AH15" s="143" t="n"/>
+      <c r="AA15" s="149" t="n">
+        <v>81</v>
+      </c>
+      <c r="AB15" s="149" t="n"/>
+      <c r="AC15" s="149" t="n"/>
+      <c r="AD15" s="149" t="n"/>
+      <c r="AE15" s="149" t="n"/>
+      <c r="AF15" s="149" t="n"/>
+      <c r="AG15" s="149" t="n"/>
+      <c r="AH15" s="149" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="118">
       <c r="C16" s="142" t="inlineStr">
@@ -5338,43 +5354,45 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D19" s="143" t="n"/>
-      <c r="E19" s="143" t="n"/>
-      <c r="F19" s="143" t="n"/>
-      <c r="G19" s="143" t="n"/>
-      <c r="H19" s="143" t="n">
+      <c r="D19" s="149" t="n"/>
+      <c r="E19" s="149" t="n"/>
+      <c r="F19" s="149" t="n"/>
+      <c r="G19" s="149" t="n"/>
+      <c r="H19" s="149" t="n">
         <v>14239</v>
       </c>
-      <c r="I19" s="143" t="n"/>
-      <c r="J19" s="143" t="n"/>
-      <c r="K19" s="143" t="n"/>
-      <c r="L19" s="143" t="n"/>
-      <c r="M19" s="143" t="n"/>
-      <c r="N19" s="143" t="n"/>
-      <c r="O19" s="143" t="n"/>
-      <c r="P19" s="143" t="n"/>
-      <c r="Q19" s="143" t="n"/>
-      <c r="R19" s="143" t="n"/>
-      <c r="S19" s="143" t="n"/>
-      <c r="T19" s="143" t="n"/>
-      <c r="U19" s="143" t="n"/>
-      <c r="V19" s="143" t="n"/>
-      <c r="W19" s="143" t="n"/>
-      <c r="X19" s="143" t="n">
+      <c r="I19" s="149" t="n"/>
+      <c r="J19" s="149" t="n"/>
+      <c r="K19" s="149" t="n"/>
+      <c r="L19" s="149" t="n"/>
+      <c r="M19" s="149" t="n"/>
+      <c r="N19" s="149" t="n"/>
+      <c r="O19" s="149" t="n"/>
+      <c r="P19" s="149" t="n"/>
+      <c r="Q19" s="149" t="n"/>
+      <c r="R19" s="149" t="n"/>
+      <c r="S19" s="149" t="n"/>
+      <c r="T19" s="149" t="n"/>
+      <c r="U19" s="149" t="n"/>
+      <c r="V19" s="149" t="n"/>
+      <c r="W19" s="149" t="n"/>
+      <c r="X19" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" s="143" t="n">
+      <c r="Y19" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="143" t="n"/>
-      <c r="AA19" s="143" t="n"/>
-      <c r="AB19" s="143" t="n"/>
-      <c r="AC19" s="143" t="n"/>
-      <c r="AD19" s="143" t="n"/>
-      <c r="AE19" s="143" t="n"/>
-      <c r="AF19" s="143" t="n"/>
-      <c r="AG19" s="143" t="n"/>
-      <c r="AH19" s="143" t="n"/>
+      <c r="Z19" s="149" t="n"/>
+      <c r="AA19" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="149" t="n"/>
+      <c r="AC19" s="149" t="n"/>
+      <c r="AD19" s="149" t="n"/>
+      <c r="AE19" s="149" t="n"/>
+      <c r="AF19" s="149" t="n"/>
+      <c r="AG19" s="149" t="n"/>
+      <c r="AH19" s="149" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="118">
       <c r="C20" s="142" t="inlineStr">
@@ -5382,43 +5400,45 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D20" s="143" t="n"/>
-      <c r="E20" s="143" t="n"/>
-      <c r="F20" s="143" t="n"/>
-      <c r="G20" s="143" t="n"/>
-      <c r="H20" s="143" t="n">
+      <c r="D20" s="149" t="n"/>
+      <c r="E20" s="149" t="n"/>
+      <c r="F20" s="149" t="n"/>
+      <c r="G20" s="149" t="n"/>
+      <c r="H20" s="149" t="n">
         <v>302714</v>
       </c>
-      <c r="I20" s="143" t="n"/>
-      <c r="J20" s="143" t="n"/>
-      <c r="K20" s="143" t="n"/>
-      <c r="L20" s="143" t="n"/>
-      <c r="M20" s="143" t="n"/>
-      <c r="N20" s="143" t="n"/>
-      <c r="O20" s="143" t="n"/>
-      <c r="P20" s="143" t="n"/>
-      <c r="Q20" s="143" t="n"/>
-      <c r="R20" s="143" t="n"/>
-      <c r="S20" s="143" t="n"/>
-      <c r="T20" s="143" t="n"/>
-      <c r="U20" s="143" t="n"/>
-      <c r="V20" s="143" t="n"/>
-      <c r="W20" s="143" t="n"/>
-      <c r="X20" s="143" t="n">
+      <c r="I20" s="149" t="n"/>
+      <c r="J20" s="149" t="n"/>
+      <c r="K20" s="149" t="n"/>
+      <c r="L20" s="149" t="n"/>
+      <c r="M20" s="149" t="n"/>
+      <c r="N20" s="149" t="n"/>
+      <c r="O20" s="149" t="n"/>
+      <c r="P20" s="149" t="n"/>
+      <c r="Q20" s="149" t="n"/>
+      <c r="R20" s="149" t="n"/>
+      <c r="S20" s="149" t="n"/>
+      <c r="T20" s="149" t="n"/>
+      <c r="U20" s="149" t="n"/>
+      <c r="V20" s="149" t="n"/>
+      <c r="W20" s="149" t="n"/>
+      <c r="X20" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" s="143" t="n">
+      <c r="Y20" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="143" t="n"/>
-      <c r="AA20" s="143" t="n"/>
-      <c r="AB20" s="143" t="n"/>
-      <c r="AC20" s="143" t="n"/>
-      <c r="AD20" s="143" t="n"/>
-      <c r="AE20" s="143" t="n"/>
-      <c r="AF20" s="143" t="n"/>
-      <c r="AG20" s="143" t="n"/>
-      <c r="AH20" s="143" t="n"/>
+      <c r="Z20" s="149" t="n"/>
+      <c r="AA20" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="149" t="n"/>
+      <c r="AC20" s="149" t="n"/>
+      <c r="AD20" s="149" t="n"/>
+      <c r="AE20" s="149" t="n"/>
+      <c r="AF20" s="149" t="n"/>
+      <c r="AG20" s="149" t="n"/>
+      <c r="AH20" s="149" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="118">
       <c r="C21" s="142" t="inlineStr">
@@ -5426,43 +5446,45 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D21" s="143" t="n"/>
-      <c r="E21" s="143" t="n"/>
-      <c r="F21" s="143" t="n"/>
-      <c r="G21" s="143" t="n"/>
-      <c r="H21" s="143" t="n">
+      <c r="D21" s="149" t="n"/>
+      <c r="E21" s="149" t="n"/>
+      <c r="F21" s="149" t="n"/>
+      <c r="G21" s="149" t="n"/>
+      <c r="H21" s="149" t="n">
         <v>5320</v>
       </c>
-      <c r="I21" s="143" t="n"/>
-      <c r="J21" s="143" t="n"/>
-      <c r="K21" s="143" t="n"/>
-      <c r="L21" s="143" t="n"/>
-      <c r="M21" s="143" t="n"/>
-      <c r="N21" s="143" t="n"/>
-      <c r="O21" s="143" t="n"/>
-      <c r="P21" s="143" t="n"/>
-      <c r="Q21" s="143" t="n"/>
-      <c r="R21" s="143" t="n"/>
-      <c r="S21" s="143" t="n"/>
-      <c r="T21" s="143" t="n"/>
-      <c r="U21" s="143" t="n"/>
-      <c r="V21" s="143" t="n"/>
-      <c r="W21" s="143" t="n"/>
-      <c r="X21" s="143" t="n">
+      <c r="I21" s="149" t="n"/>
+      <c r="J21" s="149" t="n"/>
+      <c r="K21" s="149" t="n"/>
+      <c r="L21" s="149" t="n"/>
+      <c r="M21" s="149" t="n"/>
+      <c r="N21" s="149" t="n"/>
+      <c r="O21" s="149" t="n"/>
+      <c r="P21" s="149" t="n"/>
+      <c r="Q21" s="149" t="n"/>
+      <c r="R21" s="149" t="n"/>
+      <c r="S21" s="149" t="n"/>
+      <c r="T21" s="149" t="n"/>
+      <c r="U21" s="149" t="n"/>
+      <c r="V21" s="149" t="n"/>
+      <c r="W21" s="149" t="n"/>
+      <c r="X21" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" s="143" t="n">
+      <c r="Y21" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="143" t="n"/>
-      <c r="AA21" s="143" t="n"/>
-      <c r="AB21" s="143" t="n"/>
-      <c r="AC21" s="143" t="n"/>
-      <c r="AD21" s="143" t="n"/>
-      <c r="AE21" s="143" t="n"/>
-      <c r="AF21" s="143" t="n"/>
-      <c r="AG21" s="143" t="n"/>
-      <c r="AH21" s="143" t="n"/>
+      <c r="Z21" s="149" t="n"/>
+      <c r="AA21" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="149" t="n"/>
+      <c r="AC21" s="149" t="n"/>
+      <c r="AD21" s="149" t="n"/>
+      <c r="AE21" s="149" t="n"/>
+      <c r="AF21" s="149" t="n"/>
+      <c r="AG21" s="149" t="n"/>
+      <c r="AH21" s="149" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="118">
       <c r="C22" s="142" t="inlineStr">
@@ -5470,43 +5492,45 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D22" s="143" t="n"/>
-      <c r="E22" s="143" t="n"/>
-      <c r="F22" s="143" t="n"/>
-      <c r="G22" s="143" t="n"/>
-      <c r="H22" s="143" t="n">
+      <c r="D22" s="149" t="n"/>
+      <c r="E22" s="149" t="n"/>
+      <c r="F22" s="149" t="n"/>
+      <c r="G22" s="149" t="n"/>
+      <c r="H22" s="149" t="n">
         <v>17</v>
       </c>
-      <c r="I22" s="143" t="n"/>
-      <c r="J22" s="143" t="n"/>
-      <c r="K22" s="143" t="n"/>
-      <c r="L22" s="143" t="n"/>
-      <c r="M22" s="143" t="n"/>
-      <c r="N22" s="143" t="n"/>
-      <c r="O22" s="143" t="n"/>
-      <c r="P22" s="143" t="n"/>
-      <c r="Q22" s="143" t="n"/>
-      <c r="R22" s="143" t="n"/>
-      <c r="S22" s="143" t="n"/>
-      <c r="T22" s="143" t="n"/>
-      <c r="U22" s="143" t="n"/>
-      <c r="V22" s="143" t="n"/>
-      <c r="W22" s="143" t="n"/>
-      <c r="X22" s="143" t="n">
+      <c r="I22" s="149" t="n"/>
+      <c r="J22" s="149" t="n"/>
+      <c r="K22" s="149" t="n"/>
+      <c r="L22" s="149" t="n"/>
+      <c r="M22" s="149" t="n"/>
+      <c r="N22" s="149" t="n"/>
+      <c r="O22" s="149" t="n"/>
+      <c r="P22" s="149" t="n"/>
+      <c r="Q22" s="149" t="n"/>
+      <c r="R22" s="149" t="n"/>
+      <c r="S22" s="149" t="n"/>
+      <c r="T22" s="149" t="n"/>
+      <c r="U22" s="149" t="n"/>
+      <c r="V22" s="149" t="n"/>
+      <c r="W22" s="149" t="n"/>
+      <c r="X22" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="143" t="n">
+      <c r="Y22" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="143" t="n"/>
-      <c r="AA22" s="143" t="n"/>
-      <c r="AB22" s="143" t="n"/>
-      <c r="AC22" s="143" t="n"/>
-      <c r="AD22" s="143" t="n"/>
-      <c r="AE22" s="143" t="n"/>
-      <c r="AF22" s="143" t="n"/>
-      <c r="AG22" s="143" t="n"/>
-      <c r="AH22" s="143" t="n"/>
+      <c r="Z22" s="149" t="n"/>
+      <c r="AA22" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="149" t="n"/>
+      <c r="AC22" s="149" t="n"/>
+      <c r="AD22" s="149" t="n"/>
+      <c r="AE22" s="149" t="n"/>
+      <c r="AF22" s="149" t="n"/>
+      <c r="AG22" s="149" t="n"/>
+      <c r="AH22" s="149" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="118">
       <c r="C23" s="142" t="inlineStr">
@@ -5781,41 +5805,43 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D26" s="143" t="n"/>
-      <c r="E26" s="143" t="n"/>
-      <c r="F26" s="143" t="n"/>
-      <c r="G26" s="143" t="n"/>
-      <c r="H26" s="143" t="n"/>
-      <c r="I26" s="143" t="n"/>
-      <c r="J26" s="143" t="n"/>
-      <c r="K26" s="143" t="n"/>
-      <c r="L26" s="143" t="n"/>
-      <c r="M26" s="143" t="n"/>
-      <c r="N26" s="143" t="n"/>
-      <c r="O26" s="143" t="n"/>
-      <c r="P26" s="143" t="n"/>
-      <c r="Q26" s="143" t="n"/>
-      <c r="R26" s="143" t="n"/>
-      <c r="S26" s="143" t="n"/>
-      <c r="T26" s="143" t="n"/>
-      <c r="U26" s="143" t="n"/>
-      <c r="V26" s="143" t="n"/>
-      <c r="W26" s="143" t="n"/>
-      <c r="X26" s="143" t="n">
+      <c r="D26" s="149" t="n"/>
+      <c r="E26" s="149" t="n"/>
+      <c r="F26" s="149" t="n"/>
+      <c r="G26" s="149" t="n"/>
+      <c r="H26" s="149" t="n"/>
+      <c r="I26" s="149" t="n"/>
+      <c r="J26" s="149" t="n"/>
+      <c r="K26" s="149" t="n"/>
+      <c r="L26" s="149" t="n"/>
+      <c r="M26" s="149" t="n"/>
+      <c r="N26" s="149" t="n"/>
+      <c r="O26" s="149" t="n"/>
+      <c r="P26" s="149" t="n"/>
+      <c r="Q26" s="149" t="n"/>
+      <c r="R26" s="149" t="n"/>
+      <c r="S26" s="149" t="n"/>
+      <c r="T26" s="149" t="n"/>
+      <c r="U26" s="149" t="n"/>
+      <c r="V26" s="149" t="n"/>
+      <c r="W26" s="149" t="n"/>
+      <c r="X26" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y26" s="143" t="n">
+      <c r="Y26" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="143" t="n"/>
-      <c r="AA26" s="143" t="n"/>
-      <c r="AB26" s="143" t="n"/>
-      <c r="AC26" s="143" t="n"/>
-      <c r="AD26" s="143" t="n"/>
-      <c r="AE26" s="143" t="n"/>
-      <c r="AF26" s="143" t="n"/>
-      <c r="AG26" s="143" t="n"/>
-      <c r="AH26" s="143" t="n"/>
+      <c r="Z26" s="149" t="n"/>
+      <c r="AA26" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="149" t="n"/>
+      <c r="AC26" s="149" t="n"/>
+      <c r="AD26" s="149" t="n"/>
+      <c r="AE26" s="149" t="n"/>
+      <c r="AF26" s="149" t="n"/>
+      <c r="AG26" s="149" t="n"/>
+      <c r="AH26" s="149" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="118">
       <c r="C27" s="142" t="inlineStr">
@@ -5823,41 +5849,43 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D27" s="143" t="n"/>
-      <c r="E27" s="143" t="n"/>
-      <c r="F27" s="143" t="n"/>
-      <c r="G27" s="143" t="n"/>
-      <c r="H27" s="143" t="n"/>
-      <c r="I27" s="143" t="n"/>
-      <c r="J27" s="143" t="n"/>
-      <c r="K27" s="143" t="n"/>
-      <c r="L27" s="143" t="n"/>
-      <c r="M27" s="143" t="n"/>
-      <c r="N27" s="143" t="n"/>
-      <c r="O27" s="143" t="n"/>
-      <c r="P27" s="143" t="n"/>
-      <c r="Q27" s="143" t="n"/>
-      <c r="R27" s="143" t="n"/>
-      <c r="S27" s="143" t="n"/>
-      <c r="T27" s="143" t="n"/>
-      <c r="U27" s="143" t="n"/>
-      <c r="V27" s="143" t="n"/>
-      <c r="W27" s="143" t="n"/>
-      <c r="X27" s="143" t="n">
+      <c r="D27" s="149" t="n"/>
+      <c r="E27" s="149" t="n"/>
+      <c r="F27" s="149" t="n"/>
+      <c r="G27" s="149" t="n"/>
+      <c r="H27" s="149" t="n"/>
+      <c r="I27" s="149" t="n"/>
+      <c r="J27" s="149" t="n"/>
+      <c r="K27" s="149" t="n"/>
+      <c r="L27" s="149" t="n"/>
+      <c r="M27" s="149" t="n"/>
+      <c r="N27" s="149" t="n"/>
+      <c r="O27" s="149" t="n"/>
+      <c r="P27" s="149" t="n"/>
+      <c r="Q27" s="149" t="n"/>
+      <c r="R27" s="149" t="n"/>
+      <c r="S27" s="149" t="n"/>
+      <c r="T27" s="149" t="n"/>
+      <c r="U27" s="149" t="n"/>
+      <c r="V27" s="149" t="n"/>
+      <c r="W27" s="149" t="n"/>
+      <c r="X27" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y27" s="143" t="n">
+      <c r="Y27" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="143" t="n"/>
-      <c r="AA27" s="143" t="n"/>
-      <c r="AB27" s="143" t="n"/>
-      <c r="AC27" s="143" t="n"/>
-      <c r="AD27" s="143" t="n"/>
-      <c r="AE27" s="143" t="n"/>
-      <c r="AF27" s="143" t="n"/>
-      <c r="AG27" s="143" t="n"/>
-      <c r="AH27" s="143" t="n"/>
+      <c r="Z27" s="149" t="n"/>
+      <c r="AA27" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="149" t="n"/>
+      <c r="AC27" s="149" t="n"/>
+      <c r="AD27" s="149" t="n"/>
+      <c r="AE27" s="149" t="n"/>
+      <c r="AF27" s="149" t="n"/>
+      <c r="AG27" s="149" t="n"/>
+      <c r="AH27" s="149" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="118">
       <c r="C28" s="142" t="inlineStr">
@@ -5865,41 +5893,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D28" s="143" t="n"/>
-      <c r="E28" s="143" t="n"/>
-      <c r="F28" s="143" t="n"/>
-      <c r="G28" s="143" t="n"/>
-      <c r="H28" s="143" t="n"/>
-      <c r="I28" s="143" t="n"/>
-      <c r="J28" s="143" t="n"/>
-      <c r="K28" s="143" t="n"/>
-      <c r="L28" s="143" t="n"/>
-      <c r="M28" s="143" t="n"/>
-      <c r="N28" s="143" t="n"/>
-      <c r="O28" s="143" t="n"/>
-      <c r="P28" s="143" t="n"/>
-      <c r="Q28" s="143" t="n"/>
-      <c r="R28" s="143" t="n"/>
-      <c r="S28" s="143" t="n"/>
-      <c r="T28" s="143" t="n"/>
-      <c r="U28" s="143" t="n"/>
-      <c r="V28" s="143" t="n"/>
-      <c r="W28" s="143" t="n"/>
-      <c r="X28" s="143" t="n">
+      <c r="D28" s="149" t="n"/>
+      <c r="E28" s="149" t="n"/>
+      <c r="F28" s="149" t="n"/>
+      <c r="G28" s="149" t="n"/>
+      <c r="H28" s="149" t="n"/>
+      <c r="I28" s="149" t="n"/>
+      <c r="J28" s="149" t="n"/>
+      <c r="K28" s="149" t="n"/>
+      <c r="L28" s="149" t="n"/>
+      <c r="M28" s="149" t="n"/>
+      <c r="N28" s="149" t="n"/>
+      <c r="O28" s="149" t="n"/>
+      <c r="P28" s="149" t="n"/>
+      <c r="Q28" s="149" t="n"/>
+      <c r="R28" s="149" t="n"/>
+      <c r="S28" s="149" t="n"/>
+      <c r="T28" s="149" t="n"/>
+      <c r="U28" s="149" t="n"/>
+      <c r="V28" s="149" t="n"/>
+      <c r="W28" s="149" t="n"/>
+      <c r="X28" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y28" s="143" t="n">
+      <c r="Y28" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="143" t="n"/>
-      <c r="AA28" s="143" t="n"/>
-      <c r="AB28" s="143" t="n"/>
-      <c r="AC28" s="143" t="n"/>
-      <c r="AD28" s="143" t="n"/>
-      <c r="AE28" s="143" t="n"/>
-      <c r="AF28" s="143" t="n"/>
-      <c r="AG28" s="143" t="n"/>
-      <c r="AH28" s="143" t="n"/>
+      <c r="Z28" s="149" t="n"/>
+      <c r="AA28" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="149" t="n"/>
+      <c r="AC28" s="149" t="n"/>
+      <c r="AD28" s="149" t="n"/>
+      <c r="AE28" s="149" t="n"/>
+      <c r="AF28" s="149" t="n"/>
+      <c r="AG28" s="149" t="n"/>
+      <c r="AH28" s="149" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="118">
       <c r="C29" s="142" t="inlineStr">
@@ -5907,41 +5937,43 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D29" s="143" t="n"/>
-      <c r="E29" s="143" t="n"/>
-      <c r="F29" s="143" t="n"/>
-      <c r="G29" s="143" t="n"/>
-      <c r="H29" s="143" t="n"/>
-      <c r="I29" s="143" t="n"/>
-      <c r="J29" s="143" t="n"/>
-      <c r="K29" s="143" t="n"/>
-      <c r="L29" s="143" t="n"/>
-      <c r="M29" s="143" t="n"/>
-      <c r="N29" s="143" t="n"/>
-      <c r="O29" s="143" t="n"/>
-      <c r="P29" s="143" t="n"/>
-      <c r="Q29" s="143" t="n"/>
-      <c r="R29" s="143" t="n"/>
-      <c r="S29" s="143" t="n"/>
-      <c r="T29" s="143" t="n"/>
-      <c r="U29" s="143" t="n"/>
-      <c r="V29" s="143" t="n"/>
-      <c r="W29" s="143" t="n"/>
-      <c r="X29" s="143" t="n">
+      <c r="D29" s="149" t="n"/>
+      <c r="E29" s="149" t="n"/>
+      <c r="F29" s="149" t="n"/>
+      <c r="G29" s="149" t="n"/>
+      <c r="H29" s="149" t="n"/>
+      <c r="I29" s="149" t="n"/>
+      <c r="J29" s="149" t="n"/>
+      <c r="K29" s="149" t="n"/>
+      <c r="L29" s="149" t="n"/>
+      <c r="M29" s="149" t="n"/>
+      <c r="N29" s="149" t="n"/>
+      <c r="O29" s="149" t="n"/>
+      <c r="P29" s="149" t="n"/>
+      <c r="Q29" s="149" t="n"/>
+      <c r="R29" s="149" t="n"/>
+      <c r="S29" s="149" t="n"/>
+      <c r="T29" s="149" t="n"/>
+      <c r="U29" s="149" t="n"/>
+      <c r="V29" s="149" t="n"/>
+      <c r="W29" s="149" t="n"/>
+      <c r="X29" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y29" s="143" t="n">
+      <c r="Y29" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="143" t="n"/>
-      <c r="AA29" s="143" t="n"/>
-      <c r="AB29" s="143" t="n"/>
-      <c r="AC29" s="143" t="n"/>
-      <c r="AD29" s="143" t="n"/>
-      <c r="AE29" s="143" t="n"/>
-      <c r="AF29" s="143" t="n"/>
-      <c r="AG29" s="143" t="n"/>
-      <c r="AH29" s="143" t="n"/>
+      <c r="Z29" s="149" t="n"/>
+      <c r="AA29" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="149" t="n"/>
+      <c r="AC29" s="149" t="n"/>
+      <c r="AD29" s="149" t="n"/>
+      <c r="AE29" s="149" t="n"/>
+      <c r="AF29" s="149" t="n"/>
+      <c r="AG29" s="149" t="n"/>
+      <c r="AH29" s="149" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="118">
       <c r="C30" s="142" t="inlineStr">
@@ -6216,83 +6248,85 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D33" s="143" t="n">
+      <c r="D33" s="149" t="n">
         <v>3453</v>
       </c>
-      <c r="E33" s="143" t="n">
+      <c r="E33" s="149" t="n">
         <v>1526.33</v>
       </c>
-      <c r="F33" s="143" t="n">
+      <c r="F33" s="149" t="n">
         <v>749</v>
       </c>
-      <c r="G33" s="143" t="n">
+      <c r="G33" s="149" t="n">
         <v>486</v>
       </c>
-      <c r="H33" s="143" t="n">
+      <c r="H33" s="149" t="n">
         <v>343518</v>
       </c>
-      <c r="I33" s="143" t="n">
+      <c r="I33" s="149" t="n">
         <v>951</v>
       </c>
-      <c r="J33" s="143" t="n">
+      <c r="J33" s="149" t="n">
         <v>924</v>
       </c>
-      <c r="K33" s="143" t="n">
+      <c r="K33" s="149" t="n">
         <v>508</v>
       </c>
-      <c r="L33" s="143" t="n">
+      <c r="L33" s="149" t="n">
         <v>622</v>
       </c>
-      <c r="M33" s="143" t="n">
+      <c r="M33" s="149" t="n">
         <v>798</v>
       </c>
-      <c r="N33" s="143" t="n">
+      <c r="N33" s="149" t="n">
         <v>780</v>
       </c>
-      <c r="O33" s="143" t="n">
+      <c r="O33" s="149" t="n">
         <v>878</v>
       </c>
-      <c r="P33" s="143" t="n">
+      <c r="P33" s="149" t="n">
         <v>881</v>
       </c>
-      <c r="Q33" s="143" t="n">
+      <c r="Q33" s="149" t="n">
         <v>927</v>
       </c>
-      <c r="R33" s="143" t="n">
+      <c r="R33" s="149" t="n">
         <v>4772</v>
       </c>
-      <c r="S33" s="143" t="n">
+      <c r="S33" s="149" t="n">
         <v>7440</v>
       </c>
-      <c r="T33" s="143" t="n">
+      <c r="T33" s="149" t="n">
         <v>1679</v>
       </c>
-      <c r="U33" s="143" t="n">
+      <c r="U33" s="149" t="n">
         <v>1509</v>
       </c>
-      <c r="V33" s="143" t="n">
+      <c r="V33" s="149" t="n">
         <v>5600</v>
       </c>
-      <c r="W33" s="143" t="n">
+      <c r="W33" s="149" t="n">
         <v>1142</v>
       </c>
-      <c r="X33" s="143" t="n">
+      <c r="X33" s="149" t="n">
         <v>1355</v>
       </c>
-      <c r="Y33" s="143" t="n">
+      <c r="Y33" s="149" t="n">
         <v>1322</v>
       </c>
-      <c r="Z33" s="143" t="n">
+      <c r="Z33" s="149" t="n">
         <v>2037</v>
       </c>
-      <c r="AA33" s="143" t="n"/>
-      <c r="AB33" s="143" t="n"/>
-      <c r="AC33" s="143" t="n"/>
-      <c r="AD33" s="143" t="n"/>
-      <c r="AE33" s="143" t="n"/>
-      <c r="AF33" s="143" t="n"/>
-      <c r="AG33" s="143" t="n"/>
-      <c r="AH33" s="143" t="n"/>
+      <c r="AA33" s="149" t="n">
+        <v>2832</v>
+      </c>
+      <c r="AB33" s="149" t="n"/>
+      <c r="AC33" s="149" t="n"/>
+      <c r="AD33" s="149" t="n"/>
+      <c r="AE33" s="149" t="n"/>
+      <c r="AF33" s="149" t="n"/>
+      <c r="AG33" s="149" t="n"/>
+      <c r="AH33" s="149" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="118">
       <c r="C34" s="142" t="inlineStr">
@@ -6300,79 +6334,81 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D34" s="143" t="n">
+      <c r="D34" s="149" t="n">
         <v>2078</v>
       </c>
-      <c r="E34" s="143" t="n">
+      <c r="E34" s="149" t="n">
         <v>4690</v>
       </c>
-      <c r="F34" s="143" t="n">
+      <c r="F34" s="149" t="n">
         <v>4792</v>
       </c>
-      <c r="G34" s="143" t="n">
+      <c r="G34" s="149" t="n">
         <v>3207</v>
       </c>
-      <c r="H34" s="143" t="n">
+      <c r="H34" s="149" t="n">
         <v>35011184</v>
       </c>
-      <c r="I34" s="143" t="n">
+      <c r="I34" s="149" t="n">
         <v>5630</v>
       </c>
-      <c r="J34" s="143" t="n">
+      <c r="J34" s="149" t="n">
         <v>6900</v>
       </c>
-      <c r="K34" s="143" t="n">
+      <c r="K34" s="149" t="n">
         <v>5000</v>
       </c>
-      <c r="L34" s="143" t="n">
+      <c r="L34" s="149" t="n">
         <v>6746</v>
       </c>
-      <c r="M34" s="143" t="n">
+      <c r="M34" s="149" t="n">
         <v>6346</v>
       </c>
-      <c r="N34" s="143" t="n"/>
-      <c r="O34" s="143" t="n"/>
-      <c r="P34" s="143" t="n">
+      <c r="N34" s="149" t="n"/>
+      <c r="O34" s="149" t="n"/>
+      <c r="P34" s="149" t="n">
         <v>6200</v>
       </c>
-      <c r="Q34" s="143" t="n">
+      <c r="Q34" s="149" t="n">
         <v>7200</v>
       </c>
-      <c r="R34" s="143" t="n">
+      <c r="R34" s="149" t="n">
         <v>14700</v>
       </c>
-      <c r="S34" s="143" t="n">
+      <c r="S34" s="149" t="n">
         <v>13500</v>
       </c>
-      <c r="T34" s="143" t="n">
+      <c r="T34" s="149" t="n">
         <v>9616</v>
       </c>
-      <c r="U34" s="143" t="n">
+      <c r="U34" s="149" t="n">
         <v>8806</v>
       </c>
-      <c r="V34" s="143" t="n">
+      <c r="V34" s="149" t="n">
         <v>1400</v>
       </c>
-      <c r="W34" s="143" t="n">
+      <c r="W34" s="149" t="n">
         <v>6470</v>
       </c>
-      <c r="X34" s="143" t="n">
+      <c r="X34" s="149" t="n">
         <v>8300</v>
       </c>
-      <c r="Y34" s="143" t="n">
+      <c r="Y34" s="149" t="n">
         <v>8311</v>
       </c>
-      <c r="Z34" s="143" t="n">
+      <c r="Z34" s="149" t="n">
         <v>9641</v>
       </c>
-      <c r="AA34" s="143" t="n"/>
-      <c r="AB34" s="143" t="n"/>
-      <c r="AC34" s="143" t="n"/>
-      <c r="AD34" s="143" t="n"/>
-      <c r="AE34" s="143" t="n"/>
-      <c r="AF34" s="143" t="n"/>
-      <c r="AG34" s="143" t="n"/>
-      <c r="AH34" s="143" t="n"/>
+      <c r="AA34" s="149" t="n">
+        <v>10292</v>
+      </c>
+      <c r="AB34" s="149" t="n"/>
+      <c r="AC34" s="149" t="n"/>
+      <c r="AD34" s="149" t="n"/>
+      <c r="AE34" s="149" t="n"/>
+      <c r="AF34" s="149" t="n"/>
+      <c r="AG34" s="149" t="n"/>
+      <c r="AH34" s="149" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="118">
       <c r="C35" s="142" t="inlineStr">
@@ -6380,83 +6416,85 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D35" s="143" t="n">
+      <c r="D35" s="149" t="n">
         <v>1169</v>
       </c>
-      <c r="E35" s="143" t="n">
+      <c r="E35" s="149" t="n">
         <v>2686</v>
       </c>
-      <c r="F35" s="143" t="n">
+      <c r="F35" s="149" t="n">
         <v>2950</v>
       </c>
-      <c r="G35" s="143" t="n">
+      <c r="G35" s="149" t="n">
         <v>1870</v>
       </c>
-      <c r="H35" s="143" t="n">
+      <c r="H35" s="149" t="n">
         <v>6369</v>
       </c>
-      <c r="I35" s="143" t="n">
+      <c r="I35" s="149" t="n">
         <v>2400</v>
       </c>
-      <c r="J35" s="143" t="n">
+      <c r="J35" s="149" t="n">
         <v>2974</v>
       </c>
-      <c r="K35" s="143" t="n">
+      <c r="K35" s="149" t="n">
         <v>2040</v>
       </c>
-      <c r="L35" s="143" t="n">
+      <c r="L35" s="149" t="n">
         <v>2223</v>
       </c>
-      <c r="M35" s="143" t="n">
+      <c r="M35" s="149" t="n">
         <v>2194</v>
       </c>
-      <c r="N35" s="143" t="n">
+      <c r="N35" s="149" t="n">
         <v>1900</v>
       </c>
-      <c r="O35" s="143" t="n">
+      <c r="O35" s="149" t="n">
         <v>2105</v>
       </c>
-      <c r="P35" s="143" t="n">
+      <c r="P35" s="149" t="n">
         <v>2210</v>
       </c>
-      <c r="Q35" s="143" t="n">
+      <c r="Q35" s="149" t="n">
         <v>2580</v>
       </c>
-      <c r="R35" s="143" t="n">
+      <c r="R35" s="149" t="n">
         <v>4570</v>
       </c>
-      <c r="S35" s="143" t="n">
+      <c r="S35" s="149" t="n">
         <v>3310</v>
       </c>
-      <c r="T35" s="143" t="n">
+      <c r="T35" s="149" t="n">
         <v>4520</v>
       </c>
-      <c r="U35" s="143" t="n">
+      <c r="U35" s="149" t="n">
         <v>3481</v>
       </c>
-      <c r="V35" s="143" t="n">
+      <c r="V35" s="149" t="n">
         <v>9298</v>
       </c>
-      <c r="W35" s="143" t="n">
+      <c r="W35" s="149" t="n">
         <v>2838</v>
       </c>
-      <c r="X35" s="143" t="n">
+      <c r="X35" s="149" t="n">
         <v>3700</v>
       </c>
-      <c r="Y35" s="143" t="n">
+      <c r="Y35" s="149" t="n">
         <v>3761</v>
       </c>
-      <c r="Z35" s="143" t="n">
+      <c r="Z35" s="149" t="n">
         <v>4746</v>
       </c>
-      <c r="AA35" s="143" t="n"/>
-      <c r="AB35" s="143" t="n"/>
-      <c r="AC35" s="143" t="n"/>
-      <c r="AD35" s="143" t="n"/>
-      <c r="AE35" s="143" t="n"/>
-      <c r="AF35" s="143" t="n"/>
-      <c r="AG35" s="143" t="n"/>
-      <c r="AH35" s="143" t="n"/>
+      <c r="AA35" s="149" t="n">
+        <v>5042</v>
+      </c>
+      <c r="AB35" s="149" t="n"/>
+      <c r="AC35" s="149" t="n"/>
+      <c r="AD35" s="149" t="n"/>
+      <c r="AE35" s="149" t="n"/>
+      <c r="AF35" s="149" t="n"/>
+      <c r="AG35" s="149" t="n"/>
+      <c r="AH35" s="149" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="118">
       <c r="C36" s="142" t="inlineStr">
@@ -6464,83 +6502,85 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D36" s="143" t="n">
+      <c r="D36" s="149" t="n">
         <v>373</v>
       </c>
-      <c r="E36" s="143" t="n">
+      <c r="E36" s="149" t="n">
         <v>283</v>
       </c>
-      <c r="F36" s="143" t="n">
+      <c r="F36" s="149" t="n">
         <v>541</v>
       </c>
-      <c r="G36" s="143" t="n">
+      <c r="G36" s="149" t="n">
         <v>430</v>
       </c>
-      <c r="H36" s="143" t="n">
+      <c r="H36" s="149" t="n">
         <v>1050</v>
       </c>
-      <c r="I36" s="143" t="n">
+      <c r="I36" s="149" t="n">
         <v>264</v>
       </c>
-      <c r="J36" s="143" t="n">
+      <c r="J36" s="149" t="n">
         <v>209</v>
       </c>
-      <c r="K36" s="143" t="n">
+      <c r="K36" s="149" t="n">
         <v>123</v>
       </c>
-      <c r="L36" s="143" t="n">
+      <c r="L36" s="149" t="n">
         <v>151</v>
       </c>
-      <c r="M36" s="143" t="n">
+      <c r="M36" s="149" t="n">
         <v>228</v>
       </c>
-      <c r="N36" s="143" t="n">
+      <c r="N36" s="149" t="n">
         <v>154</v>
       </c>
-      <c r="O36" s="143" t="n">
+      <c r="O36" s="149" t="n">
         <v>153</v>
       </c>
-      <c r="P36" s="143" t="n">
+      <c r="P36" s="149" t="n">
         <v>166</v>
       </c>
-      <c r="Q36" s="143" t="n">
+      <c r="Q36" s="149" t="n">
         <v>165</v>
       </c>
-      <c r="R36" s="143" t="n">
+      <c r="R36" s="149" t="n">
         <v>328</v>
       </c>
-      <c r="S36" s="143" t="n">
+      <c r="S36" s="149" t="n">
         <v>346</v>
       </c>
-      <c r="T36" s="143" t="n">
+      <c r="T36" s="149" t="n">
         <v>393</v>
       </c>
-      <c r="U36" s="143" t="n">
+      <c r="U36" s="149" t="n">
         <v>500</v>
       </c>
-      <c r="V36" s="143" t="n">
+      <c r="V36" s="149" t="n">
         <v>432</v>
       </c>
-      <c r="W36" s="143" t="n">
+      <c r="W36" s="149" t="n">
         <v>387</v>
       </c>
-      <c r="X36" s="143" t="n">
+      <c r="X36" s="149" t="n">
         <v>472</v>
       </c>
-      <c r="Y36" s="143" t="n">
+      <c r="Y36" s="149" t="n">
         <v>446</v>
       </c>
-      <c r="Z36" s="143" t="n">
+      <c r="Z36" s="149" t="n">
         <v>733</v>
       </c>
-      <c r="AA36" s="143" t="n"/>
-      <c r="AB36" s="143" t="n"/>
-      <c r="AC36" s="143" t="n"/>
-      <c r="AD36" s="143" t="n"/>
-      <c r="AE36" s="143" t="n"/>
-      <c r="AF36" s="143" t="n"/>
-      <c r="AG36" s="143" t="n"/>
-      <c r="AH36" s="143" t="n"/>
+      <c r="AA36" s="149" t="n">
+        <v>586</v>
+      </c>
+      <c r="AB36" s="149" t="n"/>
+      <c r="AC36" s="149" t="n"/>
+      <c r="AD36" s="149" t="n"/>
+      <c r="AE36" s="149" t="n"/>
+      <c r="AF36" s="149" t="n"/>
+      <c r="AG36" s="149" t="n"/>
+      <c r="AH36" s="149" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="118">
       <c r="C37" s="142" t="inlineStr">
@@ -6822,43 +6862,45 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D41" s="143" t="n"/>
-      <c r="E41" s="143" t="n"/>
-      <c r="F41" s="143" t="n"/>
-      <c r="G41" s="143" t="n"/>
-      <c r="H41" s="143" t="n">
+      <c r="D41" s="149" t="n"/>
+      <c r="E41" s="149" t="n"/>
+      <c r="F41" s="149" t="n"/>
+      <c r="G41" s="149" t="n"/>
+      <c r="H41" s="149" t="n">
         <v>16000</v>
       </c>
-      <c r="I41" s="143" t="n"/>
-      <c r="J41" s="143" t="n"/>
-      <c r="K41" s="143" t="n"/>
-      <c r="L41" s="143" t="n"/>
-      <c r="M41" s="143" t="n"/>
-      <c r="N41" s="143" t="n"/>
-      <c r="O41" s="143" t="n"/>
-      <c r="P41" s="143" t="n"/>
-      <c r="Q41" s="143" t="n"/>
-      <c r="R41" s="143" t="n"/>
-      <c r="S41" s="143" t="n"/>
-      <c r="T41" s="143" t="n"/>
-      <c r="U41" s="143" t="n"/>
-      <c r="V41" s="143" t="n"/>
-      <c r="W41" s="143" t="n"/>
-      <c r="X41" s="143" t="n">
+      <c r="I41" s="149" t="n"/>
+      <c r="J41" s="149" t="n"/>
+      <c r="K41" s="149" t="n"/>
+      <c r="L41" s="149" t="n"/>
+      <c r="M41" s="149" t="n"/>
+      <c r="N41" s="149" t="n"/>
+      <c r="O41" s="149" t="n"/>
+      <c r="P41" s="149" t="n"/>
+      <c r="Q41" s="149" t="n"/>
+      <c r="R41" s="149" t="n"/>
+      <c r="S41" s="149" t="n"/>
+      <c r="T41" s="149" t="n"/>
+      <c r="U41" s="149" t="n"/>
+      <c r="V41" s="149" t="n"/>
+      <c r="W41" s="149" t="n"/>
+      <c r="X41" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y41" s="143" t="n">
+      <c r="Y41" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="143" t="n"/>
-      <c r="AA41" s="143" t="n"/>
-      <c r="AB41" s="143" t="n"/>
-      <c r="AC41" s="143" t="n"/>
-      <c r="AD41" s="143" t="n"/>
-      <c r="AE41" s="143" t="n"/>
-      <c r="AF41" s="143" t="n"/>
-      <c r="AG41" s="143" t="n"/>
-      <c r="AH41" s="143" t="n"/>
+      <c r="Z41" s="149" t="n"/>
+      <c r="AA41" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="149" t="n"/>
+      <c r="AC41" s="149" t="n"/>
+      <c r="AD41" s="149" t="n"/>
+      <c r="AE41" s="149" t="n"/>
+      <c r="AF41" s="149" t="n"/>
+      <c r="AG41" s="149" t="n"/>
+      <c r="AH41" s="149" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="118">
       <c r="C42" s="142" t="inlineStr">
@@ -6866,43 +6908,45 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D42" s="143" t="n"/>
-      <c r="E42" s="143" t="n"/>
-      <c r="F42" s="143" t="n"/>
-      <c r="G42" s="143" t="n"/>
-      <c r="H42" s="143" t="n">
+      <c r="D42" s="149" t="n"/>
+      <c r="E42" s="149" t="n"/>
+      <c r="F42" s="149" t="n"/>
+      <c r="G42" s="149" t="n"/>
+      <c r="H42" s="149" t="n">
         <v>300000</v>
       </c>
-      <c r="I42" s="143" t="n"/>
-      <c r="J42" s="143" t="n"/>
-      <c r="K42" s="143" t="n"/>
-      <c r="L42" s="143" t="n"/>
-      <c r="M42" s="143" t="n"/>
-      <c r="N42" s="143" t="n"/>
-      <c r="O42" s="143" t="n"/>
-      <c r="P42" s="143" t="n"/>
-      <c r="Q42" s="143" t="n"/>
-      <c r="R42" s="143" t="n"/>
-      <c r="S42" s="143" t="n"/>
-      <c r="T42" s="143" t="n"/>
-      <c r="U42" s="143" t="n"/>
-      <c r="V42" s="143" t="n"/>
-      <c r="W42" s="143" t="n"/>
-      <c r="X42" s="143" t="n">
+      <c r="I42" s="149" t="n"/>
+      <c r="J42" s="149" t="n"/>
+      <c r="K42" s="149" t="n"/>
+      <c r="L42" s="149" t="n"/>
+      <c r="M42" s="149" t="n"/>
+      <c r="N42" s="149" t="n"/>
+      <c r="O42" s="149" t="n"/>
+      <c r="P42" s="149" t="n"/>
+      <c r="Q42" s="149" t="n"/>
+      <c r="R42" s="149" t="n"/>
+      <c r="S42" s="149" t="n"/>
+      <c r="T42" s="149" t="n"/>
+      <c r="U42" s="149" t="n"/>
+      <c r="V42" s="149" t="n"/>
+      <c r="W42" s="149" t="n"/>
+      <c r="X42" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y42" s="143" t="n">
+      <c r="Y42" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="143" t="n"/>
-      <c r="AA42" s="143" t="n"/>
-      <c r="AB42" s="143" t="n"/>
-      <c r="AC42" s="143" t="n"/>
-      <c r="AD42" s="143" t="n"/>
-      <c r="AE42" s="143" t="n"/>
-      <c r="AF42" s="143" t="n"/>
-      <c r="AG42" s="143" t="n"/>
-      <c r="AH42" s="143" t="n"/>
+      <c r="Z42" s="149" t="n"/>
+      <c r="AA42" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="149" t="n"/>
+      <c r="AC42" s="149" t="n"/>
+      <c r="AD42" s="149" t="n"/>
+      <c r="AE42" s="149" t="n"/>
+      <c r="AF42" s="149" t="n"/>
+      <c r="AG42" s="149" t="n"/>
+      <c r="AH42" s="149" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="118">
       <c r="C43" s="142" t="inlineStr">
@@ -6910,41 +6954,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D43" s="143" t="n"/>
-      <c r="E43" s="143" t="n"/>
-      <c r="F43" s="143" t="n"/>
-      <c r="G43" s="143" t="n"/>
-      <c r="H43" s="143" t="n"/>
-      <c r="I43" s="143" t="n"/>
-      <c r="J43" s="143" t="n"/>
-      <c r="K43" s="143" t="n"/>
-      <c r="L43" s="143" t="n"/>
-      <c r="M43" s="143" t="n"/>
-      <c r="N43" s="143" t="n"/>
-      <c r="O43" s="143" t="n"/>
-      <c r="P43" s="143" t="n"/>
-      <c r="Q43" s="143" t="n"/>
-      <c r="R43" s="143" t="n"/>
-      <c r="S43" s="143" t="n"/>
-      <c r="T43" s="143" t="n"/>
-      <c r="U43" s="143" t="n"/>
-      <c r="V43" s="143" t="n"/>
-      <c r="W43" s="143" t="n"/>
-      <c r="X43" s="143" t="n">
+      <c r="D43" s="149" t="n"/>
+      <c r="E43" s="149" t="n"/>
+      <c r="F43" s="149" t="n"/>
+      <c r="G43" s="149" t="n"/>
+      <c r="H43" s="149" t="n"/>
+      <c r="I43" s="149" t="n"/>
+      <c r="J43" s="149" t="n"/>
+      <c r="K43" s="149" t="n"/>
+      <c r="L43" s="149" t="n"/>
+      <c r="M43" s="149" t="n"/>
+      <c r="N43" s="149" t="n"/>
+      <c r="O43" s="149" t="n"/>
+      <c r="P43" s="149" t="n"/>
+      <c r="Q43" s="149" t="n"/>
+      <c r="R43" s="149" t="n"/>
+      <c r="S43" s="149" t="n"/>
+      <c r="T43" s="149" t="n"/>
+      <c r="U43" s="149" t="n"/>
+      <c r="V43" s="149" t="n"/>
+      <c r="W43" s="149" t="n"/>
+      <c r="X43" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y43" s="143" t="n">
+      <c r="Y43" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="143" t="n"/>
-      <c r="AA43" s="143" t="n"/>
-      <c r="AB43" s="143" t="n"/>
-      <c r="AC43" s="143" t="n"/>
-      <c r="AD43" s="143" t="n"/>
-      <c r="AE43" s="143" t="n"/>
-      <c r="AF43" s="143" t="n"/>
-      <c r="AG43" s="143" t="n"/>
-      <c r="AH43" s="143" t="n"/>
+      <c r="Z43" s="149" t="n"/>
+      <c r="AA43" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="149" t="n"/>
+      <c r="AC43" s="149" t="n"/>
+      <c r="AD43" s="149" t="n"/>
+      <c r="AE43" s="149" t="n"/>
+      <c r="AF43" s="149" t="n"/>
+      <c r="AG43" s="149" t="n"/>
+      <c r="AH43" s="149" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="118">
       <c r="C44" s="142" t="inlineStr">
@@ -6952,41 +6998,43 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D44" s="143" t="n"/>
-      <c r="E44" s="143" t="n"/>
-      <c r="F44" s="143" t="n"/>
-      <c r="G44" s="143" t="n"/>
-      <c r="H44" s="143" t="n"/>
-      <c r="I44" s="143" t="n"/>
-      <c r="J44" s="143" t="n"/>
-      <c r="K44" s="143" t="n"/>
-      <c r="L44" s="143" t="n"/>
-      <c r="M44" s="143" t="n"/>
-      <c r="N44" s="143" t="n"/>
-      <c r="O44" s="143" t="n"/>
-      <c r="P44" s="143" t="n"/>
-      <c r="Q44" s="143" t="n"/>
-      <c r="R44" s="143" t="n"/>
-      <c r="S44" s="143" t="n"/>
-      <c r="T44" s="143" t="n"/>
-      <c r="U44" s="143" t="n"/>
-      <c r="V44" s="143" t="n"/>
-      <c r="W44" s="143" t="n"/>
-      <c r="X44" s="143" t="n">
+      <c r="D44" s="149" t="n"/>
+      <c r="E44" s="149" t="n"/>
+      <c r="F44" s="149" t="n"/>
+      <c r="G44" s="149" t="n"/>
+      <c r="H44" s="149" t="n"/>
+      <c r="I44" s="149" t="n"/>
+      <c r="J44" s="149" t="n"/>
+      <c r="K44" s="149" t="n"/>
+      <c r="L44" s="149" t="n"/>
+      <c r="M44" s="149" t="n"/>
+      <c r="N44" s="149" t="n"/>
+      <c r="O44" s="149" t="n"/>
+      <c r="P44" s="149" t="n"/>
+      <c r="Q44" s="149" t="n"/>
+      <c r="R44" s="149" t="n"/>
+      <c r="S44" s="149" t="n"/>
+      <c r="T44" s="149" t="n"/>
+      <c r="U44" s="149" t="n"/>
+      <c r="V44" s="149" t="n"/>
+      <c r="W44" s="149" t="n"/>
+      <c r="X44" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y44" s="143" t="n">
+      <c r="Y44" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="143" t="n"/>
-      <c r="AA44" s="143" t="n"/>
-      <c r="AB44" s="143" t="n"/>
-      <c r="AC44" s="143" t="n"/>
-      <c r="AD44" s="143" t="n"/>
-      <c r="AE44" s="143" t="n"/>
-      <c r="AF44" s="143" t="n"/>
-      <c r="AG44" s="143" t="n"/>
-      <c r="AH44" s="143" t="n"/>
+      <c r="Z44" s="149" t="n"/>
+      <c r="AA44" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="149" t="n"/>
+      <c r="AC44" s="149" t="n"/>
+      <c r="AD44" s="149" t="n"/>
+      <c r="AE44" s="149" t="n"/>
+      <c r="AF44" s="149" t="n"/>
+      <c r="AG44" s="149" t="n"/>
+      <c r="AH44" s="149" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="118">
       <c r="C45" s="142" t="inlineStr">
@@ -7261,65 +7309,67 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D48" s="143" t="n">
+      <c r="D48" s="149" t="n">
         <v>2640</v>
       </c>
-      <c r="E48" s="143" t="n"/>
-      <c r="F48" s="143" t="n"/>
-      <c r="G48" s="143" t="n">
+      <c r="E48" s="149" t="n"/>
+      <c r="F48" s="149" t="n"/>
+      <c r="G48" s="149" t="n">
         <v>4800</v>
       </c>
-      <c r="H48" s="143" t="n">
+      <c r="H48" s="149" t="n">
         <v>13200</v>
       </c>
-      <c r="I48" s="143" t="n"/>
-      <c r="J48" s="143" t="n">
+      <c r="I48" s="149" t="n"/>
+      <c r="J48" s="149" t="n">
         <v>1000</v>
       </c>
-      <c r="K48" s="143" t="n">
+      <c r="K48" s="149" t="n">
         <v>1200</v>
       </c>
-      <c r="L48" s="143" t="n">
+      <c r="L48" s="149" t="n">
         <v>352</v>
       </c>
-      <c r="M48" s="143" t="n"/>
-      <c r="N48" s="143" t="n"/>
-      <c r="O48" s="143" t="n"/>
-      <c r="P48" s="143" t="n"/>
-      <c r="Q48" s="143" t="n"/>
-      <c r="R48" s="143" t="n"/>
-      <c r="S48" s="143" t="n">
+      <c r="M48" s="149" t="n"/>
+      <c r="N48" s="149" t="n"/>
+      <c r="O48" s="149" t="n"/>
+      <c r="P48" s="149" t="n"/>
+      <c r="Q48" s="149" t="n"/>
+      <c r="R48" s="149" t="n"/>
+      <c r="S48" s="149" t="n">
         <v>30000</v>
       </c>
-      <c r="T48" s="143" t="n">
+      <c r="T48" s="149" t="n">
         <v>96000</v>
       </c>
-      <c r="U48" s="143" t="n">
+      <c r="U48" s="149" t="n">
         <v>118500</v>
       </c>
-      <c r="V48" s="143" t="n">
+      <c r="V48" s="149" t="n">
         <v>102000</v>
       </c>
-      <c r="W48" s="143" t="n">
+      <c r="W48" s="149" t="n">
         <v>112500</v>
       </c>
-      <c r="X48" s="143" t="n">
+      <c r="X48" s="149" t="n">
         <v>103000</v>
       </c>
-      <c r="Y48" s="143" t="n">
+      <c r="Y48" s="149" t="n">
         <v>98500</v>
       </c>
-      <c r="Z48" s="143" t="n">
+      <c r="Z48" s="149" t="n">
         <v>167000</v>
       </c>
-      <c r="AA48" s="143" t="n"/>
-      <c r="AB48" s="143" t="n"/>
-      <c r="AC48" s="143" t="n"/>
-      <c r="AD48" s="143" t="n"/>
-      <c r="AE48" s="143" t="n"/>
-      <c r="AF48" s="143" t="n"/>
-      <c r="AG48" s="143" t="n"/>
-      <c r="AH48" s="143" t="n"/>
+      <c r="AA48" s="149" t="n">
+        <v>144500</v>
+      </c>
+      <c r="AB48" s="149" t="n"/>
+      <c r="AC48" s="149" t="n"/>
+      <c r="AD48" s="149" t="n"/>
+      <c r="AE48" s="149" t="n"/>
+      <c r="AF48" s="149" t="n"/>
+      <c r="AG48" s="149" t="n"/>
+      <c r="AH48" s="149" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="118">
       <c r="C49" s="142" t="inlineStr">
@@ -7327,47 +7377,49 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D49" s="143" t="inlineStr">
+      <c r="D49" s="149" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E49" s="143" t="n"/>
-      <c r="F49" s="143" t="n"/>
-      <c r="G49" s="143" t="n"/>
-      <c r="H49" s="143" t="n"/>
-      <c r="I49" s="143" t="n"/>
-      <c r="J49" s="143" t="n"/>
-      <c r="K49" s="143" t="n">
+      <c r="E49" s="149" t="n"/>
+      <c r="F49" s="149" t="n"/>
+      <c r="G49" s="149" t="n"/>
+      <c r="H49" s="149" t="n"/>
+      <c r="I49" s="149" t="n"/>
+      <c r="J49" s="149" t="n"/>
+      <c r="K49" s="149" t="n">
         <v>2000</v>
       </c>
-      <c r="L49" s="143" t="n"/>
-      <c r="M49" s="143" t="n"/>
-      <c r="N49" s="143" t="n"/>
-      <c r="O49" s="143" t="n"/>
-      <c r="P49" s="143" t="n"/>
-      <c r="Q49" s="143" t="n"/>
-      <c r="R49" s="143" t="n"/>
-      <c r="S49" s="143" t="n"/>
-      <c r="T49" s="143" t="n"/>
-      <c r="U49" s="143" t="n"/>
-      <c r="V49" s="143" t="n"/>
-      <c r="W49" s="143" t="n"/>
-      <c r="X49" s="143" t="n">
+      <c r="L49" s="149" t="n"/>
+      <c r="M49" s="149" t="n"/>
+      <c r="N49" s="149" t="n"/>
+      <c r="O49" s="149" t="n"/>
+      <c r="P49" s="149" t="n"/>
+      <c r="Q49" s="149" t="n"/>
+      <c r="R49" s="149" t="n"/>
+      <c r="S49" s="149" t="n"/>
+      <c r="T49" s="149" t="n"/>
+      <c r="U49" s="149" t="n"/>
+      <c r="V49" s="149" t="n"/>
+      <c r="W49" s="149" t="n"/>
+      <c r="X49" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y49" s="143" t="n">
+      <c r="Y49" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="143" t="n"/>
-      <c r="AA49" s="143" t="n"/>
-      <c r="AB49" s="143" t="n"/>
-      <c r="AC49" s="143" t="n"/>
-      <c r="AD49" s="143" t="n"/>
-      <c r="AE49" s="143" t="n"/>
-      <c r="AF49" s="143" t="n"/>
-      <c r="AG49" s="143" t="n"/>
-      <c r="AH49" s="143" t="n"/>
+      <c r="Z49" s="149" t="n"/>
+      <c r="AA49" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="149" t="n"/>
+      <c r="AC49" s="149" t="n"/>
+      <c r="AD49" s="149" t="n"/>
+      <c r="AE49" s="149" t="n"/>
+      <c r="AF49" s="149" t="n"/>
+      <c r="AG49" s="149" t="n"/>
+      <c r="AH49" s="149" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="118">
       <c r="C50" s="142" t="inlineStr">
@@ -7375,63 +7427,65 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D50" s="143" t="n">
+      <c r="D50" s="149" t="n">
         <v>511</v>
       </c>
-      <c r="E50" s="143" t="n"/>
-      <c r="F50" s="143" t="n"/>
-      <c r="G50" s="143" t="n">
+      <c r="E50" s="149" t="n"/>
+      <c r="F50" s="149" t="n"/>
+      <c r="G50" s="149" t="n">
         <v>909</v>
       </c>
-      <c r="H50" s="143" t="n">
+      <c r="H50" s="149" t="n">
         <v>2476</v>
       </c>
-      <c r="I50" s="143" t="n"/>
-      <c r="J50" s="143" t="n">
+      <c r="I50" s="149" t="n"/>
+      <c r="J50" s="149" t="n">
         <v>119</v>
       </c>
-      <c r="K50" s="143" t="n">
+      <c r="K50" s="149" t="n">
         <v>119</v>
       </c>
-      <c r="L50" s="143" t="n"/>
-      <c r="M50" s="143" t="n"/>
-      <c r="N50" s="143" t="n"/>
-      <c r="O50" s="143" t="n"/>
-      <c r="P50" s="143" t="n"/>
-      <c r="Q50" s="143" t="n"/>
-      <c r="R50" s="143" t="n"/>
-      <c r="S50" s="143" t="n">
+      <c r="L50" s="149" t="n"/>
+      <c r="M50" s="149" t="n"/>
+      <c r="N50" s="149" t="n"/>
+      <c r="O50" s="149" t="n"/>
+      <c r="P50" s="149" t="n"/>
+      <c r="Q50" s="149" t="n"/>
+      <c r="R50" s="149" t="n"/>
+      <c r="S50" s="149" t="n">
         <v>2392</v>
       </c>
-      <c r="T50" s="143" t="n">
+      <c r="T50" s="149" t="n">
         <v>4629</v>
       </c>
-      <c r="U50" s="143" t="n">
+      <c r="U50" s="149" t="n">
         <v>2779</v>
       </c>
-      <c r="V50" s="143" t="n">
+      <c r="V50" s="149" t="n">
         <v>2341</v>
       </c>
-      <c r="W50" s="143" t="n">
+      <c r="W50" s="149" t="n">
         <v>2780</v>
       </c>
-      <c r="X50" s="143" t="n">
+      <c r="X50" s="149" t="n">
         <v>1678</v>
       </c>
-      <c r="Y50" s="143" t="n">
+      <c r="Y50" s="149" t="n">
         <v>2225</v>
       </c>
-      <c r="Z50" s="143" t="n">
+      <c r="Z50" s="149" t="n">
         <v>4278</v>
       </c>
-      <c r="AA50" s="143" t="n"/>
-      <c r="AB50" s="143" t="n"/>
-      <c r="AC50" s="143" t="n"/>
-      <c r="AD50" s="143" t="n"/>
-      <c r="AE50" s="143" t="n"/>
-      <c r="AF50" s="143" t="n"/>
-      <c r="AG50" s="143" t="n"/>
-      <c r="AH50" s="143" t="n"/>
+      <c r="AA50" s="149" t="n">
+        <v>3435</v>
+      </c>
+      <c r="AB50" s="149" t="n"/>
+      <c r="AC50" s="149" t="n"/>
+      <c r="AD50" s="149" t="n"/>
+      <c r="AE50" s="149" t="n"/>
+      <c r="AF50" s="149" t="n"/>
+      <c r="AG50" s="149" t="n"/>
+      <c r="AH50" s="149" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="118">
       <c r="C51" s="142" t="inlineStr">
@@ -7439,65 +7493,67 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D51" s="143" t="n">
+      <c r="D51" s="149" t="n">
         <v>22</v>
       </c>
-      <c r="E51" s="143" t="n"/>
-      <c r="F51" s="143" t="n"/>
-      <c r="G51" s="143" t="n">
+      <c r="E51" s="149" t="n"/>
+      <c r="F51" s="149" t="n"/>
+      <c r="G51" s="149" t="n">
         <v>40</v>
       </c>
-      <c r="H51" s="143" t="n">
+      <c r="H51" s="149" t="n">
         <v>66</v>
       </c>
-      <c r="I51" s="143" t="n"/>
-      <c r="J51" s="143" t="n">
+      <c r="I51" s="149" t="n"/>
+      <c r="J51" s="149" t="n">
         <v>7</v>
       </c>
-      <c r="K51" s="143" t="n">
+      <c r="K51" s="149" t="n">
         <v>6</v>
       </c>
-      <c r="L51" s="143" t="n">
+      <c r="L51" s="149" t="n">
         <v>17</v>
       </c>
-      <c r="M51" s="143" t="n"/>
-      <c r="N51" s="143" t="n"/>
-      <c r="O51" s="143" t="n"/>
-      <c r="P51" s="143" t="n"/>
-      <c r="Q51" s="143" t="n"/>
-      <c r="R51" s="143" t="n"/>
-      <c r="S51" s="143" t="n">
+      <c r="M51" s="149" t="n"/>
+      <c r="N51" s="149" t="n"/>
+      <c r="O51" s="149" t="n"/>
+      <c r="P51" s="149" t="n"/>
+      <c r="Q51" s="149" t="n"/>
+      <c r="R51" s="149" t="n"/>
+      <c r="S51" s="149" t="n">
         <v>60</v>
       </c>
-      <c r="T51" s="143" t="n">
+      <c r="T51" s="149" t="n">
         <v>192</v>
       </c>
-      <c r="U51" s="143" t="n">
+      <c r="U51" s="149" t="n">
         <v>237</v>
       </c>
-      <c r="V51" s="143" t="n">
+      <c r="V51" s="149" t="n">
         <v>204</v>
       </c>
-      <c r="W51" s="143" t="n">
+      <c r="W51" s="149" t="n">
         <v>225</v>
       </c>
-      <c r="X51" s="143" t="n">
+      <c r="X51" s="149" t="n">
         <v>206</v>
       </c>
-      <c r="Y51" s="143" t="n">
+      <c r="Y51" s="149" t="n">
         <v>197</v>
       </c>
-      <c r="Z51" s="143" t="n">
+      <c r="Z51" s="149" t="n">
         <v>334</v>
       </c>
-      <c r="AA51" s="143" t="n"/>
-      <c r="AB51" s="143" t="n"/>
-      <c r="AC51" s="143" t="n"/>
-      <c r="AD51" s="143" t="n"/>
-      <c r="AE51" s="143" t="n"/>
-      <c r="AF51" s="143" t="n"/>
-      <c r="AG51" s="143" t="n"/>
-      <c r="AH51" s="143" t="n"/>
+      <c r="AA51" s="149" t="n">
+        <v>289</v>
+      </c>
+      <c r="AB51" s="149" t="n"/>
+      <c r="AC51" s="149" t="n"/>
+      <c r="AD51" s="149" t="n"/>
+      <c r="AE51" s="149" t="n"/>
+      <c r="AF51" s="149" t="n"/>
+      <c r="AG51" s="149" t="n"/>
+      <c r="AH51" s="149" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="118">
       <c r="C52" s="142" t="inlineStr">
@@ -7779,41 +7835,43 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D56" s="143" t="n"/>
-      <c r="E56" s="143" t="n"/>
-      <c r="F56" s="143" t="n"/>
-      <c r="G56" s="143" t="n"/>
-      <c r="H56" s="143" t="n"/>
-      <c r="I56" s="143" t="n"/>
-      <c r="J56" s="143" t="n"/>
-      <c r="K56" s="143" t="n"/>
-      <c r="L56" s="143" t="n"/>
-      <c r="M56" s="143" t="n"/>
-      <c r="N56" s="143" t="n"/>
-      <c r="O56" s="143" t="n"/>
-      <c r="P56" s="143" t="n"/>
-      <c r="Q56" s="143" t="n"/>
-      <c r="R56" s="143" t="n"/>
-      <c r="S56" s="143" t="n"/>
-      <c r="T56" s="143" t="n"/>
-      <c r="U56" s="143" t="n"/>
-      <c r="V56" s="143" t="n"/>
-      <c r="W56" s="143" t="n"/>
-      <c r="X56" s="143" t="n">
+      <c r="D56" s="149" t="n"/>
+      <c r="E56" s="149" t="n"/>
+      <c r="F56" s="149" t="n"/>
+      <c r="G56" s="149" t="n"/>
+      <c r="H56" s="149" t="n"/>
+      <c r="I56" s="149" t="n"/>
+      <c r="J56" s="149" t="n"/>
+      <c r="K56" s="149" t="n"/>
+      <c r="L56" s="149" t="n"/>
+      <c r="M56" s="149" t="n"/>
+      <c r="N56" s="149" t="n"/>
+      <c r="O56" s="149" t="n"/>
+      <c r="P56" s="149" t="n"/>
+      <c r="Q56" s="149" t="n"/>
+      <c r="R56" s="149" t="n"/>
+      <c r="S56" s="149" t="n"/>
+      <c r="T56" s="149" t="n"/>
+      <c r="U56" s="149" t="n"/>
+      <c r="V56" s="149" t="n"/>
+      <c r="W56" s="149" t="n"/>
+      <c r="X56" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y56" s="143" t="n">
+      <c r="Y56" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="143" t="n"/>
-      <c r="AA56" s="143" t="n"/>
-      <c r="AB56" s="143" t="n"/>
-      <c r="AC56" s="143" t="n"/>
-      <c r="AD56" s="143" t="n"/>
-      <c r="AE56" s="143" t="n"/>
-      <c r="AF56" s="143" t="n"/>
-      <c r="AG56" s="143" t="n"/>
-      <c r="AH56" s="143" t="n"/>
+      <c r="Z56" s="149" t="n"/>
+      <c r="AA56" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="149" t="n"/>
+      <c r="AC56" s="149" t="n"/>
+      <c r="AD56" s="149" t="n"/>
+      <c r="AE56" s="149" t="n"/>
+      <c r="AF56" s="149" t="n"/>
+      <c r="AG56" s="149" t="n"/>
+      <c r="AH56" s="149" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="118">
       <c r="C57" s="142" t="inlineStr">
@@ -7821,41 +7879,43 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D57" s="143" t="n"/>
-      <c r="E57" s="143" t="n"/>
-      <c r="F57" s="143" t="n"/>
-      <c r="G57" s="143" t="n"/>
-      <c r="H57" s="143" t="n"/>
-      <c r="I57" s="143" t="n"/>
-      <c r="J57" s="143" t="n"/>
-      <c r="K57" s="143" t="n"/>
-      <c r="L57" s="143" t="n"/>
-      <c r="M57" s="143" t="n"/>
-      <c r="N57" s="143" t="n"/>
-      <c r="O57" s="143" t="n"/>
-      <c r="P57" s="143" t="n"/>
-      <c r="Q57" s="143" t="n"/>
-      <c r="R57" s="143" t="n"/>
-      <c r="S57" s="143" t="n"/>
-      <c r="T57" s="143" t="n"/>
-      <c r="U57" s="143" t="n"/>
-      <c r="V57" s="143" t="n"/>
-      <c r="W57" s="143" t="n"/>
-      <c r="X57" s="143" t="n">
+      <c r="D57" s="149" t="n"/>
+      <c r="E57" s="149" t="n"/>
+      <c r="F57" s="149" t="n"/>
+      <c r="G57" s="149" t="n"/>
+      <c r="H57" s="149" t="n"/>
+      <c r="I57" s="149" t="n"/>
+      <c r="J57" s="149" t="n"/>
+      <c r="K57" s="149" t="n"/>
+      <c r="L57" s="149" t="n"/>
+      <c r="M57" s="149" t="n"/>
+      <c r="N57" s="149" t="n"/>
+      <c r="O57" s="149" t="n"/>
+      <c r="P57" s="149" t="n"/>
+      <c r="Q57" s="149" t="n"/>
+      <c r="R57" s="149" t="n"/>
+      <c r="S57" s="149" t="n"/>
+      <c r="T57" s="149" t="n"/>
+      <c r="U57" s="149" t="n"/>
+      <c r="V57" s="149" t="n"/>
+      <c r="W57" s="149" t="n"/>
+      <c r="X57" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y57" s="143" t="n">
+      <c r="Y57" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="143" t="n"/>
-      <c r="AA57" s="143" t="n"/>
-      <c r="AB57" s="143" t="n"/>
-      <c r="AC57" s="143" t="n"/>
-      <c r="AD57" s="143" t="n"/>
-      <c r="AE57" s="143" t="n"/>
-      <c r="AF57" s="143" t="n"/>
-      <c r="AG57" s="143" t="n"/>
-      <c r="AH57" s="143" t="n"/>
+      <c r="Z57" s="149" t="n"/>
+      <c r="AA57" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="149" t="n"/>
+      <c r="AC57" s="149" t="n"/>
+      <c r="AD57" s="149" t="n"/>
+      <c r="AE57" s="149" t="n"/>
+      <c r="AF57" s="149" t="n"/>
+      <c r="AG57" s="149" t="n"/>
+      <c r="AH57" s="149" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="118">
       <c r="C58" s="142" t="inlineStr">
@@ -7863,41 +7923,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D58" s="143" t="n"/>
-      <c r="E58" s="143" t="n"/>
-      <c r="F58" s="143" t="n"/>
-      <c r="G58" s="143" t="n"/>
-      <c r="H58" s="143" t="n"/>
-      <c r="I58" s="143" t="n"/>
-      <c r="J58" s="143" t="n"/>
-      <c r="K58" s="143" t="n"/>
-      <c r="L58" s="143" t="n"/>
-      <c r="M58" s="143" t="n"/>
-      <c r="N58" s="143" t="n"/>
-      <c r="O58" s="143" t="n"/>
-      <c r="P58" s="143" t="n"/>
-      <c r="Q58" s="143" t="n"/>
-      <c r="R58" s="143" t="n"/>
-      <c r="S58" s="143" t="n"/>
-      <c r="T58" s="143" t="n"/>
-      <c r="U58" s="143" t="n"/>
-      <c r="V58" s="143" t="n"/>
-      <c r="W58" s="143" t="n"/>
-      <c r="X58" s="143" t="n">
+      <c r="D58" s="149" t="n"/>
+      <c r="E58" s="149" t="n"/>
+      <c r="F58" s="149" t="n"/>
+      <c r="G58" s="149" t="n"/>
+      <c r="H58" s="149" t="n"/>
+      <c r="I58" s="149" t="n"/>
+      <c r="J58" s="149" t="n"/>
+      <c r="K58" s="149" t="n"/>
+      <c r="L58" s="149" t="n"/>
+      <c r="M58" s="149" t="n"/>
+      <c r="N58" s="149" t="n"/>
+      <c r="O58" s="149" t="n"/>
+      <c r="P58" s="149" t="n"/>
+      <c r="Q58" s="149" t="n"/>
+      <c r="R58" s="149" t="n"/>
+      <c r="S58" s="149" t="n"/>
+      <c r="T58" s="149" t="n"/>
+      <c r="U58" s="149" t="n"/>
+      <c r="V58" s="149" t="n"/>
+      <c r="W58" s="149" t="n"/>
+      <c r="X58" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y58" s="143" t="n">
+      <c r="Y58" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="143" t="n"/>
-      <c r="AA58" s="143" t="n"/>
-      <c r="AB58" s="143" t="n"/>
-      <c r="AC58" s="143" t="n"/>
-      <c r="AD58" s="143" t="n"/>
-      <c r="AE58" s="143" t="n"/>
-      <c r="AF58" s="143" t="n"/>
-      <c r="AG58" s="143" t="n"/>
-      <c r="AH58" s="143" t="n"/>
+      <c r="Z58" s="149" t="n"/>
+      <c r="AA58" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="149" t="n"/>
+      <c r="AC58" s="149" t="n"/>
+      <c r="AD58" s="149" t="n"/>
+      <c r="AE58" s="149" t="n"/>
+      <c r="AF58" s="149" t="n"/>
+      <c r="AG58" s="149" t="n"/>
+      <c r="AH58" s="149" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="118">
       <c r="C59" s="142" t="inlineStr">
@@ -7905,41 +7967,43 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D59" s="143" t="n"/>
-      <c r="E59" s="143" t="n"/>
-      <c r="F59" s="143" t="n"/>
-      <c r="G59" s="143" t="n"/>
-      <c r="H59" s="143" t="n"/>
-      <c r="I59" s="143" t="n"/>
-      <c r="J59" s="143" t="n"/>
-      <c r="K59" s="143" t="n"/>
-      <c r="L59" s="143" t="n"/>
-      <c r="M59" s="143" t="n"/>
-      <c r="N59" s="143" t="n"/>
-      <c r="O59" s="143" t="n"/>
-      <c r="P59" s="143" t="n"/>
-      <c r="Q59" s="143" t="n"/>
-      <c r="R59" s="143" t="n"/>
-      <c r="S59" s="143" t="n"/>
-      <c r="T59" s="143" t="n"/>
-      <c r="U59" s="143" t="n"/>
-      <c r="V59" s="143" t="n"/>
-      <c r="W59" s="143" t="n"/>
-      <c r="X59" s="143" t="n">
+      <c r="D59" s="149" t="n"/>
+      <c r="E59" s="149" t="n"/>
+      <c r="F59" s="149" t="n"/>
+      <c r="G59" s="149" t="n"/>
+      <c r="H59" s="149" t="n"/>
+      <c r="I59" s="149" t="n"/>
+      <c r="J59" s="149" t="n"/>
+      <c r="K59" s="149" t="n"/>
+      <c r="L59" s="149" t="n"/>
+      <c r="M59" s="149" t="n"/>
+      <c r="N59" s="149" t="n"/>
+      <c r="O59" s="149" t="n"/>
+      <c r="P59" s="149" t="n"/>
+      <c r="Q59" s="149" t="n"/>
+      <c r="R59" s="149" t="n"/>
+      <c r="S59" s="149" t="n"/>
+      <c r="T59" s="149" t="n"/>
+      <c r="U59" s="149" t="n"/>
+      <c r="V59" s="149" t="n"/>
+      <c r="W59" s="149" t="n"/>
+      <c r="X59" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" s="143" t="n">
+      <c r="Y59" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="143" t="n"/>
-      <c r="AA59" s="143" t="n"/>
-      <c r="AB59" s="143" t="n"/>
-      <c r="AC59" s="143" t="n"/>
-      <c r="AD59" s="143" t="n"/>
-      <c r="AE59" s="143" t="n"/>
-      <c r="AF59" s="143" t="n"/>
-      <c r="AG59" s="143" t="n"/>
-      <c r="AH59" s="143" t="n"/>
+      <c r="Z59" s="149" t="n"/>
+      <c r="AA59" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="149" t="n"/>
+      <c r="AC59" s="149" t="n"/>
+      <c r="AD59" s="149" t="n"/>
+      <c r="AE59" s="149" t="n"/>
+      <c r="AF59" s="149" t="n"/>
+      <c r="AG59" s="149" t="n"/>
+      <c r="AH59" s="149" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="118">
       <c r="C60" s="142" t="inlineStr">
@@ -8214,41 +8278,43 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D63" s="143" t="n"/>
-      <c r="E63" s="143" t="n"/>
-      <c r="F63" s="143" t="n"/>
-      <c r="G63" s="143" t="n"/>
-      <c r="H63" s="143" t="n"/>
-      <c r="I63" s="143" t="n"/>
-      <c r="J63" s="143" t="n"/>
-      <c r="K63" s="143" t="n"/>
-      <c r="L63" s="143" t="n"/>
-      <c r="M63" s="143" t="n"/>
-      <c r="N63" s="143" t="n"/>
-      <c r="O63" s="143" t="n"/>
-      <c r="P63" s="143" t="n"/>
-      <c r="Q63" s="143" t="n"/>
-      <c r="R63" s="143" t="n"/>
-      <c r="S63" s="143" t="n"/>
-      <c r="T63" s="143" t="n"/>
-      <c r="U63" s="143" t="n"/>
-      <c r="V63" s="143" t="n"/>
-      <c r="W63" s="143" t="n"/>
-      <c r="X63" s="143" t="n">
+      <c r="D63" s="149" t="n"/>
+      <c r="E63" s="149" t="n"/>
+      <c r="F63" s="149" t="n"/>
+      <c r="G63" s="149" t="n"/>
+      <c r="H63" s="149" t="n"/>
+      <c r="I63" s="149" t="n"/>
+      <c r="J63" s="149" t="n"/>
+      <c r="K63" s="149" t="n"/>
+      <c r="L63" s="149" t="n"/>
+      <c r="M63" s="149" t="n"/>
+      <c r="N63" s="149" t="n"/>
+      <c r="O63" s="149" t="n"/>
+      <c r="P63" s="149" t="n"/>
+      <c r="Q63" s="149" t="n"/>
+      <c r="R63" s="149" t="n"/>
+      <c r="S63" s="149" t="n"/>
+      <c r="T63" s="149" t="n"/>
+      <c r="U63" s="149" t="n"/>
+      <c r="V63" s="149" t="n"/>
+      <c r="W63" s="149" t="n"/>
+      <c r="X63" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y63" s="143" t="n">
+      <c r="Y63" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="143" t="n"/>
-      <c r="AA63" s="143" t="n"/>
-      <c r="AB63" s="143" t="n"/>
-      <c r="AC63" s="143" t="n"/>
-      <c r="AD63" s="143" t="n"/>
-      <c r="AE63" s="143" t="n"/>
-      <c r="AF63" s="143" t="n"/>
-      <c r="AG63" s="143" t="n"/>
-      <c r="AH63" s="143" t="n"/>
+      <c r="Z63" s="149" t="n"/>
+      <c r="AA63" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="149" t="n"/>
+      <c r="AC63" s="149" t="n"/>
+      <c r="AD63" s="149" t="n"/>
+      <c r="AE63" s="149" t="n"/>
+      <c r="AF63" s="149" t="n"/>
+      <c r="AG63" s="149" t="n"/>
+      <c r="AH63" s="149" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="118">
       <c r="C64" s="142" t="inlineStr">
@@ -8256,41 +8322,43 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D64" s="143" t="n"/>
-      <c r="E64" s="143" t="n"/>
-      <c r="F64" s="143" t="n"/>
-      <c r="G64" s="143" t="n"/>
-      <c r="H64" s="143" t="n"/>
-      <c r="I64" s="143" t="n"/>
-      <c r="J64" s="143" t="n"/>
-      <c r="K64" s="143" t="n"/>
-      <c r="L64" s="143" t="n"/>
-      <c r="M64" s="143" t="n"/>
-      <c r="N64" s="143" t="n"/>
-      <c r="O64" s="143" t="n"/>
-      <c r="P64" s="143" t="n"/>
-      <c r="Q64" s="143" t="n"/>
-      <c r="R64" s="143" t="n"/>
-      <c r="S64" s="143" t="n"/>
-      <c r="T64" s="143" t="n"/>
-      <c r="U64" s="143" t="n"/>
-      <c r="V64" s="143" t="n"/>
-      <c r="W64" s="143" t="n"/>
-      <c r="X64" s="143" t="n">
+      <c r="D64" s="149" t="n"/>
+      <c r="E64" s="149" t="n"/>
+      <c r="F64" s="149" t="n"/>
+      <c r="G64" s="149" t="n"/>
+      <c r="H64" s="149" t="n"/>
+      <c r="I64" s="149" t="n"/>
+      <c r="J64" s="149" t="n"/>
+      <c r="K64" s="149" t="n"/>
+      <c r="L64" s="149" t="n"/>
+      <c r="M64" s="149" t="n"/>
+      <c r="N64" s="149" t="n"/>
+      <c r="O64" s="149" t="n"/>
+      <c r="P64" s="149" t="n"/>
+      <c r="Q64" s="149" t="n"/>
+      <c r="R64" s="149" t="n"/>
+      <c r="S64" s="149" t="n"/>
+      <c r="T64" s="149" t="n"/>
+      <c r="U64" s="149" t="n"/>
+      <c r="V64" s="149" t="n"/>
+      <c r="W64" s="149" t="n"/>
+      <c r="X64" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y64" s="143" t="n">
+      <c r="Y64" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="143" t="n"/>
-      <c r="AA64" s="143" t="n"/>
-      <c r="AB64" s="143" t="n"/>
-      <c r="AC64" s="143" t="n"/>
-      <c r="AD64" s="143" t="n"/>
-      <c r="AE64" s="143" t="n"/>
-      <c r="AF64" s="143" t="n"/>
-      <c r="AG64" s="143" t="n"/>
-      <c r="AH64" s="143" t="n"/>
+      <c r="Z64" s="149" t="n"/>
+      <c r="AA64" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="149" t="n"/>
+      <c r="AC64" s="149" t="n"/>
+      <c r="AD64" s="149" t="n"/>
+      <c r="AE64" s="149" t="n"/>
+      <c r="AF64" s="149" t="n"/>
+      <c r="AG64" s="149" t="n"/>
+      <c r="AH64" s="149" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="118">
       <c r="C65" s="142" t="inlineStr">
@@ -8298,41 +8366,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D65" s="143" t="n"/>
-      <c r="E65" s="143" t="n"/>
-      <c r="F65" s="143" t="n"/>
-      <c r="G65" s="143" t="n"/>
-      <c r="H65" s="143" t="n"/>
-      <c r="I65" s="143" t="n"/>
-      <c r="J65" s="143" t="n"/>
-      <c r="K65" s="143" t="n"/>
-      <c r="L65" s="143" t="n"/>
-      <c r="M65" s="143" t="n"/>
-      <c r="N65" s="143" t="n"/>
-      <c r="O65" s="143" t="n"/>
-      <c r="P65" s="143" t="n"/>
-      <c r="Q65" s="143" t="n"/>
-      <c r="R65" s="143" t="n"/>
-      <c r="S65" s="143" t="n"/>
-      <c r="T65" s="143" t="n"/>
-      <c r="U65" s="143" t="n"/>
-      <c r="V65" s="143" t="n"/>
-      <c r="W65" s="143" t="n"/>
-      <c r="X65" s="143" t="n">
+      <c r="D65" s="149" t="n"/>
+      <c r="E65" s="149" t="n"/>
+      <c r="F65" s="149" t="n"/>
+      <c r="G65" s="149" t="n"/>
+      <c r="H65" s="149" t="n"/>
+      <c r="I65" s="149" t="n"/>
+      <c r="J65" s="149" t="n"/>
+      <c r="K65" s="149" t="n"/>
+      <c r="L65" s="149" t="n"/>
+      <c r="M65" s="149" t="n"/>
+      <c r="N65" s="149" t="n"/>
+      <c r="O65" s="149" t="n"/>
+      <c r="P65" s="149" t="n"/>
+      <c r="Q65" s="149" t="n"/>
+      <c r="R65" s="149" t="n"/>
+      <c r="S65" s="149" t="n"/>
+      <c r="T65" s="149" t="n"/>
+      <c r="U65" s="149" t="n"/>
+      <c r="V65" s="149" t="n"/>
+      <c r="W65" s="149" t="n"/>
+      <c r="X65" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y65" s="143" t="n">
+      <c r="Y65" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="143" t="n"/>
-      <c r="AA65" s="143" t="n"/>
-      <c r="AB65" s="143" t="n"/>
-      <c r="AC65" s="143" t="n"/>
-      <c r="AD65" s="143" t="n"/>
-      <c r="AE65" s="143" t="n"/>
-      <c r="AF65" s="143" t="n"/>
-      <c r="AG65" s="143" t="n"/>
-      <c r="AH65" s="143" t="n"/>
+      <c r="Z65" s="149" t="n"/>
+      <c r="AA65" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="149" t="n"/>
+      <c r="AC65" s="149" t="n"/>
+      <c r="AD65" s="149" t="n"/>
+      <c r="AE65" s="149" t="n"/>
+      <c r="AF65" s="149" t="n"/>
+      <c r="AG65" s="149" t="n"/>
+      <c r="AH65" s="149" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="118">
       <c r="C66" s="142" t="inlineStr">
@@ -8340,41 +8410,43 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D66" s="143" t="n"/>
-      <c r="E66" s="143" t="n"/>
-      <c r="F66" s="143" t="n"/>
-      <c r="G66" s="143" t="n"/>
-      <c r="H66" s="143" t="n"/>
-      <c r="I66" s="143" t="n"/>
-      <c r="J66" s="143" t="n"/>
-      <c r="K66" s="143" t="n"/>
-      <c r="L66" s="143" t="n"/>
-      <c r="M66" s="143" t="n"/>
-      <c r="N66" s="143" t="n"/>
-      <c r="O66" s="143" t="n"/>
-      <c r="P66" s="143" t="n"/>
-      <c r="Q66" s="143" t="n"/>
-      <c r="R66" s="143" t="n"/>
-      <c r="S66" s="143" t="n"/>
-      <c r="T66" s="143" t="n"/>
-      <c r="U66" s="143" t="n"/>
-      <c r="V66" s="143" t="n"/>
-      <c r="W66" s="143" t="n"/>
-      <c r="X66" s="143" t="n">
+      <c r="D66" s="149" t="n"/>
+      <c r="E66" s="149" t="n"/>
+      <c r="F66" s="149" t="n"/>
+      <c r="G66" s="149" t="n"/>
+      <c r="H66" s="149" t="n"/>
+      <c r="I66" s="149" t="n"/>
+      <c r="J66" s="149" t="n"/>
+      <c r="K66" s="149" t="n"/>
+      <c r="L66" s="149" t="n"/>
+      <c r="M66" s="149" t="n"/>
+      <c r="N66" s="149" t="n"/>
+      <c r="O66" s="149" t="n"/>
+      <c r="P66" s="149" t="n"/>
+      <c r="Q66" s="149" t="n"/>
+      <c r="R66" s="149" t="n"/>
+      <c r="S66" s="149" t="n"/>
+      <c r="T66" s="149" t="n"/>
+      <c r="U66" s="149" t="n"/>
+      <c r="V66" s="149" t="n"/>
+      <c r="W66" s="149" t="n"/>
+      <c r="X66" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y66" s="143" t="n">
+      <c r="Y66" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="143" t="n"/>
-      <c r="AA66" s="143" t="n"/>
-      <c r="AB66" s="143" t="n"/>
-      <c r="AC66" s="143" t="n"/>
-      <c r="AD66" s="143" t="n"/>
-      <c r="AE66" s="143" t="n"/>
-      <c r="AF66" s="143" t="n"/>
-      <c r="AG66" s="143" t="n"/>
-      <c r="AH66" s="143" t="n"/>
+      <c r="Z66" s="149" t="n"/>
+      <c r="AA66" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="149" t="n"/>
+      <c r="AC66" s="149" t="n"/>
+      <c r="AD66" s="149" t="n"/>
+      <c r="AE66" s="149" t="n"/>
+      <c r="AF66" s="149" t="n"/>
+      <c r="AG66" s="149" t="n"/>
+      <c r="AH66" s="149" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="118">
       <c r="C67" s="142" t="inlineStr">
@@ -8656,43 +8728,45 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D71" s="143" t="n"/>
-      <c r="E71" s="143" t="n"/>
-      <c r="F71" s="143" t="n"/>
-      <c r="G71" s="143" t="n"/>
-      <c r="H71" s="143" t="n"/>
-      <c r="I71" s="143" t="n"/>
-      <c r="J71" s="143" t="n"/>
-      <c r="K71" s="143" t="n"/>
-      <c r="L71" s="143" t="n"/>
-      <c r="M71" s="143" t="n"/>
-      <c r="N71" s="143" t="n"/>
-      <c r="O71" s="143" t="n"/>
-      <c r="P71" s="143" t="n"/>
-      <c r="Q71" s="143" t="n"/>
-      <c r="R71" s="143" t="n">
+      <c r="D71" s="149" t="n"/>
+      <c r="E71" s="149" t="n"/>
+      <c r="F71" s="149" t="n"/>
+      <c r="G71" s="149" t="n"/>
+      <c r="H71" s="149" t="n"/>
+      <c r="I71" s="149" t="n"/>
+      <c r="J71" s="149" t="n"/>
+      <c r="K71" s="149" t="n"/>
+      <c r="L71" s="149" t="n"/>
+      <c r="M71" s="149" t="n"/>
+      <c r="N71" s="149" t="n"/>
+      <c r="O71" s="149" t="n"/>
+      <c r="P71" s="149" t="n"/>
+      <c r="Q71" s="149" t="n"/>
+      <c r="R71" s="149" t="n">
         <v>348875</v>
       </c>
-      <c r="S71" s="143" t="n"/>
-      <c r="T71" s="143" t="n"/>
-      <c r="U71" s="143" t="n"/>
-      <c r="V71" s="143" t="n"/>
-      <c r="W71" s="143" t="n"/>
-      <c r="X71" s="143" t="n">
+      <c r="S71" s="149" t="n"/>
+      <c r="T71" s="149" t="n"/>
+      <c r="U71" s="149" t="n"/>
+      <c r="V71" s="149" t="n"/>
+      <c r="W71" s="149" t="n"/>
+      <c r="X71" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y71" s="143" t="n">
+      <c r="Y71" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="143" t="n"/>
-      <c r="AA71" s="143" t="n"/>
-      <c r="AB71" s="143" t="n"/>
-      <c r="AC71" s="143" t="n"/>
-      <c r="AD71" s="143" t="n"/>
-      <c r="AE71" s="143" t="n"/>
-      <c r="AF71" s="143" t="n"/>
-      <c r="AG71" s="143" t="n"/>
-      <c r="AH71" s="143" t="n"/>
+      <c r="Z71" s="149" t="n"/>
+      <c r="AA71" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="149" t="n"/>
+      <c r="AC71" s="149" t="n"/>
+      <c r="AD71" s="149" t="n"/>
+      <c r="AE71" s="149" t="n"/>
+      <c r="AF71" s="149" t="n"/>
+      <c r="AG71" s="149" t="n"/>
+      <c r="AH71" s="149" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="118">
       <c r="C72" s="142" t="inlineStr">
@@ -8700,43 +8774,45 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D72" s="143" t="n"/>
-      <c r="E72" s="143" t="n"/>
-      <c r="F72" s="143" t="n"/>
-      <c r="G72" s="143" t="n"/>
-      <c r="H72" s="143" t="n"/>
-      <c r="I72" s="143" t="n"/>
-      <c r="J72" s="143" t="n"/>
-      <c r="K72" s="143" t="n"/>
-      <c r="L72" s="143" t="n"/>
-      <c r="M72" s="143" t="n"/>
-      <c r="N72" s="143" t="n"/>
-      <c r="O72" s="143" t="n"/>
-      <c r="P72" s="143" t="n"/>
-      <c r="Q72" s="143" t="n"/>
-      <c r="R72" s="143" t="n">
+      <c r="D72" s="149" t="n"/>
+      <c r="E72" s="149" t="n"/>
+      <c r="F72" s="149" t="n"/>
+      <c r="G72" s="149" t="n"/>
+      <c r="H72" s="149" t="n"/>
+      <c r="I72" s="149" t="n"/>
+      <c r="J72" s="149" t="n"/>
+      <c r="K72" s="149" t="n"/>
+      <c r="L72" s="149" t="n"/>
+      <c r="M72" s="149" t="n"/>
+      <c r="N72" s="149" t="n"/>
+      <c r="O72" s="149" t="n"/>
+      <c r="P72" s="149" t="n"/>
+      <c r="Q72" s="149" t="n"/>
+      <c r="R72" s="149" t="n">
         <v>8017000</v>
       </c>
-      <c r="S72" s="143" t="n"/>
-      <c r="T72" s="143" t="n"/>
-      <c r="U72" s="143" t="n"/>
-      <c r="V72" s="143" t="n"/>
-      <c r="W72" s="143" t="n"/>
-      <c r="X72" s="143" t="n">
+      <c r="S72" s="149" t="n"/>
+      <c r="T72" s="149" t="n"/>
+      <c r="U72" s="149" t="n"/>
+      <c r="V72" s="149" t="n"/>
+      <c r="W72" s="149" t="n"/>
+      <c r="X72" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y72" s="143" t="n">
+      <c r="Y72" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="143" t="n"/>
-      <c r="AA72" s="143" t="n"/>
-      <c r="AB72" s="143" t="n"/>
-      <c r="AC72" s="143" t="n"/>
-      <c r="AD72" s="143" t="n"/>
-      <c r="AE72" s="143" t="n"/>
-      <c r="AF72" s="143" t="n"/>
-      <c r="AG72" s="143" t="n"/>
-      <c r="AH72" s="143" t="n"/>
+      <c r="Z72" s="149" t="n"/>
+      <c r="AA72" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="149" t="n"/>
+      <c r="AC72" s="149" t="n"/>
+      <c r="AD72" s="149" t="n"/>
+      <c r="AE72" s="149" t="n"/>
+      <c r="AF72" s="149" t="n"/>
+      <c r="AG72" s="149" t="n"/>
+      <c r="AH72" s="149" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="118">
       <c r="C73" s="142" t="inlineStr">
@@ -8744,41 +8820,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D73" s="143" t="n"/>
-      <c r="E73" s="143" t="n"/>
-      <c r="F73" s="143" t="n"/>
-      <c r="G73" s="143" t="n"/>
-      <c r="H73" s="143" t="n"/>
-      <c r="I73" s="143" t="n"/>
-      <c r="J73" s="143" t="n"/>
-      <c r="K73" s="143" t="n"/>
-      <c r="L73" s="143" t="n"/>
-      <c r="M73" s="143" t="n"/>
-      <c r="N73" s="143" t="n"/>
-      <c r="O73" s="143" t="n"/>
-      <c r="P73" s="143" t="n"/>
-      <c r="Q73" s="143" t="n"/>
-      <c r="R73" s="143" t="n"/>
-      <c r="S73" s="143" t="n"/>
-      <c r="T73" s="143" t="n"/>
-      <c r="U73" s="143" t="n"/>
-      <c r="V73" s="143" t="n"/>
-      <c r="W73" s="143" t="n"/>
-      <c r="X73" s="143" t="n">
+      <c r="D73" s="149" t="n"/>
+      <c r="E73" s="149" t="n"/>
+      <c r="F73" s="149" t="n"/>
+      <c r="G73" s="149" t="n"/>
+      <c r="H73" s="149" t="n"/>
+      <c r="I73" s="149" t="n"/>
+      <c r="J73" s="149" t="n"/>
+      <c r="K73" s="149" t="n"/>
+      <c r="L73" s="149" t="n"/>
+      <c r="M73" s="149" t="n"/>
+      <c r="N73" s="149" t="n"/>
+      <c r="O73" s="149" t="n"/>
+      <c r="P73" s="149" t="n"/>
+      <c r="Q73" s="149" t="n"/>
+      <c r="R73" s="149" t="n"/>
+      <c r="S73" s="149" t="n"/>
+      <c r="T73" s="149" t="n"/>
+      <c r="U73" s="149" t="n"/>
+      <c r="V73" s="149" t="n"/>
+      <c r="W73" s="149" t="n"/>
+      <c r="X73" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y73" s="143" t="n">
+      <c r="Y73" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="143" t="n"/>
-      <c r="AA73" s="143" t="n"/>
-      <c r="AB73" s="143" t="n"/>
-      <c r="AC73" s="143" t="n"/>
-      <c r="AD73" s="143" t="n"/>
-      <c r="AE73" s="143" t="n"/>
-      <c r="AF73" s="143" t="n"/>
-      <c r="AG73" s="143" t="n"/>
-      <c r="AH73" s="143" t="n"/>
+      <c r="Z73" s="149" t="n"/>
+      <c r="AA73" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="149" t="n"/>
+      <c r="AC73" s="149" t="n"/>
+      <c r="AD73" s="149" t="n"/>
+      <c r="AE73" s="149" t="n"/>
+      <c r="AF73" s="149" t="n"/>
+      <c r="AG73" s="149" t="n"/>
+      <c r="AH73" s="149" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="118">
       <c r="C74" s="142" t="inlineStr">
@@ -8786,43 +8864,45 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D74" s="143" t="n"/>
-      <c r="E74" s="143" t="n"/>
-      <c r="F74" s="143" t="n"/>
-      <c r="G74" s="143" t="n"/>
-      <c r="H74" s="143" t="n"/>
-      <c r="I74" s="143" t="n"/>
-      <c r="J74" s="143" t="n"/>
-      <c r="K74" s="143" t="n"/>
-      <c r="L74" s="143" t="n"/>
-      <c r="M74" s="143" t="n"/>
-      <c r="N74" s="143" t="n"/>
-      <c r="O74" s="143" t="n"/>
-      <c r="P74" s="143" t="n"/>
-      <c r="Q74" s="143" t="n"/>
-      <c r="R74" s="143" t="n">
+      <c r="D74" s="149" t="n"/>
+      <c r="E74" s="149" t="n"/>
+      <c r="F74" s="149" t="n"/>
+      <c r="G74" s="149" t="n"/>
+      <c r="H74" s="149" t="n"/>
+      <c r="I74" s="149" t="n"/>
+      <c r="J74" s="149" t="n"/>
+      <c r="K74" s="149" t="n"/>
+      <c r="L74" s="149" t="n"/>
+      <c r="M74" s="149" t="n"/>
+      <c r="N74" s="149" t="n"/>
+      <c r="O74" s="149" t="n"/>
+      <c r="P74" s="149" t="n"/>
+      <c r="Q74" s="149" t="n"/>
+      <c r="R74" s="149" t="n">
         <v>157</v>
       </c>
-      <c r="S74" s="143" t="n"/>
-      <c r="T74" s="143" t="n"/>
-      <c r="U74" s="143" t="n"/>
-      <c r="V74" s="143" t="n"/>
-      <c r="W74" s="143" t="n"/>
-      <c r="X74" s="143" t="n">
+      <c r="S74" s="149" t="n"/>
+      <c r="T74" s="149" t="n"/>
+      <c r="U74" s="149" t="n"/>
+      <c r="V74" s="149" t="n"/>
+      <c r="W74" s="149" t="n"/>
+      <c r="X74" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y74" s="143" t="n">
+      <c r="Y74" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="143" t="n"/>
-      <c r="AA74" s="143" t="n"/>
-      <c r="AB74" s="143" t="n"/>
-      <c r="AC74" s="143" t="n"/>
-      <c r="AD74" s="143" t="n"/>
-      <c r="AE74" s="143" t="n"/>
-      <c r="AF74" s="143" t="n"/>
-      <c r="AG74" s="143" t="n"/>
-      <c r="AH74" s="143" t="n"/>
+      <c r="Z74" s="149" t="n"/>
+      <c r="AA74" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="149" t="n"/>
+      <c r="AC74" s="149" t="n"/>
+      <c r="AD74" s="149" t="n"/>
+      <c r="AE74" s="149" t="n"/>
+      <c r="AF74" s="149" t="n"/>
+      <c r="AG74" s="149" t="n"/>
+      <c r="AH74" s="149" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1" s="118">
       <c r="C75" s="142" t="inlineStr">
@@ -9097,39 +9177,45 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D78" s="143" t="n"/>
-      <c r="E78" s="143" t="n"/>
-      <c r="F78" s="143" t="n"/>
-      <c r="G78" s="143" t="n"/>
-      <c r="H78" s="143" t="n"/>
-      <c r="I78" s="143" t="n"/>
-      <c r="J78" s="143" t="n"/>
-      <c r="K78" s="143" t="n"/>
-      <c r="L78" s="143" t="n"/>
-      <c r="M78" s="143" t="n">
+      <c r="D78" s="149" t="n"/>
+      <c r="E78" s="149" t="n"/>
+      <c r="F78" s="149" t="n"/>
+      <c r="G78" s="149" t="n"/>
+      <c r="H78" s="149" t="n"/>
+      <c r="I78" s="149" t="n"/>
+      <c r="J78" s="149" t="n"/>
+      <c r="K78" s="149" t="n"/>
+      <c r="L78" s="149" t="n"/>
+      <c r="M78" s="149" t="n">
         <v>35800</v>
       </c>
-      <c r="N78" s="143" t="n"/>
-      <c r="O78" s="143" t="n"/>
-      <c r="P78" s="143" t="n"/>
-      <c r="Q78" s="143" t="n"/>
-      <c r="R78" s="143" t="n"/>
-      <c r="S78" s="143" t="n"/>
-      <c r="T78" s="143" t="n"/>
-      <c r="U78" s="143" t="n"/>
-      <c r="V78" s="143" t="n"/>
-      <c r="W78" s="143" t="n"/>
-      <c r="X78" s="143" t="n"/>
-      <c r="Y78" s="143" t="n"/>
-      <c r="Z78" s="143" t="n"/>
-      <c r="AA78" s="143" t="n"/>
-      <c r="AB78" s="143" t="n"/>
-      <c r="AC78" s="143" t="n"/>
-      <c r="AD78" s="143" t="n"/>
-      <c r="AE78" s="143" t="n"/>
-      <c r="AF78" s="143" t="n"/>
-      <c r="AG78" s="143" t="n"/>
-      <c r="AH78" s="143" t="n"/>
+      <c r="N78" s="149" t="n"/>
+      <c r="O78" s="149" t="n"/>
+      <c r="P78" s="149" t="n"/>
+      <c r="Q78" s="149" t="n"/>
+      <c r="R78" s="149" t="n"/>
+      <c r="S78" s="149" t="n"/>
+      <c r="T78" s="149" t="n"/>
+      <c r="U78" s="149" t="n"/>
+      <c r="V78" s="149" t="n"/>
+      <c r="W78" s="149" t="n"/>
+      <c r="X78" s="149" t="n"/>
+      <c r="Y78" s="149" t="n">
+        <v>4098.3</v>
+      </c>
+      <c r="Z78" s="149" t="n">
+        <v>3917.7</v>
+      </c>
+      <c r="AA78" s="149" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB78" s="149" t="n"/>
+      <c r="AC78" s="149" t="n"/>
+      <c r="AD78" s="149" t="n"/>
+      <c r="AE78" s="149" t="n"/>
+      <c r="AF78" s="149" t="n"/>
+      <c r="AG78" s="149" t="n"/>
+      <c r="AH78" s="149" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="118">
       <c r="C79" s="142" t="inlineStr">
@@ -9137,37 +9223,43 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D79" s="143" t="n"/>
-      <c r="E79" s="143" t="n"/>
-      <c r="F79" s="143" t="n"/>
-      <c r="G79" s="143" t="n"/>
-      <c r="H79" s="143" t="n"/>
-      <c r="I79" s="143" t="n"/>
-      <c r="J79" s="143" t="n"/>
-      <c r="K79" s="143" t="n"/>
-      <c r="L79" s="143" t="n"/>
-      <c r="M79" s="143" t="n"/>
-      <c r="N79" s="143" t="n"/>
-      <c r="O79" s="143" t="n"/>
-      <c r="P79" s="143" t="n"/>
-      <c r="Q79" s="143" t="n"/>
-      <c r="R79" s="143" t="n"/>
-      <c r="S79" s="143" t="n"/>
-      <c r="T79" s="143" t="n"/>
-      <c r="U79" s="143" t="n"/>
-      <c r="V79" s="143" t="n"/>
-      <c r="W79" s="143" t="n"/>
-      <c r="X79" s="143" t="n"/>
-      <c r="Y79" s="143" t="n"/>
-      <c r="Z79" s="143" t="n"/>
-      <c r="AA79" s="143" t="n"/>
-      <c r="AB79" s="143" t="n"/>
-      <c r="AC79" s="143" t="n"/>
-      <c r="AD79" s="143" t="n"/>
-      <c r="AE79" s="143" t="n"/>
-      <c r="AF79" s="143" t="n"/>
-      <c r="AG79" s="143" t="n"/>
-      <c r="AH79" s="143" t="n"/>
+      <c r="D79" s="149" t="n"/>
+      <c r="E79" s="149" t="n"/>
+      <c r="F79" s="149" t="n"/>
+      <c r="G79" s="149" t="n"/>
+      <c r="H79" s="149" t="n"/>
+      <c r="I79" s="149" t="n"/>
+      <c r="J79" s="149" t="n"/>
+      <c r="K79" s="149" t="n"/>
+      <c r="L79" s="149" t="n"/>
+      <c r="M79" s="149" t="n"/>
+      <c r="N79" s="149" t="n"/>
+      <c r="O79" s="149" t="n"/>
+      <c r="P79" s="149" t="n"/>
+      <c r="Q79" s="149" t="n"/>
+      <c r="R79" s="149" t="n"/>
+      <c r="S79" s="149" t="n"/>
+      <c r="T79" s="149" t="n"/>
+      <c r="U79" s="149" t="n"/>
+      <c r="V79" s="149" t="n"/>
+      <c r="W79" s="149" t="n"/>
+      <c r="X79" s="149" t="n"/>
+      <c r="Y79" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="149" t="n"/>
+      <c r="AC79" s="149" t="n"/>
+      <c r="AD79" s="149" t="n"/>
+      <c r="AE79" s="149" t="n"/>
+      <c r="AF79" s="149" t="n"/>
+      <c r="AG79" s="149" t="n"/>
+      <c r="AH79" s="149" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="118">
       <c r="C80" s="142" t="inlineStr">
@@ -9175,37 +9267,43 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D80" s="143" t="n"/>
-      <c r="E80" s="143" t="n"/>
-      <c r="F80" s="143" t="n"/>
-      <c r="G80" s="143" t="n"/>
-      <c r="H80" s="143" t="n"/>
-      <c r="I80" s="143" t="n"/>
-      <c r="J80" s="143" t="n"/>
-      <c r="K80" s="143" t="n"/>
-      <c r="L80" s="143" t="n"/>
-      <c r="M80" s="143" t="n"/>
-      <c r="N80" s="143" t="n"/>
-      <c r="O80" s="143" t="n"/>
-      <c r="P80" s="143" t="n"/>
-      <c r="Q80" s="143" t="n"/>
-      <c r="R80" s="143" t="n"/>
-      <c r="S80" s="143" t="n"/>
-      <c r="T80" s="143" t="n"/>
-      <c r="U80" s="143" t="n"/>
-      <c r="V80" s="143" t="n"/>
-      <c r="W80" s="143" t="n"/>
-      <c r="X80" s="143" t="n"/>
-      <c r="Y80" s="143" t="n"/>
-      <c r="Z80" s="143" t="n"/>
-      <c r="AA80" s="143" t="n"/>
-      <c r="AB80" s="143" t="n"/>
-      <c r="AC80" s="143" t="n"/>
-      <c r="AD80" s="143" t="n"/>
-      <c r="AE80" s="143" t="n"/>
-      <c r="AF80" s="143" t="n"/>
-      <c r="AG80" s="143" t="n"/>
-      <c r="AH80" s="143" t="n"/>
+      <c r="D80" s="149" t="n"/>
+      <c r="E80" s="149" t="n"/>
+      <c r="F80" s="149" t="n"/>
+      <c r="G80" s="149" t="n"/>
+      <c r="H80" s="149" t="n"/>
+      <c r="I80" s="149" t="n"/>
+      <c r="J80" s="149" t="n"/>
+      <c r="K80" s="149" t="n"/>
+      <c r="L80" s="149" t="n"/>
+      <c r="M80" s="149" t="n"/>
+      <c r="N80" s="149" t="n"/>
+      <c r="O80" s="149" t="n"/>
+      <c r="P80" s="149" t="n"/>
+      <c r="Q80" s="149" t="n"/>
+      <c r="R80" s="149" t="n"/>
+      <c r="S80" s="149" t="n"/>
+      <c r="T80" s="149" t="n"/>
+      <c r="U80" s="149" t="n"/>
+      <c r="V80" s="149" t="n"/>
+      <c r="W80" s="149" t="n"/>
+      <c r="X80" s="149" t="n"/>
+      <c r="Y80" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="149" t="n"/>
+      <c r="AC80" s="149" t="n"/>
+      <c r="AD80" s="149" t="n"/>
+      <c r="AE80" s="149" t="n"/>
+      <c r="AF80" s="149" t="n"/>
+      <c r="AG80" s="149" t="n"/>
+      <c r="AH80" s="149" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1" s="118">
       <c r="C81" s="142" t="inlineStr">
@@ -9213,39 +9311,45 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D81" s="143" t="n"/>
-      <c r="E81" s="143" t="n"/>
-      <c r="F81" s="143" t="n"/>
-      <c r="G81" s="143" t="n"/>
-      <c r="H81" s="143" t="n"/>
-      <c r="I81" s="143" t="n"/>
-      <c r="J81" s="143" t="n"/>
-      <c r="K81" s="143" t="n"/>
-      <c r="L81" s="143" t="n"/>
-      <c r="M81" s="143" t="n">
+      <c r="D81" s="149" t="n"/>
+      <c r="E81" s="149" t="n"/>
+      <c r="F81" s="149" t="n"/>
+      <c r="G81" s="149" t="n"/>
+      <c r="H81" s="149" t="n"/>
+      <c r="I81" s="149" t="n"/>
+      <c r="J81" s="149" t="n"/>
+      <c r="K81" s="149" t="n"/>
+      <c r="L81" s="149" t="n"/>
+      <c r="M81" s="149" t="n">
         <v>80</v>
       </c>
-      <c r="N81" s="143" t="n"/>
-      <c r="O81" s="143" t="n"/>
-      <c r="P81" s="143" t="n"/>
-      <c r="Q81" s="143" t="n"/>
-      <c r="R81" s="143" t="n"/>
-      <c r="S81" s="143" t="n"/>
-      <c r="T81" s="143" t="n"/>
-      <c r="U81" s="143" t="n"/>
-      <c r="V81" s="143" t="n"/>
-      <c r="W81" s="143" t="n"/>
-      <c r="X81" s="143" t="n"/>
-      <c r="Y81" s="143" t="n"/>
-      <c r="Z81" s="143" t="n"/>
-      <c r="AA81" s="143" t="n"/>
-      <c r="AB81" s="143" t="n"/>
-      <c r="AC81" s="143" t="n"/>
-      <c r="AD81" s="143" t="n"/>
-      <c r="AE81" s="143" t="n"/>
-      <c r="AF81" s="143" t="n"/>
-      <c r="AG81" s="143" t="n"/>
-      <c r="AH81" s="143" t="n"/>
+      <c r="N81" s="149" t="n"/>
+      <c r="O81" s="149" t="n"/>
+      <c r="P81" s="149" t="n"/>
+      <c r="Q81" s="149" t="n"/>
+      <c r="R81" s="149" t="n"/>
+      <c r="S81" s="149" t="n"/>
+      <c r="T81" s="149" t="n"/>
+      <c r="U81" s="149" t="n"/>
+      <c r="V81" s="149" t="n"/>
+      <c r="W81" s="149" t="n"/>
+      <c r="X81" s="149" t="n"/>
+      <c r="Y81" s="149" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z81" s="149" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA81" s="149" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB81" s="149" t="n"/>
+      <c r="AC81" s="149" t="n"/>
+      <c r="AD81" s="149" t="n"/>
+      <c r="AE81" s="149" t="n"/>
+      <c r="AF81" s="149" t="n"/>
+      <c r="AG81" s="149" t="n"/>
+      <c r="AH81" s="149" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="118">
       <c r="C82" s="142" t="inlineStr">
@@ -9527,45 +9631,47 @@
           <t>Cost (kr.)</t>
         </is>
       </c>
-      <c r="D86" s="143" t="n"/>
-      <c r="E86" s="143" t="n"/>
-      <c r="F86" s="143" t="n"/>
-      <c r="G86" s="143" t="n"/>
-      <c r="H86" s="143" t="n"/>
-      <c r="I86" s="143" t="n">
+      <c r="D86" s="149" t="n"/>
+      <c r="E86" s="149" t="n"/>
+      <c r="F86" s="149" t="n"/>
+      <c r="G86" s="149" t="n"/>
+      <c r="H86" s="149" t="n"/>
+      <c r="I86" s="149" t="n">
         <v>6500</v>
       </c>
-      <c r="J86" s="143" t="n"/>
-      <c r="K86" s="143" t="n"/>
-      <c r="L86" s="143" t="n"/>
-      <c r="M86" s="143" t="n"/>
-      <c r="N86" s="143" t="n"/>
-      <c r="O86" s="143" t="n"/>
-      <c r="P86" s="143" t="n"/>
-      <c r="Q86" s="143" t="n"/>
-      <c r="R86" s="143" t="n"/>
-      <c r="S86" s="143" t="n"/>
-      <c r="T86" s="143" t="n"/>
-      <c r="U86" s="143" t="n"/>
-      <c r="V86" s="143" t="n"/>
-      <c r="W86" s="143" t="n"/>
-      <c r="X86" s="143" t="n">
+      <c r="J86" s="149" t="n"/>
+      <c r="K86" s="149" t="n"/>
+      <c r="L86" s="149" t="n"/>
+      <c r="M86" s="149" t="n"/>
+      <c r="N86" s="149" t="n"/>
+      <c r="O86" s="149" t="n"/>
+      <c r="P86" s="149" t="n"/>
+      <c r="Q86" s="149" t="n"/>
+      <c r="R86" s="149" t="n"/>
+      <c r="S86" s="149" t="n"/>
+      <c r="T86" s="149" t="n"/>
+      <c r="U86" s="149" t="n"/>
+      <c r="V86" s="149" t="n"/>
+      <c r="W86" s="149" t="n"/>
+      <c r="X86" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y86" s="143" t="n">
+      <c r="Y86" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="143" t="n">
+      <c r="Z86" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AA86" s="143" t="n"/>
-      <c r="AB86" s="143" t="n"/>
-      <c r="AC86" s="143" t="n"/>
-      <c r="AD86" s="143" t="n"/>
-      <c r="AE86" s="143" t="n"/>
-      <c r="AF86" s="143" t="n"/>
-      <c r="AG86" s="143" t="n"/>
-      <c r="AH86" s="143" t="n"/>
+      <c r="AA86" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="149" t="n"/>
+      <c r="AC86" s="149" t="n"/>
+      <c r="AD86" s="149" t="n"/>
+      <c r="AE86" s="149" t="n"/>
+      <c r="AF86" s="149" t="n"/>
+      <c r="AG86" s="149" t="n"/>
+      <c r="AH86" s="149" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="118">
       <c r="C87" s="142" t="inlineStr">
@@ -9573,43 +9679,45 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D87" s="143" t="n"/>
-      <c r="E87" s="143" t="n"/>
-      <c r="F87" s="143" t="n"/>
-      <c r="G87" s="143" t="n"/>
-      <c r="H87" s="143" t="n"/>
-      <c r="I87" s="143" t="n"/>
-      <c r="J87" s="143" t="n"/>
-      <c r="K87" s="143" t="n"/>
-      <c r="L87" s="143" t="n"/>
-      <c r="M87" s="143" t="n"/>
-      <c r="N87" s="143" t="n"/>
-      <c r="O87" s="143" t="n"/>
-      <c r="P87" s="143" t="n"/>
-      <c r="Q87" s="143" t="n"/>
-      <c r="R87" s="143" t="n"/>
-      <c r="S87" s="143" t="n"/>
-      <c r="T87" s="143" t="n"/>
-      <c r="U87" s="143" t="n"/>
-      <c r="V87" s="143" t="n"/>
-      <c r="W87" s="143" t="n"/>
-      <c r="X87" s="143" t="n">
+      <c r="D87" s="149" t="n"/>
+      <c r="E87" s="149" t="n"/>
+      <c r="F87" s="149" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="149" t="n"/>
+      <c r="I87" s="149" t="n"/>
+      <c r="J87" s="149" t="n"/>
+      <c r="K87" s="149" t="n"/>
+      <c r="L87" s="149" t="n"/>
+      <c r="M87" s="149" t="n"/>
+      <c r="N87" s="149" t="n"/>
+      <c r="O87" s="149" t="n"/>
+      <c r="P87" s="149" t="n"/>
+      <c r="Q87" s="149" t="n"/>
+      <c r="R87" s="149" t="n"/>
+      <c r="S87" s="149" t="n"/>
+      <c r="T87" s="149" t="n"/>
+      <c r="U87" s="149" t="n"/>
+      <c r="V87" s="149" t="n"/>
+      <c r="W87" s="149" t="n"/>
+      <c r="X87" s="149" t="n">
         <v>686000</v>
       </c>
-      <c r="Y87" s="143" t="n">
+      <c r="Y87" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="143" t="n">
+      <c r="Z87" s="149" t="n">
         <v>389000</v>
       </c>
-      <c r="AA87" s="143" t="n"/>
-      <c r="AB87" s="143" t="n"/>
-      <c r="AC87" s="143" t="n"/>
-      <c r="AD87" s="143" t="n"/>
-      <c r="AE87" s="143" t="n"/>
-      <c r="AF87" s="143" t="n"/>
-      <c r="AG87" s="143" t="n"/>
-      <c r="AH87" s="143" t="n"/>
+      <c r="AA87" s="149" t="n">
+        <v>413000</v>
+      </c>
+      <c r="AB87" s="149" t="n"/>
+      <c r="AC87" s="149" t="n"/>
+      <c r="AD87" s="149" t="n"/>
+      <c r="AE87" s="149" t="n"/>
+      <c r="AF87" s="149" t="n"/>
+      <c r="AG87" s="149" t="n"/>
+      <c r="AH87" s="149" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1" s="118">
       <c r="C88" s="142" t="inlineStr">
@@ -9617,69 +9725,71 @@
           <t>Traffic</t>
         </is>
       </c>
-      <c r="D88" s="143" t="n">
+      <c r="D88" s="149" t="n">
         <v>147</v>
       </c>
-      <c r="E88" s="143" t="n">
+      <c r="E88" s="149" t="n">
         <v>2966</v>
       </c>
-      <c r="F88" s="143" t="n"/>
-      <c r="G88" s="143" t="n"/>
-      <c r="H88" s="143" t="n"/>
-      <c r="I88" s="143" t="n"/>
-      <c r="J88" s="143" t="n"/>
-      <c r="K88" s="143" t="n"/>
-      <c r="L88" s="143" t="n"/>
-      <c r="M88" s="143" t="n">
+      <c r="F88" s="149" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="149" t="n"/>
+      <c r="I88" s="149" t="n"/>
+      <c r="J88" s="149" t="n"/>
+      <c r="K88" s="149" t="n"/>
+      <c r="L88" s="149" t="n"/>
+      <c r="M88" s="149" t="n">
         <v>1520</v>
       </c>
-      <c r="N88" s="143" t="n">
+      <c r="N88" s="149" t="n">
         <v>2441</v>
       </c>
-      <c r="O88" s="143" t="n">
+      <c r="O88" s="149" t="n">
         <v>94000</v>
       </c>
-      <c r="P88" s="143" t="n">
+      <c r="P88" s="149" t="n">
         <v>38983</v>
       </c>
-      <c r="Q88" s="143" t="n">
+      <c r="Q88" s="149" t="n">
         <v>31000</v>
       </c>
-      <c r="R88" s="143" t="n">
+      <c r="R88" s="149" t="n">
         <v>70000</v>
       </c>
-      <c r="S88" s="143" t="n">
+      <c r="S88" s="149" t="n">
         <v>75320</v>
       </c>
-      <c r="T88" s="143" t="n">
+      <c r="T88" s="149" t="n">
         <v>16200</v>
       </c>
-      <c r="U88" s="143" t="n">
+      <c r="U88" s="149" t="n">
         <v>8560</v>
       </c>
-      <c r="V88" s="143" t="n">
+      <c r="V88" s="149" t="n">
         <v>9290</v>
       </c>
-      <c r="W88" s="143" t="n">
+      <c r="W88" s="149" t="n">
         <v>18000</v>
       </c>
-      <c r="X88" s="143" t="n">
+      <c r="X88" s="149" t="n">
         <v>7180</v>
       </c>
-      <c r="Y88" s="143" t="n">
+      <c r="Y88" s="149" t="n">
         <v>4800</v>
       </c>
-      <c r="Z88" s="143" t="n">
+      <c r="Z88" s="149" t="n">
         <v>3640</v>
       </c>
-      <c r="AA88" s="143" t="n"/>
-      <c r="AB88" s="143" t="n"/>
-      <c r="AC88" s="143" t="n"/>
-      <c r="AD88" s="143" t="n"/>
-      <c r="AE88" s="143" t="n"/>
-      <c r="AF88" s="143" t="n"/>
-      <c r="AG88" s="143" t="n"/>
-      <c r="AH88" s="143" t="n"/>
+      <c r="AA88" s="149" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AB88" s="149" t="n"/>
+      <c r="AC88" s="149" t="n"/>
+      <c r="AD88" s="149" t="n"/>
+      <c r="AE88" s="149" t="n"/>
+      <c r="AF88" s="149" t="n"/>
+      <c r="AG88" s="149" t="n"/>
+      <c r="AH88" s="149" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1" s="118">
       <c r="C89" s="142" t="inlineStr">
@@ -9687,53 +9797,55 @@
           <t>Clients</t>
         </is>
       </c>
-      <c r="D89" s="143" t="n">
+      <c r="D89" s="149" t="n">
         <v>53</v>
       </c>
-      <c r="E89" s="143" t="n">
+      <c r="E89" s="149" t="n">
         <v>841</v>
       </c>
-      <c r="F89" s="143" t="n"/>
-      <c r="G89" s="143" t="n"/>
-      <c r="H89" s="143" t="n"/>
-      <c r="I89" s="143" t="n"/>
-      <c r="J89" s="143" t="n"/>
-      <c r="K89" s="143" t="n"/>
-      <c r="L89" s="143" t="n"/>
-      <c r="M89" s="143" t="n"/>
-      <c r="N89" s="143" t="n">
+      <c r="F89" s="149" t="n"/>
+      <c r="G89" s="149" t="n"/>
+      <c r="H89" s="149" t="n"/>
+      <c r="I89" s="149" t="n"/>
+      <c r="J89" s="149" t="n"/>
+      <c r="K89" s="149" t="n"/>
+      <c r="L89" s="149" t="n"/>
+      <c r="M89" s="149" t="n"/>
+      <c r="N89" s="149" t="n">
         <v>353</v>
       </c>
-      <c r="O89" s="143" t="n">
+      <c r="O89" s="149" t="n">
         <v>375</v>
       </c>
-      <c r="P89" s="143" t="n">
+      <c r="P89" s="149" t="n">
         <v>346</v>
       </c>
-      <c r="Q89" s="143" t="n"/>
-      <c r="R89" s="143" t="n"/>
-      <c r="S89" s="143" t="n"/>
-      <c r="T89" s="143" t="n"/>
-      <c r="U89" s="143" t="n"/>
-      <c r="V89" s="143" t="n"/>
-      <c r="W89" s="143" t="n"/>
-      <c r="X89" s="143" t="n">
+      <c r="Q89" s="149" t="n"/>
+      <c r="R89" s="149" t="n"/>
+      <c r="S89" s="149" t="n"/>
+      <c r="T89" s="149" t="n"/>
+      <c r="U89" s="149" t="n"/>
+      <c r="V89" s="149" t="n"/>
+      <c r="W89" s="149" t="n"/>
+      <c r="X89" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Y89" s="143" t="n">
+      <c r="Y89" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="143" t="n">
+      <c r="Z89" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AA89" s="143" t="n"/>
-      <c r="AB89" s="143" t="n"/>
-      <c r="AC89" s="143" t="n"/>
-      <c r="AD89" s="143" t="n"/>
-      <c r="AE89" s="143" t="n"/>
-      <c r="AF89" s="143" t="n"/>
-      <c r="AG89" s="143" t="n"/>
-      <c r="AH89" s="143" t="n"/>
+      <c r="AA89" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="149" t="n"/>
+      <c r="AC89" s="149" t="n"/>
+      <c r="AD89" s="149" t="n"/>
+      <c r="AE89" s="149" t="n"/>
+      <c r="AF89" s="149" t="n"/>
+      <c r="AG89" s="149" t="n"/>
+      <c r="AH89" s="149" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="118">
       <c r="C90" s="142" t="inlineStr">
@@ -10788,79 +10900,81 @@
           <t>Unique uploads</t>
         </is>
       </c>
-      <c r="D104" s="143" t="n"/>
-      <c r="E104" s="143" t="n"/>
-      <c r="F104" s="143" t="n">
+      <c r="D104" s="149" t="n"/>
+      <c r="E104" s="149" t="n"/>
+      <c r="F104" s="149" t="n">
         <v>370</v>
       </c>
-      <c r="G104" s="143" t="n">
+      <c r="G104" s="149" t="n">
         <v>656</v>
       </c>
-      <c r="H104" s="143" t="n">
+      <c r="H104" s="149" t="n">
         <v>1315</v>
       </c>
-      <c r="I104" s="143" t="n">
+      <c r="I104" s="149" t="n">
         <v>1526</v>
       </c>
-      <c r="J104" s="143" t="n">
+      <c r="J104" s="149" t="n">
         <v>314</v>
       </c>
-      <c r="K104" s="143" t="n">
+      <c r="K104" s="149" t="n">
         <v>334</v>
       </c>
-      <c r="L104" s="143" t="n">
+      <c r="L104" s="149" t="n">
         <v>326</v>
       </c>
-      <c r="M104" s="143" t="n">
+      <c r="M104" s="149" t="n">
         <v>270</v>
       </c>
-      <c r="N104" s="143" t="n">
+      <c r="N104" s="149" t="n">
         <v>205</v>
       </c>
-      <c r="O104" s="143" t="n">
+      <c r="O104" s="149" t="n">
         <v>210</v>
       </c>
-      <c r="P104" s="143" t="n">
+      <c r="P104" s="149" t="n">
         <v>208</v>
       </c>
-      <c r="Q104" s="143" t="n">
+      <c r="Q104" s="149" t="n">
         <v>309</v>
       </c>
-      <c r="R104" s="143" t="n">
+      <c r="R104" s="149" t="n">
         <v>407</v>
       </c>
-      <c r="S104" s="143" t="n">
+      <c r="S104" s="149" t="n">
         <v>238</v>
       </c>
-      <c r="T104" s="143" t="n">
+      <c r="T104" s="149" t="n">
         <v>375</v>
       </c>
-      <c r="U104" s="143" t="n">
+      <c r="U104" s="149" t="n">
         <v>443</v>
       </c>
-      <c r="V104" s="143" t="n">
+      <c r="V104" s="149" t="n">
         <v>304</v>
       </c>
-      <c r="W104" s="143" t="n">
+      <c r="W104" s="149" t="n">
         <v>191</v>
       </c>
-      <c r="X104" s="143" t="n">
+      <c r="X104" s="149" t="n">
         <v>168</v>
       </c>
       <c r="Y104" s="149" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="Z104" s="149" t="n">
-        <v>186</v>
-      </c>
-      <c r="AA104" s="143" t="n"/>
-      <c r="AB104" s="143" t="n"/>
-      <c r="AC104" s="143" t="n"/>
-      <c r="AD104" s="143" t="n"/>
-      <c r="AE104" s="143" t="n"/>
-      <c r="AF104" s="143" t="n"/>
-      <c r="AG104" s="143" t="n"/>
-      <c r="AH104" s="143" t="n"/>
+        <v>174</v>
+      </c>
+      <c r="AA104" s="149" t="n">
+        <v>189</v>
+      </c>
+      <c r="AB104" s="149" t="n"/>
+      <c r="AC104" s="149" t="n"/>
+      <c r="AD104" s="149" t="n"/>
+      <c r="AE104" s="149" t="n"/>
+      <c r="AF104" s="149" t="n"/>
+      <c r="AG104" s="149" t="n"/>
+      <c r="AH104" s="149" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1" s="118">
       <c r="C105" s="142" t="inlineStr">
@@ -10868,63 +10982,63 @@
           <t>New customer</t>
         </is>
       </c>
-      <c r="D105" s="143" t="n"/>
-      <c r="E105" s="143" t="n"/>
-      <c r="F105" s="143" t="n">
+      <c r="D105" s="149" t="n"/>
+      <c r="E105" s="149" t="n"/>
+      <c r="F105" s="149" t="n">
         <v>75</v>
       </c>
-      <c r="G105" s="143" t="n">
+      <c r="G105" s="149" t="n">
         <v>148</v>
       </c>
-      <c r="H105" s="143" t="n">
+      <c r="H105" s="149" t="n">
         <v>288</v>
       </c>
-      <c r="I105" s="143" t="n">
+      <c r="I105" s="149" t="n">
         <v>83</v>
       </c>
-      <c r="J105" s="143" t="n">
+      <c r="J105" s="149" t="n">
         <v>66</v>
       </c>
-      <c r="K105" s="143" t="n">
+      <c r="K105" s="149" t="n">
         <v>32</v>
       </c>
-      <c r="L105" s="143" t="n">
+      <c r="L105" s="149" t="n">
         <v>83</v>
       </c>
-      <c r="M105" s="143" t="n">
+      <c r="M105" s="149" t="n">
         <v>50</v>
       </c>
-      <c r="N105" s="143" t="n">
+      <c r="N105" s="149" t="n">
         <v>38</v>
       </c>
-      <c r="O105" s="143" t="n">
+      <c r="O105" s="149" t="n">
         <v>30</v>
       </c>
-      <c r="P105" s="143" t="n">
+      <c r="P105" s="149" t="n">
         <v>37</v>
       </c>
-      <c r="Q105" s="143" t="n">
+      <c r="Q105" s="149" t="n">
         <v>31</v>
       </c>
-      <c r="R105" s="143" t="n">
+      <c r="R105" s="149" t="n">
         <v>42</v>
       </c>
-      <c r="S105" s="143" t="n">
+      <c r="S105" s="149" t="n">
         <v>30</v>
       </c>
-      <c r="T105" s="143" t="n">
+      <c r="T105" s="149" t="n">
         <v>43</v>
       </c>
-      <c r="U105" s="143" t="n">
+      <c r="U105" s="149" t="n">
         <v>56</v>
       </c>
-      <c r="V105" s="143" t="n">
+      <c r="V105" s="149" t="n">
         <v>45</v>
       </c>
-      <c r="W105" s="143" t="n">
+      <c r="W105" s="149" t="n">
         <v>21</v>
       </c>
-      <c r="X105" s="143" t="n">
+      <c r="X105" s="149" t="n">
         <v>29</v>
       </c>
       <c r="Y105" s="149" t="n">
@@ -10933,14 +11047,16 @@
       <c r="Z105" s="149" t="n">
         <v>20</v>
       </c>
-      <c r="AA105" s="143" t="n"/>
-      <c r="AB105" s="143" t="n"/>
-      <c r="AC105" s="143" t="n"/>
-      <c r="AD105" s="143" t="n"/>
-      <c r="AE105" s="143" t="n"/>
-      <c r="AF105" s="143" t="n"/>
-      <c r="AG105" s="143" t="n"/>
-      <c r="AH105" s="143" t="n"/>
+      <c r="AA105" s="149" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB105" s="149" t="n"/>
+      <c r="AC105" s="149" t="n"/>
+      <c r="AD105" s="149" t="n"/>
+      <c r="AE105" s="149" t="n"/>
+      <c r="AF105" s="149" t="n"/>
+      <c r="AG105" s="149" t="n"/>
+      <c r="AH105" s="149" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1" s="118">
       <c r="C106" s="142" t="inlineStr">
@@ -10948,63 +11064,63 @@
           <t>Omkostning (kr.)</t>
         </is>
       </c>
-      <c r="D106" s="143" t="n"/>
-      <c r="E106" s="143" t="n"/>
-      <c r="F106" s="143" t="n">
+      <c r="D106" s="149" t="n"/>
+      <c r="E106" s="149" t="n"/>
+      <c r="F106" s="149" t="n">
         <v>4411</v>
       </c>
-      <c r="G106" s="143" t="n">
+      <c r="G106" s="149" t="n">
         <v>8645</v>
       </c>
-      <c r="H106" s="143" t="n">
+      <c r="H106" s="149" t="n">
         <v>14861</v>
       </c>
-      <c r="I106" s="143" t="n">
+      <c r="I106" s="149" t="n">
         <v>6972</v>
       </c>
-      <c r="J106" s="143" t="n">
+      <c r="J106" s="149" t="n">
         <v>6138</v>
       </c>
-      <c r="K106" s="143" t="n">
+      <c r="K106" s="149" t="n">
         <v>6150</v>
       </c>
-      <c r="L106" s="143" t="n">
+      <c r="L106" s="149" t="n">
         <v>3818</v>
       </c>
-      <c r="M106" s="143" t="n">
+      <c r="M106" s="149" t="n">
         <v>3855</v>
       </c>
-      <c r="N106" s="143" t="n">
+      <c r="N106" s="149" t="n">
         <v>5125</v>
       </c>
-      <c r="O106" s="143" t="n">
+      <c r="O106" s="149" t="n">
         <v>4688</v>
       </c>
-      <c r="P106" s="143" t="n">
+      <c r="P106" s="149" t="n">
         <v>5021</v>
       </c>
-      <c r="Q106" s="143" t="n">
+      <c r="Q106" s="149" t="n">
         <v>5499</v>
       </c>
-      <c r="R106" s="143" t="n">
+      <c r="R106" s="149" t="n">
         <v>5502</v>
       </c>
-      <c r="S106" s="143" t="n">
+      <c r="S106" s="149" t="n">
         <v>4690</v>
       </c>
-      <c r="T106" s="143" t="n">
+      <c r="T106" s="149" t="n">
         <v>4367</v>
       </c>
-      <c r="U106" s="143" t="n">
+      <c r="U106" s="149" t="n">
         <v>6726</v>
       </c>
-      <c r="V106" s="143" t="n">
+      <c r="V106" s="149" t="n">
         <v>5712</v>
       </c>
-      <c r="W106" s="143" t="n">
+      <c r="W106" s="149" t="n">
         <v>4625</v>
       </c>
-      <c r="X106" s="143" t="n">
+      <c r="X106" s="149" t="n">
         <v>4554</v>
       </c>
       <c r="Y106" s="149" t="n">
@@ -11013,14 +11129,16 @@
       <c r="Z106" s="149" t="n">
         <v>3917.7</v>
       </c>
-      <c r="AA106" s="143" t="n"/>
-      <c r="AB106" s="143" t="n"/>
-      <c r="AC106" s="143" t="n"/>
-      <c r="AD106" s="143" t="n"/>
-      <c r="AE106" s="143" t="n"/>
-      <c r="AF106" s="143" t="n"/>
-      <c r="AG106" s="143" t="n"/>
-      <c r="AH106" s="143" t="n"/>
+      <c r="AA106" s="149" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB106" s="149" t="n"/>
+      <c r="AC106" s="149" t="n"/>
+      <c r="AD106" s="149" t="n"/>
+      <c r="AE106" s="149" t="n"/>
+      <c r="AF106" s="149" t="n"/>
+      <c r="AG106" s="149" t="n"/>
+      <c r="AH106" s="149" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1" s="118">
       <c r="C107" s="142" t="inlineStr">
@@ -13286,83 +13404,85 @@
           <t>Total signups (alle, inkl. non-marketing)</t>
         </is>
       </c>
-      <c r="D129" s="143" t="n">
+      <c r="D129" s="149" t="n">
         <v>424</v>
       </c>
-      <c r="E129" s="143" t="n">
+      <c r="E129" s="149" t="n">
         <v>1192</v>
       </c>
-      <c r="F129" s="143" t="n">
+      <c r="F129" s="149" t="n">
         <v>782</v>
       </c>
-      <c r="G129" s="143" t="n">
+      <c r="G129" s="149" t="n">
         <v>632</v>
       </c>
-      <c r="H129" s="143" t="n">
+      <c r="H129" s="149" t="n">
         <v>1115</v>
       </c>
-      <c r="I129" s="143" t="n">
+      <c r="I129" s="149" t="n">
         <v>604</v>
       </c>
-      <c r="J129" s="143" t="n">
+      <c r="J129" s="149" t="n">
         <v>600</v>
       </c>
-      <c r="K129" s="143" t="n">
+      <c r="K129" s="149" t="n">
         <v>457</v>
       </c>
-      <c r="L129" s="143" t="n">
+      <c r="L129" s="149" t="n">
         <v>603</v>
       </c>
-      <c r="M129" s="143" t="n">
+      <c r="M129" s="149" t="n">
         <v>654</v>
       </c>
-      <c r="N129" s="143" t="n">
+      <c r="N129" s="149" t="n">
         <v>558</v>
       </c>
-      <c r="O129" s="143" t="n">
+      <c r="O129" s="149" t="n">
         <v>577</v>
       </c>
-      <c r="P129" s="143" t="n">
+      <c r="P129" s="149" t="n">
         <v>548</v>
       </c>
-      <c r="Q129" s="143" t="n">
+      <c r="Q129" s="149" t="n">
         <v>598</v>
       </c>
-      <c r="R129" s="143" t="n">
+      <c r="R129" s="149" t="n">
         <v>920</v>
       </c>
-      <c r="S129" s="143" t="n">
+      <c r="S129" s="149" t="n">
         <v>760</v>
       </c>
-      <c r="T129" s="143" t="n">
+      <c r="T129" s="149" t="n">
         <v>1178</v>
       </c>
-      <c r="U129" s="143" t="n">
+      <c r="U129" s="149" t="n">
         <v>1300</v>
       </c>
-      <c r="V129" s="143" t="n">
+      <c r="V129" s="149" t="n">
         <v>1286</v>
       </c>
-      <c r="W129" s="143" t="n">
+      <c r="W129" s="149" t="n">
         <v>1144</v>
       </c>
-      <c r="X129" s="143" t="n">
+      <c r="X129" s="149" t="n">
         <v>1035</v>
       </c>
-      <c r="Y129" s="143" t="n">
+      <c r="Y129" s="149" t="n">
         <v>984</v>
       </c>
-      <c r="Z129" s="143" t="n">
+      <c r="Z129" s="149" t="n">
         <v>1461</v>
       </c>
-      <c r="AA129" s="143" t="n"/>
-      <c r="AB129" s="143" t="n"/>
-      <c r="AC129" s="143" t="n"/>
-      <c r="AD129" s="143" t="n"/>
-      <c r="AE129" s="143" t="n"/>
-      <c r="AF129" s="143" t="n"/>
-      <c r="AG129" s="143" t="n"/>
-      <c r="AH129" s="143" t="n"/>
+      <c r="AA129" s="149" t="n">
+        <v>1250</v>
+      </c>
+      <c r="AB129" s="149" t="n"/>
+      <c r="AC129" s="149" t="n"/>
+      <c r="AD129" s="149" t="n"/>
+      <c r="AE129" s="149" t="n"/>
+      <c r="AF129" s="149" t="n"/>
+      <c r="AG129" s="149" t="n"/>
+      <c r="AH129" s="149" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1" s="118">
       <c r="C130" s="142" t="inlineStr">
@@ -13370,45 +13490,47 @@
           <t>Space timer brugt (denne måned)</t>
         </is>
       </c>
-      <c r="D130" s="143" t="n"/>
-      <c r="E130" s="143" t="n"/>
-      <c r="F130" s="143" t="n"/>
-      <c r="G130" s="143" t="n"/>
-      <c r="H130" s="143" t="n"/>
-      <c r="I130" s="143" t="n"/>
-      <c r="J130" s="143" t="n"/>
-      <c r="K130" s="143" t="n"/>
-      <c r="L130" s="143" t="n"/>
-      <c r="M130" s="143" t="n"/>
-      <c r="N130" s="143" t="n"/>
-      <c r="O130" s="143" t="n"/>
-      <c r="P130" s="143" t="n"/>
-      <c r="Q130" s="143" t="n"/>
-      <c r="R130" s="143" t="n"/>
-      <c r="S130" s="143" t="n"/>
-      <c r="T130" s="143" t="n"/>
-      <c r="U130" s="143" t="n"/>
-      <c r="V130" s="143" t="n"/>
-      <c r="W130" s="143" t="n">
+      <c r="D130" s="149" t="n"/>
+      <c r="E130" s="149" t="n"/>
+      <c r="F130" s="149" t="n"/>
+      <c r="G130" s="149" t="n"/>
+      <c r="H130" s="149" t="n"/>
+      <c r="I130" s="149" t="n"/>
+      <c r="J130" s="149" t="n"/>
+      <c r="K130" s="149" t="n"/>
+      <c r="L130" s="149" t="n"/>
+      <c r="M130" s="149" t="n"/>
+      <c r="N130" s="149" t="n"/>
+      <c r="O130" s="149" t="n"/>
+      <c r="P130" s="149" t="n"/>
+      <c r="Q130" s="149" t="n"/>
+      <c r="R130" s="149" t="n"/>
+      <c r="S130" s="149" t="n"/>
+      <c r="T130" s="149" t="n"/>
+      <c r="U130" s="149" t="n"/>
+      <c r="V130" s="149" t="n"/>
+      <c r="W130" s="149" t="n">
         <v>10</v>
       </c>
-      <c r="X130" s="143" t="n">
+      <c r="X130" s="149" t="n">
         <v>9.33</v>
       </c>
-      <c r="Y130" s="143" t="n">
+      <c r="Y130" s="149" t="n">
         <v>15</v>
       </c>
-      <c r="Z130" s="143" t="n">
+      <c r="Z130" s="149" t="n">
         <v>3</v>
       </c>
-      <c r="AA130" s="143" t="n"/>
-      <c r="AB130" s="143" t="n"/>
-      <c r="AC130" s="143" t="n"/>
-      <c r="AD130" s="143" t="n"/>
-      <c r="AE130" s="143" t="n"/>
-      <c r="AF130" s="143" t="n"/>
-      <c r="AG130" s="143" t="n"/>
-      <c r="AH130" s="143" t="n"/>
+      <c r="AA130" s="149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB130" s="149" t="n"/>
+      <c r="AC130" s="149" t="n"/>
+      <c r="AD130" s="149" t="n"/>
+      <c r="AE130" s="149" t="n"/>
+      <c r="AF130" s="149" t="n"/>
+      <c r="AG130" s="149" t="n"/>
+      <c r="AH130" s="149" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1" s="118">
       <c r="C131" s="142" t="inlineStr">
@@ -13416,29 +13538,31 @@
           <t>Space timer brugt (akkumuleret total)</t>
         </is>
       </c>
-      <c r="V131" s="143" t="n">
+      <c r="V131" s="149" t="n">
         <v>573</v>
       </c>
-      <c r="W131" s="143" t="n">
+      <c r="W131" s="149" t="n">
         <v>583</v>
       </c>
-      <c r="X131" s="143" t="n">
+      <c r="X131" s="149" t="n">
         <v>592.33</v>
       </c>
-      <c r="Y131" s="143" t="n">
+      <c r="Y131" s="149" t="n">
         <v>607.33</v>
       </c>
-      <c r="Z131" s="143" t="n">
+      <c r="Z131" s="149" t="n">
         <v>610.33</v>
       </c>
-      <c r="AA131" s="143" t="n"/>
-      <c r="AB131" s="143" t="n"/>
-      <c r="AC131" s="143" t="n"/>
-      <c r="AD131" s="143" t="n"/>
-      <c r="AE131" s="143" t="n"/>
-      <c r="AF131" s="143" t="n"/>
-      <c r="AG131" s="143" t="n"/>
-      <c r="AH131" s="143" t="n"/>
+      <c r="AA131" s="149" t="n">
+        <v>618.33</v>
+      </c>
+      <c r="AB131" s="149" t="n"/>
+      <c r="AC131" s="149" t="n"/>
+      <c r="AD131" s="149" t="n"/>
+      <c r="AE131" s="149" t="n"/>
+      <c r="AF131" s="149" t="n"/>
+      <c r="AG131" s="149" t="n"/>
+      <c r="AH131" s="149" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1" s="118">
       <c r="C132" s="142" t="inlineStr">
@@ -13446,75 +13570,77 @@
           <t>Aktive kunder (slut af måned)</t>
         </is>
       </c>
-      <c r="D132" s="143" t="n"/>
-      <c r="E132" s="143" t="n"/>
-      <c r="F132" s="143" t="n"/>
-      <c r="G132" s="143" t="n"/>
-      <c r="H132" s="143" t="n">
+      <c r="D132" s="149" t="n"/>
+      <c r="E132" s="149" t="n"/>
+      <c r="F132" s="149" t="n"/>
+      <c r="G132" s="149" t="n"/>
+      <c r="H132" s="149" t="n">
         <v>4708</v>
       </c>
-      <c r="I132" s="143" t="n">
+      <c r="I132" s="149" t="n">
         <v>5518</v>
       </c>
-      <c r="J132" s="143" t="n">
+      <c r="J132" s="149" t="n">
         <v>5990</v>
       </c>
-      <c r="K132" s="143" t="n">
+      <c r="K132" s="149" t="n">
         <v>6422</v>
       </c>
-      <c r="L132" s="143" t="n">
+      <c r="L132" s="149" t="n">
         <v>6737</v>
       </c>
-      <c r="M132" s="143" t="n">
+      <c r="M132" s="149" t="n">
         <v>7008</v>
       </c>
-      <c r="N132" s="143" t="n">
+      <c r="N132" s="149" t="n">
         <v>7498</v>
       </c>
-      <c r="O132" s="143" t="n">
+      <c r="O132" s="149" t="n">
         <v>7802</v>
       </c>
-      <c r="P132" s="143" t="n">
+      <c r="P132" s="149" t="n">
         <v>8178</v>
       </c>
-      <c r="Q132" s="143" t="n">
+      <c r="Q132" s="149" t="n">
         <v>8411</v>
       </c>
-      <c r="R132" s="143" t="n">
+      <c r="R132" s="149" t="n">
         <v>8728</v>
       </c>
-      <c r="S132" s="143" t="n">
+      <c r="S132" s="149" t="n">
         <v>9100</v>
       </c>
-      <c r="T132" s="143" t="n">
+      <c r="T132" s="149" t="n">
         <v>9650</v>
       </c>
-      <c r="U132" s="143" t="n">
+      <c r="U132" s="149" t="n">
         <v>10389</v>
       </c>
-      <c r="V132" s="143" t="n">
+      <c r="V132" s="149" t="n">
         <v>11290</v>
       </c>
-      <c r="W132" s="143" t="n">
+      <c r="W132" s="149" t="n">
         <v>11998</v>
       </c>
-      <c r="X132" s="143" t="n">
+      <c r="X132" s="149" t="n">
         <v>12736</v>
       </c>
-      <c r="Y132" s="143" t="n">
+      <c r="Y132" s="149" t="n">
         <v>13318</v>
       </c>
-      <c r="Z132" s="143" t="n">
+      <c r="Z132" s="149" t="n">
         <v>13970</v>
       </c>
-      <c r="AA132" s="143" t="n"/>
-      <c r="AB132" s="143" t="n"/>
-      <c r="AC132" s="143" t="n"/>
-      <c r="AD132" s="143" t="n"/>
-      <c r="AE132" s="143" t="n"/>
-      <c r="AF132" s="143" t="n"/>
-      <c r="AG132" s="143" t="n"/>
-      <c r="AH132" s="143" t="n"/>
+      <c r="AA132" s="149" t="n">
+        <v>14748</v>
+      </c>
+      <c r="AB132" s="149" t="n"/>
+      <c r="AC132" s="149" t="n"/>
+      <c r="AD132" s="149" t="n"/>
+      <c r="AE132" s="149" t="n"/>
+      <c r="AF132" s="149" t="n"/>
+      <c r="AG132" s="149" t="n"/>
+      <c r="AH132" s="149" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" s="118">
       <c r="C133" s="142" t="inlineStr">
@@ -13583,7 +13709,9 @@
       <c r="Z133" s="154" t="n">
         <v>0.022</v>
       </c>
-      <c r="AA133" s="154" t="n"/>
+      <c r="AA133" s="154" t="n">
+        <v>0.025</v>
+      </c>
       <c r="AB133" s="154" t="n"/>
       <c r="AC133" s="154" t="n"/>
       <c r="AD133" s="154" t="n"/>
@@ -13663,6 +13791,9 @@
       </c>
       <c r="Y134" s="117" t="n">
         <v>296715</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>394660</v>
       </c>
     </row>
   </sheetData>

--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -9207,7 +9207,7 @@
         <v>3917.7</v>
       </c>
       <c r="AA78" s="149" t="n">
-        <v>3000</v>
+        <v>4180</v>
       </c>
       <c r="AB78" s="149" t="n"/>
       <c r="AC78" s="149" t="n"/>
@@ -11130,7 +11130,7 @@
         <v>3917.7</v>
       </c>
       <c r="AA106" s="149" t="n">
-        <v>3000</v>
+        <v>4180</v>
       </c>
       <c r="AB106" s="149" t="n"/>
       <c r="AC106" s="149" t="n"/>
@@ -13792,7 +13792,7 @@
       <c r="Y134" s="117" t="n">
         <v>296715</v>
       </c>
-      <c r="Z134" t="n">
+      <c r="Z134" s="117" t="n">
         <v>394660</v>
       </c>
     </row>
